--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>UD Value</t>
+          <t>Adjusted Value</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00008000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF7F50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -114,19 +119,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -494,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +608,7 @@
         <v>56</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -632,7 +640,7 @@
         <v>55</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -677,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -693,7 +701,7 @@
         <v>54</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>5</v>
@@ -709,7 +717,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -725,7 +733,7 @@
         <v>53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>6</v>
@@ -741,7 +749,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -757,7 +765,7 @@
         <v>52</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>7</v>
@@ -837,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -852,8 +860,8 @@
       <c r="F11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>50</v>
+      <c r="G11" s="6" t="n">
+        <v>45</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>10</v>
@@ -900,8 +908,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>13</v>
+      <c r="C13" s="6" t="n">
+        <v>23</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -916,8 +924,8 @@
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>45</v>
+      <c r="G13" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
@@ -933,7 +941,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -948,8 +956,8 @@
       <c r="F14" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>33</v>
+      <c r="G14" s="4" t="n">
+        <v>36</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
@@ -964,8 +972,8 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>24</v>
+      <c r="C15" s="7" t="n">
+        <v>31</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -980,8 +988,8 @@
       <c r="F15" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>32</v>
+      <c r="G15" s="7" t="n">
+        <v>26</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14</v>
@@ -996,8 +1004,8 @@
       <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>12</v>
+      <c r="C16" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1021,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
@@ -1028,8 +1036,8 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>28</v>
+      <c r="C17" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1044,8 +1052,8 @@
       <c r="F17" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>29</v>
+      <c r="G17" s="7" t="n">
+        <v>28</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
@@ -1060,8 +1068,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>14</v>
+      <c r="C18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1077,7 +1085,7 @@
         <v>38</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1093,7 +1101,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1108,8 +1116,8 @@
       <c r="F19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>38</v>
+      <c r="G19" s="6" t="n">
+        <v>33</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
@@ -1124,8 +1132,8 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>16</v>
+      <c r="C20" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1141,7 +1149,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
@@ -1156,8 +1164,8 @@
       <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>19</v>
+      <c r="C21" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1173,7 +1181,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
@@ -1188,8 +1196,8 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>25</v>
+      <c r="C22" s="7" t="n">
+        <v>35</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1204,8 +1212,8 @@
       <c r="F22" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>31</v>
+      <c r="G22" s="7" t="n">
+        <v>22</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1220,8 +1228,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>20</v>
+      <c r="C23" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1237,7 +1245,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
@@ -1253,7 +1261,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1269,10 +1277,10 @@
         <v>32</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -1284,8 +1292,8 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>15</v>
+      <c r="C25" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1301,10 +1309,10 @@
         <v>32</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1316,8 +1324,8 @@
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>29</v>
+      <c r="C26" s="4" t="n">
+        <v>20</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1332,8 +1340,8 @@
       <c r="F26" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>28</v>
+      <c r="G26" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
@@ -1348,7 +1356,7 @@
       <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="7" t="n">
         <v>40</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1368,7 +1376,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1380,8 +1388,8 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="6" t="n">
-        <v>37</v>
+      <c r="C28" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1390,17 +1398,17 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>22</v>
+      <c r="G28" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1412,8 +1420,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="6" t="n">
-        <v>35</v>
+      <c r="C29" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1428,8 +1436,8 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <v>22</v>
+      <c r="G29" s="4" t="n">
+        <v>27</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
@@ -1444,8 +1452,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>21</v>
+      <c r="C30" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1461,7 +1469,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
@@ -1476,8 +1484,8 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="7" t="n">
-        <v>18</v>
+      <c r="C31" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1492,8 +1500,8 @@
       <c r="F31" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>37</v>
+      <c r="G31" s="9" t="n">
+        <v>46</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1508,8 +1516,8 @@
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="4" t="n">
-        <v>33</v>
+      <c r="C32" s="9" t="n">
+        <v>27</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1533,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
@@ -1540,8 +1548,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>31</v>
+      <c r="C33" s="6" t="n">
+        <v>37</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1557,7 +1565,7 @@
         <v>25</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
@@ -1573,7 +1581,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1597,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1604,8 +1612,8 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>36</v>
+      <c r="C35" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1620,8 +1628,8 @@
       <c r="F35" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>22</v>
+      <c r="G35" s="10" t="n">
+        <v>31</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
@@ -1636,8 +1644,8 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="9" t="n">
-        <v>50</v>
+      <c r="C36" s="4" t="n">
+        <v>38</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1652,11 +1660,11 @@
       <c r="F36" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="6" t="n">
-        <v>13</v>
+      <c r="G36" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
@@ -1668,8 +1676,8 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="10" t="n">
-        <v>27</v>
+      <c r="C37" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1684,11 +1692,11 @@
       <c r="F37" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="10" t="n">
-        <v>30</v>
+      <c r="G37" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1700,8 +1708,8 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="4" t="n">
-        <v>34</v>
+      <c r="C38" s="9" t="n">
+        <v>28</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1717,7 +1725,7 @@
         <v>22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>36</v>
@@ -1732,8 +1740,8 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="7" t="n">
-        <v>26</v>
+      <c r="C39" s="4" t="n">
+        <v>36</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1749,7 +1757,7 @@
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>39</v>
@@ -1765,7 +1773,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1780,8 +1788,8 @@
       <c r="F40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>17</v>
+      <c r="G40" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>38</v>
@@ -1797,7 +1805,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1813,7 +1821,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1829,7 +1837,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1844,8 +1852,8 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="4" t="n">
-        <v>21</v>
+      <c r="G42" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>41</v>
@@ -1860,8 +1868,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="7" t="n">
-        <v>23</v>
+      <c r="C43" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1876,8 +1884,8 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="7" t="n">
-        <v>32</v>
+      <c r="G43" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>42</v>
@@ -1893,7 +1901,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1909,7 +1917,7 @@
         <v>18</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
@@ -1925,7 +1933,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1940,8 +1948,8 @@
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>21</v>
+      <c r="G45" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
@@ -1956,8 +1964,8 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="6" t="n">
-        <v>54</v>
+      <c r="C46" s="4" t="n">
+        <v>46</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1972,8 +1980,8 @@
       <c r="F46" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G46" s="6" t="n">
-        <v>10</v>
+      <c r="G46" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
@@ -1988,8 +1996,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="7" t="n">
-        <v>32</v>
+      <c r="C47" s="9" t="n">
+        <v>26</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2004,8 +2012,8 @@
       <c r="F47" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G47" s="7" t="n">
-        <v>25</v>
+      <c r="G47" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>46</v>
@@ -2020,8 +2028,8 @@
       <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="4" t="n">
-        <v>41</v>
+      <c r="C48" s="9" t="n">
+        <v>32</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2036,8 +2044,8 @@
       <c r="F48" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G48" s="10" t="n">
-        <v>19</v>
+      <c r="G48" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>47</v>
@@ -2053,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2068,8 +2076,8 @@
       <c r="F49" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G49" s="10" t="n">
-        <v>18</v>
+      <c r="G49" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2084,8 +2092,8 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>48</v>
+      <c r="C50" s="10" t="n">
+        <v>41</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2100,11 +2108,11 @@
       <c r="F50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>14</v>
+      <c r="G50" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -2117,7 +2125,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2133,10 +2141,10 @@
         <v>13</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2148,8 +2156,8 @@
       <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="6" t="n">
-        <v>58</v>
+      <c r="C52" s="7" t="n">
+        <v>73</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2164,8 +2172,8 @@
       <c r="F52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="4" t="n">
-        <v>9</v>
+      <c r="G52" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
@@ -2180,8 +2188,8 @@
       <c r="B53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C53" s="9" t="n">
-        <v>66</v>
+      <c r="C53" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2196,8 +2204,8 @@
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="6" t="n">
-        <v>7</v>
+      <c r="G53" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>52</v>
@@ -2212,8 +2220,8 @@
       <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="6" t="n">
-        <v>59</v>
+      <c r="C54" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2229,39 +2237,39 @@
         <v>11</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>54</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>10</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>54</v>
@@ -2274,29 +2282,29 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="C56" s="10" t="n">
-        <v>47</v>
-      </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
         <v>10</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57">
@@ -2306,29 +2314,29 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="C57" s="9" t="n">
-        <v>71</v>
+        <v>56</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>45</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G57" s="6" t="n">
-        <v>6</v>
+      <c r="G57" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58">
@@ -2338,61 +2346,61 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="C59" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Jalen Hurts</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60">
@@ -2402,19 +2410,19 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -2434,29 +2442,29 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62">
@@ -2466,29 +2474,29 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>46</v>
+        <v>61</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>69</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63">
@@ -2498,29 +2506,29 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="C63" s="7" t="n">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>51</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -2530,61 +2538,61 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="C65" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Tony Pollard</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>TEN</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Marvin Harrison</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ARI</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
@@ -2594,29 +2602,29 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>85</v>
+        <v>65</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>77</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
@@ -2626,19 +2634,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>113</v>
+        <v>66</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Michael Pittman</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -2658,14 +2666,14 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="C68" s="9" t="n">
-        <v>84</v>
+        <v>67</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>109</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Michael Pittman</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2674,13 +2682,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69">
@@ -2690,29 +2698,29 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>80</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70">
@@ -2722,61 +2730,61 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C70" s="6" t="n">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>72</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="C71" s="9" t="n">
-        <v>101</v>
+        <v>70</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>79</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Kyle Pitts</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="6" t="n">
-        <v>2</v>
+      <c r="G71" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72">
@@ -2786,29 +2794,29 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Harold Fannin</t>
+          <t>Kyle Pitts</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73">
@@ -2818,61 +2826,61 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Harold Fannin</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Sam LaPorta</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H73" s="3" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="H74" s="3" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -2882,51 +2890,51 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>55</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="C76" s="9" t="n">
-        <v>95</v>
+        <v>75</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>112</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
@@ -2936,7 +2944,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -2946,29 +2954,29 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>84</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
@@ -2978,14 +2986,14 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C78" s="9" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2994,13 +3002,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="G78" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79">
@@ -3010,26 +3018,26 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>82</v>
@@ -3042,29 +3050,29 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G80" s="4" t="n">
-        <v>5</v>
+      <c r="G80" s="9" t="n">
+        <v>13</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81">
@@ -3074,61 +3082,61 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="C81" s="9" t="n">
-        <v>112</v>
+        <v>80</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>61</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H81" s="3" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
         <v>81</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>93</v>
+      <c r="C82" s="7" t="n">
+        <v>137</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -3138,29 +3146,29 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84">
@@ -3170,29 +3178,29 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85">
@@ -3202,29 +3210,29 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>97</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86">
@@ -3234,19 +3242,19 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="C86" s="9" t="n">
-        <v>103</v>
+        <v>85</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>96</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -3256,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87">
@@ -3266,61 +3274,61 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Stafford</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>LAR</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C87" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="C88" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Caleb Williams</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>CHI</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="C88" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Wan'Dale Robinson</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89">
@@ -3330,29 +3338,29 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>149</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90">
@@ -3362,19 +3370,19 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -3384,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -3394,19 +3402,19 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="C91" s="9" t="n">
-        <v>111</v>
+        <v>90</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>108</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Ricky Pearsall</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -3416,7 +3424,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -3426,61 +3434,61 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Ricky Pearsall</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="C93" s="7" t="n">
-        <v>72</v>
+        <v>92</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94">
@@ -3490,61 +3498,61 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>102</v>
+        <v>93</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="C95" s="7" t="n">
-        <v>62</v>
+        <v>94</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>104</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96">
@@ -3554,29 +3562,29 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="C96" s="7" t="n">
-        <v>68</v>
+        <v>95</v>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>67</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97">
@@ -3586,29 +3594,29 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="C97" s="10" t="n">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>65</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98">
@@ -3618,29 +3626,29 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>61</v>
+        <v>97</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>94</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99">
@@ -3650,51 +3658,51 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>66</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -3704,29 +3712,29 @@
         <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -3746,19 +3754,19 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -3768,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103">
@@ -3778,93 +3786,93 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106">
@@ -3874,29 +3882,29 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>69</v>
+        <v>105</v>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>92</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107">
@@ -3906,19 +3914,19 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="C107" s="7" t="n">
-        <v>91</v>
+        <v>106</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -3928,71 +3936,71 @@
         <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>135</v>
+        <v>107</v>
+      </c>
+      <c r="C108" s="10" t="n">
+        <v>103</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C109" s="10" t="n">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>93</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110">
@@ -4002,93 +4010,93 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="C110" s="9" t="n">
-        <v>159</v>
+        <v>109</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>120</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C111" s="9" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C112" s="4" t="n">
-        <v>96</v>
+        <v>111</v>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>213</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113">
@@ -4098,115 +4106,115 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="C113" s="4" t="n">
-        <v>99</v>
+        <v>112</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>150</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -4216,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="117">
@@ -4226,29 +4234,29 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C117" s="4" t="n">
-        <v>125</v>
+        <v>116</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>216</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118">
@@ -4258,51 +4266,51 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="C118" s="4" t="n">
-        <v>161</v>
-      </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C119" s="7" t="n">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>106</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
@@ -4312,39 +4320,39 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C120" s="7" t="n">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>157</v>
+        <v>99</v>
       </c>
     </row>
     <row r="121">
@@ -4354,29 +4362,29 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122">
@@ -4386,51 +4394,51 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>107</v>
+        <v>121</v>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H122" s="3" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" s="4" t="n">
         <v>151</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>122</v>
-      </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
@@ -4440,39 +4448,39 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>86</v>
+        <v>123</v>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125">
@@ -4482,29 +4490,29 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126">
@@ -4514,19 +4522,19 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -4536,7 +4544,7 @@
         <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="127">
@@ -4546,29 +4554,29 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>114</v>
+        <v>126</v>
+      </c>
+      <c r="C127" s="10" t="n">
+        <v>89</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128">
@@ -4578,19 +4586,19 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C128" s="4" t="n">
         <v>127</v>
       </c>
+      <c r="C128" s="6" t="n">
+        <v>136</v>
+      </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -4600,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129">
@@ -4610,29 +4618,29 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C129" s="9" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130">
@@ -4642,29 +4650,29 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="C130" s="4" t="n">
-        <v>116</v>
-      </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="131">
@@ -4674,83 +4682,83 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="C131" s="6" t="n">
-        <v>144</v>
+        <v>130</v>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>200</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>89</v>
+        <v>131</v>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>134</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -4770,29 +4778,29 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135">
@@ -4802,51 +4810,51 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>191</v>
+        <v>135</v>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>177</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -4856,39 +4864,39 @@
         <v>0</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>188</v>
+        <v>136</v>
+      </c>
+      <c r="C137" s="10" t="n">
+        <v>114</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="138">
@@ -4898,29 +4906,29 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>154</v>
+        <v>137</v>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>244</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="139">
@@ -4930,29 +4938,29 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C139" s="7" t="n">
-        <v>110</v>
+        <v>138</v>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>171</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140">
@@ -4962,19 +4970,19 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -4984,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="141">
@@ -4994,93 +5002,93 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>166</v>
+        <v>140</v>
+      </c>
+      <c r="C141" s="9" t="n">
+        <v>110</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="C143" s="6" t="n">
-        <v>156</v>
+        <v>142</v>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>167</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="144">
@@ -5090,19 +5098,19 @@
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="C144" s="9" t="n">
-        <v>180</v>
+        <v>143</v>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>181</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -5112,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145">
@@ -5122,29 +5130,29 @@
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C145" s="4" t="n">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>206</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146">
@@ -5154,19 +5162,19 @@
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C146" s="9" t="n">
-        <v>203</v>
+        <v>145</v>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>225</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -5186,157 +5194,157 @@
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="C147" s="9" t="n">
-        <v>174</v>
+        <v>146</v>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>147</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C148" s="4" t="n">
-        <v>129</v>
+        <v>147</v>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>226</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
         <v>148</v>
       </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="n">
-        <v>150</v>
-      </c>
       <c r="C149" s="7" t="n">
-        <v>106</v>
+        <v>236</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="C150" s="6" t="n">
-        <v>199</v>
+        <v>149</v>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>115</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="C151" s="6" t="n">
-        <v>176</v>
+        <v>150</v>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>132</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="152">
@@ -5346,19 +5354,19 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C152" s="6" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -5368,61 +5376,61 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>180</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>209</v>
+        <v>153</v>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>207</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
@@ -5432,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155">
@@ -5442,29 +5450,29 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="C155" s="7" t="n">
-        <v>140</v>
+        <v>154</v>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>219</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="156">
@@ -5474,19 +5482,19 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
@@ -5496,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="157">
@@ -5506,51 +5514,51 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="C157" s="4" t="n">
-        <v>169</v>
+        <v>156</v>
+      </c>
+      <c r="C157" s="9" t="n">
+        <v>143</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -5560,29 +5568,29 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C159" s="4" t="n">
         <v>158</v>
       </c>
+      <c r="C159" s="10" t="n">
+        <v>152</v>
+      </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -5592,71 +5600,71 @@
         <v>1</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C160" s="4" t="n">
-        <v>137</v>
+        <v>159</v>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>257</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Jalen Nailor</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Juwan Johnson</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H160" s="3" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C161" s="6" t="n">
-        <v>232</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Rashod Bateman</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G161" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
     </row>
     <row r="162">
@@ -5666,17 +5674,21 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr"/>
+          <t>Jalen Nailor</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
       <c r="F162" s="3" t="n">
         <v>0</v>
       </c>
@@ -5684,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163">
@@ -5694,117 +5706,117 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="C163" s="6" t="n">
+        <v>283</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Rashod Bateman</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="C164" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Jauan Jennings</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="C165" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Jaylin Noel</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C163" s="6" t="n">
-        <v>223</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="C166" s="6" t="n">
+        <v>235</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Darnell Mooney</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>NYG</t>
         </is>
       </c>
-      <c r="F163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" s="3" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C164" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Allgeier</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" s="3" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C165" s="6" t="n">
-        <v>219</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>James Conner</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="3" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Keaton Mitchell</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
       <c r="F166" s="3" t="n">
         <v>0</v>
       </c>
@@ -5812,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167">
@@ -5822,19 +5834,19 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
@@ -5844,39 +5856,39 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="C168" s="7" t="n">
-        <v>151</v>
+        <v>167</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>276</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="169">
@@ -5886,174 +5898,174 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="C169" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="C169" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Keaton Mitchell</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Aubrey</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Cameron Dicker</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Jordan James</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="3" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="C170" s="4" t="n">
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Kaelon Black</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="3" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C171" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Chris Bell</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" s="3" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="C172" s="7" t="n">
-        <v>105</v>
+      <c r="C172" s="9" t="n">
+        <v>130</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="C173" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="C173" s="7" t="n">
-        <v>149</v>
-      </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Harrison Mevis</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="C174" s="10" t="n">
-        <v>139</v>
+        <v>185</v>
+      </c>
+      <c r="C174" s="9" t="n">
+        <v>144</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Ka'imi Fairbairn</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -6068,29 +6080,29 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
@@ -6100,55 +6112,63 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C176" s="10" t="n">
-        <v>148</v>
+        <v>187</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>172</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr"/>
+          <t>Harrison Butker</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
       <c r="F176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C177" s="10" t="n">
-        <v>146</v>
+        <v>188</v>
+      </c>
+      <c r="C177" s="9" t="n">
+        <v>128</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr"/>
+          <t>Cam Little</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
       <c r="F177" s="3" t="n">
         <v>0</v>
       </c>
@@ -6156,223 +6176,223 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Jake Bates</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="C179" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Loop</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="C180" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Cairo Santos</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Will Reichard</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="C182" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Justice Hill</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C178" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Isaac TeSlaa</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="3" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="B179" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="C179" s="4" t="n">
-        <v>217</v>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Pat Freiermuth</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" s="3" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="C180" s="10" t="n">
-        <v>160</v>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Schultz</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="3" t="n">
+      <c r="B183" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Brenton Strange</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n">
         <v>195</v>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>177</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Ryan Flournoy</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>209</v>
-      </c>
-      <c r="C182" s="10" t="n">
-        <v>145</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Aiyuk</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
+      <c r="C184" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="F182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Cooper Kupp</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" s="3" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Tank Dell</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F184" s="3" t="n">
         <v>0</v>
       </c>
@@ -6380,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="185">
@@ -6390,19 +6410,19 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>182</v>
+        <v>196</v>
+      </c>
+      <c r="C185" s="6" t="n">
+        <v>253</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6412,125 +6432,125 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>217</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C186" s="4" t="n">
-        <v>212</v>
+        <v>197</v>
+      </c>
+      <c r="C186" s="6" t="n">
+        <v>248</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="C187" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Love</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Cam Ward</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
           <t>TEN</t>
         </is>
       </c>
-      <c r="F186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" s="3" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>Gunnar Helm</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" s="3" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="C188" s="10" t="n">
-        <v>133</v>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>Oronde Gadsden</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
       <c r="F188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>196</v>
+        <v>251</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="C189" s="10" t="n">
         <v>163</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -6540,125 +6560,125 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="C190" s="10" t="n">
-        <v>138</v>
+        <v>201</v>
+      </c>
+      <c r="C190" s="6" t="n">
+        <v>259</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G190" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Deebo Samuel</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="C192" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H190" s="3" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C191" s="10" t="n">
-        <v>130</v>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>Bryce Young</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H191" s="3" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="n">
+      <c r="H192" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="C192" s="10" t="n">
-        <v>171</v>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Fernando Mendoza</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" s="3" t="n">
-        <v>218</v>
-      </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C193" s="10" t="n">
-        <v>168</v>
+        <v>205</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>208</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -6668,29 +6688,29 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>200</v>
+        <v>249</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C194" s="10" t="n">
-        <v>189</v>
+        <v>206</v>
+      </c>
+      <c r="C194" s="6" t="n">
+        <v>275</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Pat Freiermuth</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
@@ -6700,29 +6720,29 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Dalton Schultz</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F195" s="3" t="n">
@@ -6732,39 +6752,39 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>178</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C196" s="10" t="n">
-        <v>142</v>
+        <v>208</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>170</v>
+        <v>252</v>
       </c>
     </row>
     <row r="197">
@@ -6774,19 +6794,19 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -6796,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>173</v>
+        <v>232</v>
       </c>
     </row>
     <row r="198">
@@ -6806,19 +6826,19 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -6828,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>159</v>
+        <v>234</v>
       </c>
     </row>
     <row r="199">
@@ -6838,495 +6858,499 @@
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C199" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="C199" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Tank Dell</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Kaytron Allen</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C201" s="6" t="n">
+        <v>297</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Nicholas Singleton</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Demond Claiborne</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Gunnar Helm</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Oronde Gadsden</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="C205" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Chig Okonkwo</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="C206" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Sam Darnold</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="C207" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Young</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Fernando Mendoza</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Jonah Coleman</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Christian Kirk</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" s="3" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C200" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brazzell</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H200" s="3" t="n">
+      <c r="C210" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Seth McGowan</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>264</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Emmett Johnson</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="3" t="n">
         <v>163</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C201" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Tyreek Hill</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr"/>
-      <c r="F201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" s="3" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="C202" s="10" t="n">
-        <v>175</v>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" s="3" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="C212" s="6" t="n">
+        <v>260</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Zachariah Branch</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B203" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Kimani Vidal</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H203" s="3" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="B213" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="C213" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Dylan Sampson</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B204" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C204" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Adam Randall</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" s="3" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="C205" s="10" t="n">
-        <v>192</v>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>253</v>
-      </c>
-      <c r="C206" s="4" t="n">
+      <c r="B214" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H206" s="3" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C207" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>AJ Barner</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H207" s="3" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C208" s="10" t="n">
-        <v>164</v>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" s="3" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="C209" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Tory Horton</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" s="3" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="C210" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" s="3" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="C211" s="4" t="n">
-        <v>233</v>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>Keon Coleman</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" s="3" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C212" s="10" t="n">
-        <v>170</v>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C213" s="10" t="n">
-        <v>173</v>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" s="3" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="C214" s="4" t="n">
-        <v>208</v>
+      <c r="C214" s="6" t="n">
+        <v>293</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -7336,29 +7360,29 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="C215" s="10" t="n">
-        <v>172</v>
+        <v>228</v>
+      </c>
+      <c r="C215" s="6" t="n">
+        <v>285</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -7368,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="216">
@@ -7378,19 +7402,19 @@
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>271</v>
+        <v>229</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Elijah Sarratt</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -7400,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="217">
@@ -7410,19 +7434,19 @@
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C217" s="4" t="n">
-        <v>200</v>
+        <v>230</v>
+      </c>
+      <c r="C217" s="6" t="n">
+        <v>287</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Christian Kirk</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F217" s="3" t="n">
@@ -7432,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
     </row>
     <row r="218">
@@ -7442,19 +7466,19 @@
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C218" s="10" t="n">
-        <v>186</v>
+        <v>232</v>
+      </c>
+      <c r="C218" s="6" t="n">
+        <v>268</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Chris Brazzell</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -7464,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="219">
@@ -7474,78 +7498,78 @@
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="C219" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="C220" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Chris Boswell</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>Darius Slayton</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>NYG</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" s="3" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C220" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>DJ Giddens</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" s="3" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>278</v>
-      </c>
       <c r="C221" s="10" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Chase McLaughlin</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
@@ -7560,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>191</v>
+        <v>230</v>
       </c>
     </row>
     <row r="222">
@@ -7570,153 +7594,1117 @@
         </is>
       </c>
       <c r="B222" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C222" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="C223" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Kimani Vidal</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="C225" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" s="3" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Jaydon Blue</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" s="3" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="C227" s="6" t="n">
+        <v>292</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Ty Johnson</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Pat Bryant</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="C229" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Evan McPherson</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="3" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Nick Folk</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C231" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>AJ Barner</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Greg Dulcich</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="C233" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Tory Horton</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C235" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C236" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hurst</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Keon Coleman</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C238" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Geno Smith</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Rodgers</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C243" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="C244" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Dontayvion Wicks</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="C245" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Kayshon Boutte</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>DJ Giddens</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Sean Tucker</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="C222" s="10" t="n">
-        <v>190</v>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
+      <c r="C249" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
         <is>
           <t>Emanuel Wilson</t>
         </is>
       </c>
-      <c r="E222" s="3" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F222" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H222" s="3" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="8" t="inlineStr">
+      <c r="F249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Trey Smack</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="C251" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Jake Elliott</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B252" s="3" t="n">
         <v>289</v>
       </c>
-      <c r="C223" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="C252" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
         <is>
           <t>Mike Gesicki</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="F223" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" s="3" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="8" t="inlineStr">
+      <c r="F252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="B224" s="3" t="n">
+      <c r="B253" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Evan Engram</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="C224" s="10" t="n">
-        <v>194</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
+      <c r="C254" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="E224" s="3" t="inlineStr"/>
-      <c r="F224" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" s="3" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="C225" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="C255" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
         <is>
           <t>Andrei Iosivas</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
+      <c r="E255" s="3" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="F225" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H225" s="3" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="11" t="inlineStr">
+      <c r="F255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B226" s="3" t="n">
+      <c r="B256" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C226" s="4" t="n">
-        <v>205</v>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
+      <c r="C256" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E226" s="3" t="inlineStr">
+      <c r="E256" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F226" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H226" s="3" t="n">
-        <v>160</v>
+      <c r="F256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -608,7 +608,7 @@
         <v>56</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
         <v>55</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1280,7 +1280,7 @@
         <v>23</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -1312,7 +1312,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1696,7 +1696,7 @@
         <v>24</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1728,7 +1728,7 @@
         <v>29</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -2272,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56">
@@ -2368,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59">
@@ -2432,7 +2432,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62">
@@ -2496,7 +2496,7 @@
         <v>6</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
@@ -2528,7 +2528,7 @@
         <v>12</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64">
@@ -2560,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -2592,7 +2592,7 @@
         <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66">
@@ -2624,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
@@ -2656,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68">
@@ -2688,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69">
@@ -2720,7 +2720,7 @@
         <v>4</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70">
@@ -2752,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -2784,7 +2784,7 @@
         <v>4</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
@@ -2816,7 +2816,7 @@
         <v>5</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73">
@@ -2848,7 +2848,7 @@
         <v>3</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74">
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75">
@@ -2912,7 +2912,7 @@
         <v>10</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -2944,7 +2944,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77">
@@ -2976,7 +2976,7 @@
         <v>4</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -3008,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
@@ -3072,7 +3072,7 @@
         <v>13</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -3104,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82">
@@ -3136,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83">
@@ -3168,7 +3168,7 @@
         <v>4</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -3200,7 +3200,7 @@
         <v>5</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85">
@@ -3232,7 +3232,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -3264,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
@@ -3296,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88">
@@ -3360,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90">
@@ -3392,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91">
@@ -3424,7 +3424,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92">
@@ -3456,7 +3456,7 @@
         <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -3488,7 +3488,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94">
@@ -3520,7 +3520,7 @@
         <v>5</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95">
@@ -3552,7 +3552,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96">
@@ -3584,7 +3584,7 @@
         <v>7</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97">
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98">
@@ -3648,7 +3648,7 @@
         <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99">
@@ -3680,7 +3680,7 @@
         <v>7</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100">
@@ -3712,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101">
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102">
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103">
@@ -3808,7 +3808,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104">
@@ -3840,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
@@ -3872,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106">
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107">
@@ -3936,7 +3936,7 @@
         <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -3968,7 +3968,7 @@
         <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109">
@@ -4000,7 +4000,7 @@
         <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110">
@@ -4032,7 +4032,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111">
@@ -4064,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112">
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113">
@@ -4128,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114">
@@ -4160,7 +4160,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115">
@@ -4192,7 +4192,7 @@
         <v>3</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116">
@@ -4224,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117">
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118">
@@ -4288,7 +4288,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119">
@@ -4320,7 +4320,7 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
     <row r="120">
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121">
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122">
@@ -4416,7 +4416,7 @@
         <v>3</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123">
@@ -4448,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124">
@@ -4480,7 +4480,7 @@
         <v>2</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125">
@@ -4512,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126">
@@ -4544,7 +4544,7 @@
         <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127">
@@ -4576,7 +4576,7 @@
         <v>3</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="128">
@@ -4608,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129">
@@ -4640,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130">
@@ -4672,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131">
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132">
@@ -4736,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="133">
@@ -4768,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="134">
@@ -4800,7 +4800,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135">
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136">
@@ -4864,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137">
@@ -4896,7 +4896,7 @@
         <v>2</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138">
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139">
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140">
@@ -4992,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="141">
@@ -5024,7 +5024,7 @@
         <v>2</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>154</v>
+        <v>123</v>
       </c>
     </row>
     <row r="142">
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="143">
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144">
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="145">
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146">
@@ -5184,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="147">
@@ -5216,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="148">
@@ -5248,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149">
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="150">
@@ -5312,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="151">
@@ -5344,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="152">
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153">
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154">
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="155">
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="156">
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157">
@@ -5536,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="158">
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="159">
@@ -5600,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
     </row>
     <row r="160">
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="161">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
     </row>
     <row r="162">
@@ -5696,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="163">
@@ -5728,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>196</v>
+        <v>240</v>
       </c>
     </row>
     <row r="164">
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165">
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>195</v>
+        <v>241</v>
       </c>
     </row>
     <row r="166">
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="167">
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>221</v>
+        <v>168</v>
       </c>
     </row>
     <row r="168">
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>200</v>
+        <v>236</v>
       </c>
     </row>
     <row r="169">
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>208</v>
+        <v>163</v>
       </c>
     </row>
     <row r="170">
@@ -5952,7 +5952,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171">
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>214</v>
+        <v>161</v>
       </c>
     </row>
     <row r="172">
@@ -6016,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>215</v>
+        <v>162</v>
       </c>
     </row>
     <row r="173">
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>233</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174">
@@ -6080,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>222</v>
+        <v>186</v>
       </c>
     </row>
     <row r="175">
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>227</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176">
@@ -6144,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>219</v>
+        <v>188</v>
       </c>
     </row>
     <row r="177">
@@ -6176,7 +6176,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>211</v>
+        <v>166</v>
       </c>
     </row>
     <row r="178">
@@ -6208,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="179">
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>229</v>
+        <v>171</v>
       </c>
     </row>
     <row r="180">
@@ -6272,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>238</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181">
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182">
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183">
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>210</v>
+        <v>178</v>
       </c>
     </row>
     <row r="184">
@@ -6400,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="185">
@@ -6432,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>176</v>
+        <v>218</v>
       </c>
     </row>
     <row r="186">
@@ -6464,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>177</v>
+        <v>219</v>
       </c>
     </row>
     <row r="187">
@@ -6496,7 +6496,7 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>246</v>
+        <v>164</v>
       </c>
     </row>
     <row r="188">
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>251</v>
+        <v>198</v>
       </c>
     </row>
     <row r="189">
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>225</v>
+        <v>167</v>
       </c>
     </row>
     <row r="190">
@@ -6592,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191">
@@ -6624,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="192">
@@ -6656,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>220</v>
+        <v>185</v>
       </c>
     </row>
     <row r="193">
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>249</v>
+        <v>196</v>
       </c>
     </row>
     <row r="194">
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="195">
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>244</v>
+        <v>192</v>
       </c>
     </row>
     <row r="196">
@@ -6784,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>252</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197">
@@ -6816,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198">
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199">
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="200">
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>235</v>
+        <v>204</v>
       </c>
     </row>
     <row r="201">
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>183</v>
+        <v>253</v>
       </c>
     </row>
     <row r="202">
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>199</v>
+        <v>237</v>
       </c>
     </row>
     <row r="203">
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="204">
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>231</v>
+        <v>181</v>
       </c>
     </row>
     <row r="205">
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>223</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206">
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="207">
@@ -7136,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>216</v>
+        <v>175</v>
       </c>
     </row>
     <row r="208">
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>250</v>
+        <v>199</v>
       </c>
     </row>
     <row r="209">
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>236</v>
+        <v>202</v>
       </c>
     </row>
     <row r="210">
@@ -7264,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>163</v>
+        <v>226</v>
       </c>
     </row>
     <row r="212">
@@ -7296,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>168</v>
+        <v>224</v>
       </c>
     </row>
     <row r="213">
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="214">
@@ -7360,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>186</v>
+        <v>250</v>
       </c>
     </row>
     <row r="215">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="216">
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
     </row>
     <row r="217">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>192</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218">
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>180</v>
+        <v>229</v>
       </c>
     </row>
     <row r="219">
@@ -7520,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220">
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
     </row>
     <row r="221">
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>230</v>
+        <v>176</v>
       </c>
     </row>
     <row r="222">
@@ -7616,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>190</v>
+        <v>246</v>
       </c>
     </row>
     <row r="223">
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="224">
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>243</v>
+        <v>206</v>
       </c>
     </row>
     <row r="225">
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="226">
@@ -7744,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>174</v>
+        <v>220</v>
       </c>
     </row>
     <row r="227">
@@ -7776,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>187</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228">
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>167</v>
+        <v>212</v>
       </c>
     </row>
     <row r="229">
@@ -7840,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>228</v>
+        <v>172</v>
       </c>
     </row>
     <row r="230">
@@ -7872,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>240</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231">
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="232">
@@ -7936,7 +7936,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>245</v>
+        <v>193</v>
       </c>
     </row>
     <row r="233">
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>239</v>
+        <v>200</v>
       </c>
     </row>
     <row r="234">
@@ -8000,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>189</v>
+        <v>247</v>
       </c>
     </row>
     <row r="235">
@@ -8032,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>193</v>
+        <v>243</v>
       </c>
     </row>
     <row r="236">
@@ -8064,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>182</v>
+        <v>254</v>
       </c>
     </row>
     <row r="237">
@@ -8096,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>188</v>
+        <v>248</v>
       </c>
     </row>
     <row r="238">
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>185</v>
+        <v>251</v>
       </c>
     </row>
     <row r="239">
@@ -8160,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>248</v>
+        <v>195</v>
       </c>
     </row>
     <row r="240">
@@ -8192,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>241</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241">
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>169</v>
+        <v>217</v>
       </c>
     </row>
     <row r="242">
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>171</v>
+        <v>216</v>
       </c>
     </row>
     <row r="243">
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>181</v>
+        <v>230</v>
       </c>
     </row>
     <row r="244">
@@ -8320,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>170</v>
+        <v>222</v>
       </c>
     </row>
     <row r="245">
@@ -8352,7 +8352,7 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
     </row>
     <row r="246">
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>197</v>
+        <v>239</v>
       </c>
     </row>
     <row r="247">
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
     </row>
     <row r="248">
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="249">
@@ -8480,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="250">
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>247</v>
+        <v>194</v>
       </c>
     </row>
     <row r="251">
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>209</v>
+        <v>177</v>
       </c>
     </row>
     <row r="252">
@@ -8576,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>175</v>
+        <v>228</v>
       </c>
     </row>
     <row r="253">
@@ -8608,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>162</v>
+        <v>227</v>
       </c>
     </row>
     <row r="254">
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>198</v>
+        <v>238</v>
       </c>
     </row>
     <row r="255">
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>184</v>
+        <v>252</v>
       </c>
     </row>
     <row r="256">
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>172</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -113,10 +113,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,8 +588,8 @@
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
+      <c r="C3" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
         <v>56</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -621,7 +621,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -637,14 +637,14 @@
         <v>56</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -676,7 +676,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -772,7 +772,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -804,7 +804,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -860,7 +860,7 @@
       <c r="F11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
         <v>45</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -868,7 +868,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -908,8 +908,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="6" t="n">
-        <v>23</v>
+      <c r="C13" s="7" t="n">
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -925,14 +925,14 @@
         <v>46</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -940,7 +940,7 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -973,7 +973,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>43</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14</v>
@@ -1037,7 +1037,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
@@ -1068,8 +1068,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="9" t="n">
-        <v>15</v>
+      <c r="C18" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>38</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1116,7 +1116,7 @@
       <c r="F19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="5" t="n">
         <v>33</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -1197,7 +1197,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1229,7 +1229,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
@@ -1261,7 +1261,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1276,8 +1276,8 @@
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>23</v>
+      <c r="G24" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
@@ -1316,7 +1316,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1348,7 +1348,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1372,15 +1372,15 @@
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="5" t="n">
         <v>20</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1408,11 +1408,11 @@
         <v>34</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1420,8 +1420,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>30</v>
+      <c r="C29" s="5" t="n">
+        <v>37</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1436,15 +1436,15 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>27</v>
+      <c r="G29" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1453,7 +1453,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1516,8 +1516,8 @@
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="9" t="n">
-        <v>27</v>
+      <c r="C32" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1533,14 +1533,14 @@
         <v>26</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1548,8 +1548,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="6" t="n">
-        <v>37</v>
+      <c r="C33" s="5" t="n">
+        <v>39</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1565,14 +1565,14 @@
         <v>25</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1580,8 +1580,8 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="6" t="n">
-        <v>39</v>
+      <c r="C34" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1597,14 +1597,14 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1612,8 +1612,8 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="10" t="n">
-        <v>25</v>
+      <c r="C35" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1629,14 +1629,14 @@
         <v>23</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>37</v>
@@ -1676,8 +1676,8 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>33</v>
+      <c r="C37" s="10" t="n">
+        <v>28</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       <c r="F37" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>24</v>
+      <c r="G37" s="10" t="n">
+        <v>29</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1709,7 +1709,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         <v>22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -1741,7 +1741,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>39</v>
@@ -1805,7 +1805,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1820,8 +1820,8 @@
       <c r="F41" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="6" t="n">
-        <v>11</v>
+      <c r="G41" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1836,8 +1836,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>60</v>
+      <c r="C42" s="7" t="n">
+        <v>68</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1852,15 +1852,15 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="6" t="n">
-        <v>9</v>
+      <c r="G42" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1868,8 +1868,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>43</v>
+      <c r="C43" s="9" t="n">
+        <v>24</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1884,15 +1884,15 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>18</v>
+      <c r="G43" s="9" t="n">
+        <v>32</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1900,8 +1900,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="6" t="n">
-        <v>50</v>
+      <c r="C44" s="5" t="n">
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1916,15 +1916,15 @@
       <c r="F44" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G44" s="6" t="n">
-        <v>13</v>
+      <c r="G44" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1933,7 +1933,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1949,14 +1949,14 @@
         <v>17</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1965,7 +1965,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1981,14 +1981,14 @@
         <v>17</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1997,7 +1997,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2013,14 +2013,14 @@
         <v>15</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2029,7 +2029,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2045,14 +2045,14 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2061,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2093,7 +2093,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2108,8 +2108,8 @@
       <c r="F50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>19</v>
+      <c r="G50" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>49</v>
@@ -2125,7 +2125,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2140,15 +2140,15 @@
       <c r="F51" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G51" s="6" t="n">
-        <v>6</v>
+      <c r="G51" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2172,7 +2172,7 @@
       <c r="F52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H52" s="3" t="n">
@@ -2180,7 +2180,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2188,8 +2188,8 @@
       <c r="B53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C53" s="6" t="n">
-        <v>62</v>
+      <c r="C53" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2205,14 +2205,14 @@
         <v>11</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2221,7 +2221,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
         <v>11</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2253,7 +2253,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>56</v>
@@ -2285,7 +2285,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>10</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
@@ -2336,7 +2336,7 @@
         <v>17</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
@@ -2349,7 +2349,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59">
@@ -2381,7 +2381,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -2413,7 +2413,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2429,10 +2429,10 @@
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -2445,7 +2445,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -2477,7 +2477,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
@@ -2509,7 +2509,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>63</v>
@@ -2540,8 +2540,8 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="10" t="n">
-        <v>57</v>
+      <c r="C64" s="9" t="n">
+        <v>55</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
@@ -2592,11 +2592,11 @@
         <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2604,8 +2604,8 @@
       <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="6" t="n">
-        <v>77</v>
+      <c r="C66" s="5" t="n">
+        <v>74</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2637,7 +2637,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2652,15 +2652,15 @@
       <c r="F67" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2669,7 +2669,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G68" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="3" t="n">
@@ -2692,7 +2692,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2700,8 +2700,8 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="6" t="n">
-        <v>80</v>
+      <c r="C69" s="7" t="n">
+        <v>83</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2720,11 +2720,11 @@
         <v>4</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2733,7 +2733,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2749,14 +2749,14 @@
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2764,8 +2764,8 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="6" t="n">
-        <v>79</v>
+      <c r="C71" s="5" t="n">
+        <v>76</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         <v>6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72">
@@ -2797,7 +2797,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
@@ -2829,7 +2829,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -2861,7 +2861,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75">
@@ -2893,7 +2893,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76">
@@ -2925,7 +2925,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2956,8 +2956,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="6" t="n">
-        <v>84</v>
+      <c r="C77" s="4" t="n">
+        <v>66</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -2973,14 +2973,14 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3012,7 +3012,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3021,7 +3021,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
         <v>2</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3053,7 +3053,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3068,15 +3068,15 @@
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G80" s="9" t="n">
-        <v>13</v>
+      <c r="G80" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3085,7 +3085,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3101,14 +3101,14 @@
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3117,7 +3117,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -3149,7 +3149,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         <v>4</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84">
@@ -3181,7 +3181,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         <v>4</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85">
@@ -3212,8 +3212,8 @@
       <c r="B85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="7" t="n">
-        <v>97</v>
+      <c r="C85" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86">
@@ -3244,8 +3244,8 @@
       <c r="B86" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C86" s="4" t="n">
-        <v>96</v>
+      <c r="C86" s="7" t="n">
+        <v>99</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3276,8 +3276,8 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="7" t="n">
-        <v>102</v>
+      <c r="C87" s="4" t="n">
+        <v>97</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88">
@@ -3328,11 +3328,11 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3341,7 +3341,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3360,11 +3360,11 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3373,7 +3373,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
         <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3405,7 +3405,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3424,29 +3424,29 @@
         <v>2</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Ricky Pearsall</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -3456,39 +3456,39 @@
         <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>83</v>
+        <v>93</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>77</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
@@ -3498,61 +3498,61 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="C94" s="10" t="n">
-        <v>75</v>
+        <v>94</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>104</v>
+        <v>95</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>64</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96">
@@ -3562,29 +3562,29 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97">
@@ -3594,29 +3594,29 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="C97" s="9" t="n">
-        <v>65</v>
+        <v>97</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>107</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98">
@@ -3626,29 +3626,29 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>94</v>
+        <v>98</v>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99">
@@ -3658,29 +3658,29 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="C99" s="9" t="n">
-        <v>66</v>
+        <v>99</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>148</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -3712,29 +3712,29 @@
         <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -3754,19 +3754,19 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103">
@@ -3786,29 +3786,29 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>121</v>
+        <v>104</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>149</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -3840,39 +3840,39 @@
         <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="C105" s="4" t="n">
-        <v>140</v>
+        <v>105</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>92</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="106">
@@ -3882,19 +3882,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107">
@@ -3914,14 +3914,14 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -3933,10 +3933,10 @@
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108">
@@ -3946,61 +3946,61 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="C108" s="10" t="n">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="C109" s="9" t="n">
-        <v>93</v>
+        <v>109</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>122</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="110">
@@ -4010,29 +4010,29 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="C110" s="4" t="n">
-        <v>120</v>
+        <v>110</v>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>79</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
@@ -4042,147 +4042,147 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C111" s="9" t="n">
-        <v>81</v>
+        <v>111</v>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>213</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>213</v>
+        <v>145</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="C113" s="7" t="n">
-        <v>150</v>
+        <v>113</v>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>104</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="3" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
         <v>114</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>100</v>
+      <c r="C114" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>90</v>
+        <v>115</v>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>93</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -4192,39 +4192,39 @@
         <v>3</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>123</v>
+        <v>116</v>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>212</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="117">
@@ -4234,29 +4234,29 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C117" s="7" t="n">
-        <v>216</v>
+        <v>117</v>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>127</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118">
@@ -4266,19 +4266,19 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="C118" s="10" t="n">
+        <v>112</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -4288,7 +4288,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119">
@@ -4298,61 +4298,61 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C119" s="9" t="n">
-        <v>106</v>
+        <v>119</v>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>186</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="C120" s="7" t="n">
-        <v>195</v>
+        <v>120</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>123</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121">
@@ -4362,29 +4362,29 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>124</v>
+        <v>121</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>90</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>96</v>
+        <v>145</v>
       </c>
     </row>
     <row r="122">
@@ -4394,29 +4394,29 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="C122" s="9" t="n">
-        <v>87</v>
+        <v>122</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>152</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123">
@@ -4426,51 +4426,51 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>151</v>
+        <v>123</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>106</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="C124" s="9" t="n">
-        <v>111</v>
+        <v>124</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -4480,253 +4480,253 @@
         <v>2</v>
       </c>
       <c r="H124" s="3" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>124</v>
-      </c>
       <c r="C125" s="4" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125" s="3" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>101</v>
+      <c r="C126" s="9" t="n">
+        <v>86</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="C127" s="10" t="n">
-        <v>89</v>
+        <v>127</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>135</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C128" s="6" t="n">
-        <v>136</v>
+        <v>128</v>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C129" s="9" t="n">
-        <v>85</v>
+        <v>129</v>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>132</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>131</v>
+        <v>130</v>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>189</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C131" s="7" t="n">
-        <v>200</v>
+        <v>131</v>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>111</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -4736,39 +4736,39 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134">
@@ -4778,29 +4778,29 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>105</v>
+        <v>134</v>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>165</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="135">
@@ -4810,19 +4810,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="136">
@@ -4842,61 +4842,61 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="C136" s="7" t="n">
-        <v>177</v>
+        <v>136</v>
+      </c>
+      <c r="C136" s="10" t="n">
+        <v>115</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="C137" s="10" t="n">
-        <v>114</v>
+        <v>137</v>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>238</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="138">
@@ -4906,19 +4906,19 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="C138" s="7" t="n">
-        <v>244</v>
+        <v>138</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>181</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="139">
@@ -4938,19 +4938,19 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
     </row>
     <row r="140">
@@ -4970,29 +4970,29 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>169</v>
+        <v>140</v>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>108</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141">
@@ -5002,29 +5002,29 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C141" s="9" t="n">
-        <v>110</v>
+        <v>141</v>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>218</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -5056,61 +5056,61 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C143" s="5" t="n">
         <v>155</v>
       </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>167</v>
-      </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C144" s="7" t="n">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -5120,29 +5120,29 @@
         <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -5152,93 +5152,93 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="C146" s="7" t="n">
-        <v>225</v>
+        <v>146</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>157</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C147" s="4" t="n">
         <v>147</v>
       </c>
+      <c r="C147" s="7" t="n">
+        <v>226</v>
+      </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -5248,39 +5248,39 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="C149" s="7" t="n">
-        <v>236</v>
+        <v>149</v>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="150">
@@ -5290,78 +5290,78 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C150" s="9" t="n">
-        <v>115</v>
+        <v>150</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>131</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="C151" s="4" t="n">
-        <v>132</v>
+        <v>151</v>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>188</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="C152" s="6" t="n">
-        <v>179</v>
+        <v>152</v>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>190</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -5376,29 +5376,29 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="C153" s="6" t="n">
-        <v>180</v>
+        <v>153</v>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>208</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
@@ -5408,24 +5408,24 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="C154" s="6" t="n">
-        <v>207</v>
+        <v>154</v>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>217</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155">
@@ -5450,19 +5450,19 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -5482,29 +5482,29 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157">
@@ -5514,29 +5514,29 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="C157" s="9" t="n">
-        <v>143</v>
+        <v>157</v>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>169</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="158">
@@ -5546,19 +5546,19 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -5568,39 +5568,39 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="C159" s="10" t="n">
-        <v>152</v>
+        <v>159</v>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>232</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="160">
@@ -5610,19 +5610,19 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C160" s="6" t="n">
-        <v>257</v>
+        <v>160</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>173</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Juwan Johnson</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
@@ -5632,93 +5632,93 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G161" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H161" s="3" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="inlineStr">
+      <c r="A162" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C162" s="4" t="n">
-        <v>148</v>
+        <v>162</v>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>210</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Jalen Nailor</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="inlineStr">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C163" s="6" t="n">
-        <v>283</v>
+        <v>163</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>192</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -5728,29 +5728,29 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
+      <c r="A164" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="C164" s="6" t="n">
-        <v>201</v>
+        <v>164</v>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>268</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
@@ -5760,29 +5760,29 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="inlineStr">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="C165" s="6" t="n">
-        <v>284</v>
+        <v>165</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>259</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
@@ -5792,29 +5792,29 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>241</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="C166" s="6" t="n">
-        <v>235</v>
+        <v>166</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>168</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="167">
@@ -5834,14 +5834,14 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>242</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168">
@@ -5866,61 +5866,61 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C168" s="6" t="n">
-        <v>276</v>
+        <v>168</v>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>124</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C169" s="9" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>163</v>
+        <v>235</v>
       </c>
     </row>
     <row r="170">
@@ -5930,29 +5930,29 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aubrey</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>165</v>
+        <v>217</v>
       </c>
     </row>
     <row r="171">
@@ -5962,19 +5962,19 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="C171" s="9" t="n">
-        <v>129</v>
+        <v>183</v>
+      </c>
+      <c r="C171" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
     </row>
     <row r="172">
@@ -5994,29 +5994,29 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="C172" s="9" t="n">
-        <v>130</v>
+        <v>184</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>163</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>Harrison Mevis</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173">
@@ -6026,29 +6026,29 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v>199</v>
+        <v>185</v>
+      </c>
+      <c r="C173" s="9" t="n">
+        <v>139</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Harrison Mevis</t>
+          <t>Ka'imi Fairbairn</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="174">
@@ -6058,29 +6058,29 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="C174" s="9" t="n">
-        <v>144</v>
+        <v>186</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>162</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Ka'imi Fairbairn</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="175">
@@ -6090,19 +6090,19 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Eddy Pineiro</t>
+          <t>Harrison Butker</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>173</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176">
@@ -6122,29 +6122,29 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>172</v>
+        <v>188</v>
+      </c>
+      <c r="C176" s="9" t="n">
+        <v>137</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Harrison Butker</t>
+          <t>Cam Little</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="177">
@@ -6154,19 +6154,19 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C177" s="9" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Cam Little</t>
+          <t>Jake Bates</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
@@ -6176,7 +6176,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>166</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178">
@@ -6186,19 +6186,19 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="C178" s="4" t="n">
-        <v>162</v>
+        <v>190</v>
+      </c>
+      <c r="C178" s="10" t="n">
+        <v>161</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Tyler Loop</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
@@ -6208,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>174</v>
+        <v>226</v>
       </c>
     </row>
     <row r="179">
@@ -6218,29 +6218,29 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C179" s="10" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Tyler Loop</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>171</v>
+        <v>227</v>
       </c>
     </row>
     <row r="180">
@@ -6250,83 +6250,83 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="C180" s="10" t="n">
-        <v>157</v>
+        <v>192</v>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>221</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="C181" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Justice Hill</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Will Reichard</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>189</v>
-      </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="C182" s="6" t="n">
-        <v>237</v>
+        <v>194</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>180</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6340,25 +6340,25 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>186</v>
+        <v>195</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>249</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Jordan James</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F183" s="3" t="n">
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="184">
@@ -6378,14 +6378,14 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="C184" s="6" t="n">
-        <v>272</v>
+        <v>196</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>205</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -6400,29 +6400,29 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="C185" s="6" t="n">
-        <v>253</v>
+        <v>197</v>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>258</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6432,39 +6432,39 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>218</v>
+        <v>169</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C186" s="6" t="n">
-        <v>248</v>
+        <v>198</v>
+      </c>
+      <c r="C186" s="9" t="n">
+        <v>116</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="187">
@@ -6474,29 +6474,29 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="C187" s="9" t="n">
-        <v>113</v>
+        <v>199</v>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>199</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F187" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>164</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188">
@@ -6506,19 +6506,19 @@
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="C188" s="10" t="n">
+        <v>164</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -6528,29 +6528,29 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="C189" s="10" t="n">
-        <v>163</v>
+        <v>201</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>244</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -6564,131 +6564,131 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="C190" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Deebo Samuel</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="C191" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Isaac TeSlaa</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Pat Freiermuth</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="3" t="n">
         <v>201</v>
-      </c>
-      <c r="C190" s="6" t="n">
-        <v>259</v>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>Jack Bech</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" s="3" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C191" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>Deebo Samuel</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" s="3" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C192" s="10" t="n">
-        <v>135</v>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H192" s="3" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>205</v>
-      </c>
-      <c r="C193" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>Isaac TeSlaa</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" s="3" t="n">
-        <v>196</v>
       </c>
     </row>
     <row r="194">
@@ -6698,19 +6698,19 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="C194" s="6" t="n">
-        <v>275</v>
+        <v>207</v>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>215</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Dalton Schultz</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
@@ -6720,29 +6720,29 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Dalton Schultz</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F195" s="3" t="n">
@@ -6752,29 +6752,29 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>192</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
+      <c r="A196" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -6784,29 +6784,29 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C197" s="4" t="n">
         <v>234</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -6816,29 +6816,29 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="inlineStr">
+      <c r="A198" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v>233</v>
+        <v>211</v>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>274</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -6848,29 +6848,29 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C199" s="6" t="n">
-        <v>288</v>
+        <v>212</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>227</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="200">
@@ -6890,19 +6890,19 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="C200" s="4" t="n">
-        <v>229</v>
+        <v>213</v>
+      </c>
+      <c r="C200" s="5" t="n">
+        <v>272</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201">
@@ -6922,53 +6922,53 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C201" s="6" t="n">
-        <v>297</v>
+        <v>214</v>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>279</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="C202" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Gunnar Helm</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
           <t>TEN</t>
         </is>
       </c>
-      <c r="F201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" s="3" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>214</v>
-      </c>
-      <c r="C202" s="6" t="n">
-        <v>278</v>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Demond Claiborne</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F202" s="3" t="n">
         <v>0</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="203">
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Gunnar Helm</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="204">
@@ -7018,19 +7018,19 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="C204" s="4" t="n">
-        <v>196</v>
+        <v>217</v>
+      </c>
+      <c r="C204" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
@@ -7040,29 +7040,29 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>181</v>
+        <v>215</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C205" s="10" t="n">
         <v>166</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F205" s="3" t="n">
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206">
@@ -7082,19 +7082,19 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C206" s="10" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>170</v>
+        <v>214</v>
       </c>
     </row>
     <row r="207">
@@ -7114,19 +7114,19 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C207" s="10" t="n">
-        <v>176</v>
+        <v>220</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -7136,29 +7136,29 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>175</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209">
@@ -7178,19 +7178,19 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C209" s="4" t="n">
-        <v>228</v>
+        <v>223</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>262</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -7200,29 +7200,29 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C210" s="6" t="n">
-        <v>299</v>
+        <v>224</v>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>256</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Seth McGowan</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
@@ -7232,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>255</v>
+        <v>176</v>
       </c>
     </row>
     <row r="211">
@@ -7242,19 +7242,19 @@
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C211" s="6" t="n">
-        <v>264</v>
+        <v>225</v>
+      </c>
+      <c r="C211" s="10" t="n">
+        <v>182</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7264,319 +7264,319 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
         <v>226</v>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>224</v>
-      </c>
-      <c r="C212" s="6" t="n">
+      <c r="C212" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Samaje Perine</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="C214" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Malik Washington</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Christian Kirk</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="C216" s="4" t="n">
         <v>260</v>
       </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Zachariah Branch</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brazzell</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="C217" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="C218" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Chris Boswell</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C219" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Chase McLaughlin</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B213" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C213" s="10" t="n">
+      <c r="B220" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>LeQuint Allen</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>Dylan Sampson</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" s="3" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B214" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="C214" s="6" t="n">
-        <v>293</v>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>Samaje Perine</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H214" s="3" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C215" s="6" t="n">
-        <v>285</v>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Tolbert</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
+      <c r="B221" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C221" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="F215" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" s="3" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="C216" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>Malik Washington</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H216" s="3" t="n">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C217" s="6" t="n">
-        <v>287</v>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Christian Kirk</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H217" s="3" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C218" s="6" t="n">
-        <v>268</v>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brazzell</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H218" s="3" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="C219" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" s="3" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="C220" s="10" t="n">
-        <v>174</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>Chris Boswell</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" s="3" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C221" s="10" t="n">
-        <v>192</v>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>Chase McLaughlin</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F221" s="3" t="n">
         <v>0</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="222">
@@ -7594,14 +7594,14 @@
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C222" s="6" t="n">
-        <v>289</v>
+        <v>241</v>
+      </c>
+      <c r="C222" s="4" t="n">
+        <v>275</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -7616,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>246</v>
+        <v>192</v>
       </c>
     </row>
     <row r="223">
@@ -7629,7 +7629,7 @@
         <v>242</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>232</v>
+        <v>202</v>
       </c>
     </row>
     <row r="224">
@@ -7661,7 +7661,7 @@
         <v>244</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>206</v>
+        <v>247</v>
       </c>
     </row>
     <row r="225">
@@ -7693,7 +7693,7 @@
         <v>245</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="226">
@@ -7725,7 +7725,7 @@
         <v>246</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
     </row>
     <row r="227">
@@ -7754,19 +7754,19 @@
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="C227" s="6" t="n">
-        <v>292</v>
+        <v>251</v>
+      </c>
+      <c r="C227" s="4" t="n">
+        <v>283</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Ty Johnson</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -7776,11 +7776,11 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>249</v>
+        <v>185</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="inlineStr">
+      <c r="A228" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7789,7 +7789,7 @@
         <v>253</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>212</v>
+        <v>166</v>
       </c>
     </row>
     <row r="229">
@@ -7821,7 +7821,7 @@
         <v>256</v>
       </c>
       <c r="C229" s="10" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -7840,29 +7840,29 @@
         <v>1</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>172</v>
+        <v>222</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="C230" s="4" t="n">
-        <v>223</v>
+        <v>258</v>
+      </c>
+      <c r="C230" s="10" t="n">
+        <v>179</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Nick Folk</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -7872,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="231">
@@ -7882,19 +7882,19 @@
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C231" s="10" t="n">
-        <v>184</v>
+        <v>259</v>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v>214</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>179</v>
+        <v>239</v>
       </c>
     </row>
     <row r="232">
@@ -7914,19 +7914,19 @@
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -7936,159 +7936,159 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C235" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hurst</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="F233" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H233" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="C234" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>Tory Horton</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="C236" s="4" t="n">
+        <v>278</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Keon Coleman</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H234" s="3" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="C235" s="4" t="n">
-        <v>286</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C236" s="4" t="n">
-        <v>298</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>Ted Hurst</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H236" s="3" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="C237" s="4" t="n">
-        <v>291</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>Keon Coleman</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
       <c r="F237" s="3" t="n">
         <v>0</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>248</v>
+        <v>186</v>
       </c>
     </row>
     <row r="238">
@@ -8106,19 +8106,19 @@
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>251</v>
+        <v>187</v>
       </c>
     </row>
     <row r="239">
@@ -8141,7 +8141,7 @@
         <v>267</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>195</v>
+        <v>249</v>
       </c>
     </row>
     <row r="240">
@@ -8173,7 +8173,7 @@
         <v>268</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="241">
@@ -8205,7 +8205,7 @@
         <v>269</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>217</v>
+        <v>170</v>
       </c>
     </row>
     <row r="242">
@@ -8237,7 +8237,7 @@
         <v>270</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
@@ -8256,11 +8256,11 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>216</v>
+        <v>172</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8269,7 +8269,7 @@
         <v>271</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
@@ -8288,11 +8288,11 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8301,7 +8301,7 @@
         <v>272</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -8320,11 +8320,11 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="inlineStr">
+      <c r="A245" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8333,7 +8333,7 @@
         <v>273</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
@@ -8352,11 +8352,11 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="inlineStr">
+      <c r="A246" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8365,7 +8365,7 @@
         <v>275</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="247">
@@ -8397,7 +8397,7 @@
         <v>276</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="248">
@@ -8429,7 +8429,7 @@
         <v>278</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>214</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249">
@@ -8461,7 +8461,7 @@
         <v>280</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>234</v>
+        <v>196</v>
       </c>
     </row>
     <row r="250">
@@ -8490,19 +8490,19 @@
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Trey Smack</t>
+          <t>Jake Elliott</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F250" s="3" t="n">
@@ -8512,29 +8512,29 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C251" s="10" t="n">
-        <v>188</v>
+        <v>289</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>255</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F251" s="3" t="n">
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="252">
@@ -8554,19 +8554,19 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Mike Gesicki</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F252" s="3" t="n">
@@ -8576,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>228</v>
+        <v>162</v>
       </c>
     </row>
     <row r="253">
@@ -8586,51 +8586,51 @@
         </is>
       </c>
       <c r="B253" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>David Njoku</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="C254" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="C253" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F253" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="3" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>280</v>
-      </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Andrei Iosivas</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -8640,29 +8640,29 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>238</v>
+        <v>182</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -8672,39 +8672,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" s="3" t="n">
-        <v>221</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -908,56 +908,56 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <v>30</v>
+      <c r="C13" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>James Cook</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>27</v>
+      <c r="G13" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>19</v>
+      <c r="C14" s="7" t="n">
+        <v>30</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>36</v>
+      <c r="G14" s="7" t="n">
+        <v>27</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
@@ -972,24 +972,24 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>43</v>
+      <c r="C15" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>18</v>
+      <c r="G15" s="4" t="n">
+        <v>36</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14</v>
@@ -1005,87 +1005,87 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>James Cook</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>43</v>
+      <c r="G16" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>40</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>17</v>
+      <c r="C18" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>38</v>
+      <c r="G18" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1196,24 +1196,24 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>34</v>
+      <c r="C22" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>23</v>
+      <c r="G22" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1229,23 +1229,23 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kenneth Walker</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
@@ -1261,23 +1261,23 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>31</v>
+      <c r="G24" s="5" t="n">
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
@@ -1485,23 +1485,23 @@
         <v>30</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Kenneth Walker</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>46</v>
+      <c r="G31" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1548,24 +1548,24 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>39</v>
+      <c r="C33" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>21</v>
+      <c r="G33" s="10" t="n">
+        <v>32</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
@@ -1580,24 +1580,24 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="4" t="n">
-        <v>35</v>
+      <c r="C34" s="5" t="n">
+        <v>39</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1613,23 +1613,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>30</v>
+      <c r="G35" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
@@ -1644,27 +1644,27 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="4" t="n">
-        <v>36</v>
+      <c r="C36" s="10" t="n">
+        <v>26</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>22</v>
+      <c r="G36" s="10" t="n">
+        <v>30</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -1728,7 +1728,7 @@
         <v>24</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -1868,27 +1868,27 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="9" t="n">
-        <v>24</v>
+      <c r="C43" s="4" t="n">
+        <v>36</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>32</v>
+      <c r="G43" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -2016,7 +2016,7 @@
         <v>28</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -2048,7 +2048,7 @@
         <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
@@ -2208,7 +2208,7 @@
         <v>13</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -2240,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -2336,7 +2336,7 @@
         <v>17</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58">
@@ -2368,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -2400,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61">
@@ -2476,27 +2476,27 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>67</v>
+      <c r="C62" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63">
@@ -2509,26 +2509,26 @@
         <v>62</v>
       </c>
       <c r="C63" s="9" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -2540,24 +2540,24 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="9" t="n">
-        <v>55</v>
+      <c r="C64" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>61</v>
@@ -2604,27 +2604,27 @@
       <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="5" t="n">
-        <v>74</v>
+      <c r="C66" s="7" t="n">
+        <v>102</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Marvin Harrison</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="4" t="n">
-        <v>5</v>
+      <c r="G66" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
@@ -2637,16 +2637,16 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Michael Pittman</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -2656,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
@@ -2668,27 +2668,27 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="7" t="n">
-        <v>110</v>
+      <c r="C68" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Michael Pittman</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>2</v>
+      <c r="G68" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69">
@@ -2700,27 +2700,27 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="7" t="n">
-        <v>83</v>
+      <c r="C69" s="5" t="n">
+        <v>74</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
@@ -2732,27 +2732,27 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="4" t="n">
-        <v>65</v>
+      <c r="C70" s="7" t="n">
+        <v>83</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
@@ -2784,7 +2784,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72">
@@ -2816,7 +2816,7 @@
         <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73">
@@ -2848,7 +2848,7 @@
         <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75">
@@ -2912,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
@@ -2956,24 +2956,24 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>66</v>
+      <c r="C77" s="9" t="n">
+        <v>52</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>74</v>
@@ -2988,27 +2988,27 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="9" t="n">
-        <v>47</v>
+      <c r="C78" s="4" t="n">
+        <v>66</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="9" t="n">
-        <v>15</v>
+      <c r="G78" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
@@ -3020,12 +3020,12 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="7" t="n">
-        <v>101</v>
+      <c r="C79" s="9" t="n">
+        <v>47</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3036,8 +3036,8 @@
       <c r="F79" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G79" s="4" t="n">
-        <v>2</v>
+      <c r="G79" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>78</v>
@@ -3052,27 +3052,27 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="9" t="n">
-        <v>52</v>
+      <c r="C80" s="7" t="n">
+        <v>101</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81">
@@ -3084,27 +3084,27 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="n">
-        <v>75</v>
+      <c r="C81" s="7" t="n">
+        <v>103</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82">
@@ -3116,12 +3116,12 @@
       <c r="B82" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C82" s="7" t="n">
-        <v>146</v>
+      <c r="C82" s="4" t="n">
+        <v>75</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3133,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
@@ -3229,10 +3229,10 @@
         <v>4</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86">
@@ -3264,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
@@ -3296,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88">
@@ -3341,16 +3341,16 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -3360,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90">
@@ -3372,27 +3372,27 @@
       <c r="B90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="4" t="n">
-        <v>84</v>
+      <c r="C90" s="7" t="n">
+        <v>136</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91">
@@ -3404,27 +3404,27 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="7" t="n">
-        <v>103</v>
+      <c r="C91" s="4" t="n">
+        <v>84</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92">
@@ -3434,61 +3434,61 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="C93" s="10" t="n">
-        <v>77</v>
+        <v>92</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>87</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -3498,61 +3498,61 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>117</v>
+        <v>93</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>77</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="C95" s="9" t="n">
-        <v>64</v>
+        <v>94</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96">
@@ -3562,29 +3562,29 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97">
@@ -3594,29 +3594,29 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="C97" s="4" t="n">
-        <v>107</v>
+        <v>96</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>69</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98">
@@ -3626,29 +3626,29 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="C98" s="9" t="n">
-        <v>82</v>
+        <v>97</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>107</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99">
@@ -3658,19 +3658,19 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -3680,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100">
@@ -3690,51 +3690,51 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>147</v>
+        <v>99</v>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102">
@@ -3754,19 +3754,19 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103">
@@ -3786,29 +3786,29 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="C103" s="4" t="n">
-        <v>129</v>
+        <v>102</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>79</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="104">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>149</v>
+        <v>103</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>121</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -3840,39 +3840,39 @@
         <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="C105" s="9" t="n">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>129</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106">
@@ -3882,19 +3882,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107">
@@ -3914,29 +3914,29 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108">
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -3968,39 +3968,39 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="C109" s="4" t="n">
-        <v>122</v>
+        <v>108</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110">
@@ -4010,29 +4010,29 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C110" s="9" t="n">
-        <v>79</v>
+        <v>109</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>149</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111">
@@ -4042,61 +4042,61 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>213</v>
+        <v>110</v>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>122</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113">
@@ -4106,29 +4106,29 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C113" s="4" t="n">
-        <v>104</v>
+        <v>112</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>145</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114">
@@ -4138,93 +4138,93 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="C114" s="10" t="n">
-        <v>85</v>
+        <v>113</v>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>104</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="C115" s="9" t="n">
-        <v>93</v>
+        <v>114</v>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>86</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C116" s="7" t="n">
-        <v>212</v>
+        <v>115</v>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="117">
@@ -4234,29 +4234,29 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="C117" s="4" t="n">
-        <v>127</v>
+        <v>116</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>212</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118">
@@ -4266,29 +4266,29 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C118" s="10" t="n">
-        <v>112</v>
+        <v>117</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>127</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="119">
@@ -4298,61 +4298,61 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="C119" s="7" t="n">
-        <v>186</v>
+        <v>118</v>
+      </c>
+      <c r="C119" s="10" t="n">
+        <v>112</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
         <v>104</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>186</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="121">
@@ -4362,29 +4362,29 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="C121" s="9" t="n">
-        <v>90</v>
+        <v>120</v>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>123</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G121" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="H121" s="3" t="n">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="122">
@@ -4394,29 +4394,29 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>152</v>
+        <v>121</v>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>90</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>157</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123">
@@ -4426,61 +4426,61 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="C123" s="9" t="n">
-        <v>106</v>
+        <v>122</v>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>152</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>119</v>
+        <v>123</v>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>238</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="125">
@@ -4490,29 +4490,29 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>105</v>
+        <v>124</v>
+      </c>
+      <c r="C125" s="10" t="n">
+        <v>88</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126">
@@ -4522,29 +4522,29 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="C126" s="9" t="n">
-        <v>86</v>
+        <v>125</v>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127">
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C127" s="5" t="n">
-        <v>135</v>
+        <v>126</v>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>156</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -4576,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128">
@@ -4586,29 +4586,29 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C128" s="9" t="n">
-        <v>88</v>
+        <v>127</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>105</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129">
@@ -4618,19 +4618,19 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>132</v>
+        <v>128</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>135</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="130">
@@ -4650,29 +4650,29 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C130" s="7" t="n">
-        <v>189</v>
+        <v>129</v>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>132</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131">
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
         <v>111</v>
@@ -4704,7 +4704,7 @@
         <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132">
@@ -4714,61 +4714,61 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>189</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="C133" s="4" t="n">
-        <v>114</v>
-      </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134">
@@ -4778,26 +4778,26 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="C134" s="7" t="n">
-        <v>165</v>
+        <v>133</v>
+      </c>
+      <c r="C134" s="4" t="n">
+        <v>114</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>122</v>
@@ -4810,19 +4810,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="136">
@@ -4842,9 +4842,9 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="C136" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="C136" s="4" t="n">
         <v>115</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -4864,29 +4864,29 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138">
@@ -4906,29 +4906,29 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>181</v>
+        <v>137</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>106</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="139">
@@ -4938,19 +4938,19 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
     </row>
     <row r="140">
@@ -4970,29 +4970,29 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C140" s="9" t="n">
-        <v>108</v>
+        <v>139</v>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>170</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="141">
@@ -5002,29 +5002,29 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="C141" s="7" t="n">
-        <v>218</v>
+        <v>140</v>
+      </c>
+      <c r="C141" s="9" t="n">
+        <v>108</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -5056,39 +5056,39 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>155</v>
+        <v>142</v>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>167</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144">
@@ -5098,29 +5098,29 @@
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="C144" s="7" t="n">
-        <v>211</v>
+        <v>143</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>155</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145">
@@ -5130,19 +5130,19 @@
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
     </row>
     <row r="146">
@@ -5162,29 +5162,29 @@
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C146" s="5" t="n">
-        <v>157</v>
+        <v>145</v>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>225</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147">
@@ -5194,26 +5194,26 @@
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C147" s="7" t="n">
-        <v>226</v>
+        <v>146</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>157</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
         <v>140</v>
@@ -5226,19 +5226,19 @@
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -5248,29 +5248,29 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C149" s="9" t="n">
-        <v>118</v>
+        <v>148</v>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>120</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -5280,7 +5280,7 @@
         <v>2</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="150">
@@ -5290,61 +5290,61 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>131</v>
+        <v>149</v>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="C151" s="5" t="n">
-        <v>188</v>
+        <v>150</v>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>131</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="152">
@@ -5354,19 +5354,19 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row r="153">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
@@ -5408,24 +5408,24 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>217</v>
+        <v>153</v>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>208</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
         <v>204</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156">
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C156" s="4" t="n">
         <v>153</v>
@@ -5504,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="157">
@@ -5514,19 +5514,19 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158">
@@ -5546,19 +5546,19 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -5568,29 +5568,29 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C159" s="5" t="n">
-        <v>232</v>
+        <v>158</v>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>182</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -5600,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="160">
@@ -5610,19 +5610,19 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C160" s="4" t="n">
-        <v>173</v>
+        <v>159</v>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>232</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
@@ -5632,39 +5632,39 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C161" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Juwan Johnson</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="3" t="n">
         <v>154</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Nailor</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H161" s="3" t="n">
-        <v>177</v>
       </c>
     </row>
     <row r="162">
@@ -5674,29 +5674,29 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C162" s="5" t="n">
-        <v>210</v>
+        <v>161</v>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>154</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>240</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163">
@@ -5706,19 +5706,19 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -5728,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>253</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164">
@@ -5738,19 +5738,19 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165">
@@ -5770,51 +5770,51 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Jauan Jennings</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C165" s="5" t="n">
-        <v>259</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Darnell Mooney</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>NYG</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="3" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>168</v>
+      <c r="C166" s="5" t="n">
+        <v>274</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167">
@@ -5834,19 +5834,19 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C167" s="5" t="n">
-        <v>242</v>
+        <v>166</v>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>171</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168">
@@ -5866,61 +5866,61 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Braelon Allen</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C168" s="9" t="n">
+      <c r="C169" s="9" t="n">
         <v>124</v>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Keaton Mitchell</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="F168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="4" t="n">
+      <c r="F169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H168" s="3" t="n">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C169" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Aubrey</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H169" s="3" t="n">
-        <v>235</v>
+        <v>161</v>
       </c>
     </row>
     <row r="170">
@@ -5930,29 +5930,29 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>217</v>
+        <v>162</v>
       </c>
     </row>
     <row r="171">
@@ -5962,19 +5962,19 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="C171" s="10" t="n">
-        <v>150</v>
+        <v>182</v>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>138</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>228</v>
+        <v>189</v>
       </c>
     </row>
     <row r="172">
@@ -5994,29 +5994,29 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>163</v>
+        <v>183</v>
+      </c>
+      <c r="C172" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Harrison Mevis</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>224</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173">
@@ -6026,29 +6026,29 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="C173" s="9" t="n">
-        <v>139</v>
+        <v>184</v>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>163</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Ka'imi Fairbairn</t>
+          <t>Harrison Mevis</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>218</v>
+        <v>169</v>
       </c>
     </row>
     <row r="174">
@@ -6058,29 +6058,29 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>162</v>
+        <v>185</v>
+      </c>
+      <c r="C174" s="9" t="n">
+        <v>139</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Eddy Pineiro</t>
+          <t>Ka'imi Fairbairn</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
     </row>
     <row r="175">
@@ -6090,19 +6090,19 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Harrison Butker</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>251</v>
+        <v>171</v>
       </c>
     </row>
     <row r="176">
@@ -6122,29 +6122,29 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="C176" s="9" t="n">
-        <v>137</v>
+        <v>187</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>195</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Cam Little</t>
+          <t>Harrison Butker</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177">
@@ -6154,19 +6154,19 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C177" s="9" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Cam Little</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
@@ -6176,7 +6176,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>220</v>
+        <v>188</v>
       </c>
     </row>
     <row r="178">
@@ -6186,29 +6186,29 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="C178" s="10" t="n">
-        <v>161</v>
+        <v>189</v>
+      </c>
+      <c r="C178" s="9" t="n">
+        <v>143</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Tyler Loop</t>
+          <t>Jake Bates</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>226</v>
+        <v>185</v>
       </c>
     </row>
     <row r="179">
@@ -6218,19 +6218,19 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C179" s="10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Tyler Loop</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
@@ -6240,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>227</v>
+        <v>166</v>
       </c>
     </row>
     <row r="180">
@@ -6250,117 +6250,117 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="C180" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Cairo Santos</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C180" s="5" t="n">
+      <c r="C181" s="5" t="n">
         <v>221</v>
       </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Will Reichard</t>
         </is>
       </c>
-      <c r="E180" s="3" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="3" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="F181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B181" s="3" t="n">
+      <c r="B182" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="C181" s="5" t="n">
-        <v>237</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Justice Hill</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="8" t="inlineStr">
+      <c r="C182" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="B182" s="3" t="n">
+      <c r="B183" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="C182" s="4" t="n">
+      <c r="C183" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Brenton Strange</t>
         </is>
       </c>
-      <c r="E182" s="3" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>JAC</t>
         </is>
       </c>
-      <c r="F182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="C183" s="5" t="n">
-        <v>249</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Jordan James</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
       <c r="F183" s="3" t="n">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184">
@@ -6378,93 +6378,93 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>James Conner</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C184" s="4" t="n">
-        <v>205</v>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Kaelon Black</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" s="3" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="n">
+      <c r="C185" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Justice Hill</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Chris Bell</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" s="3" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="C186" s="9" t="n">
-        <v>116</v>
+      <c r="C186" s="5" t="n">
+        <v>256</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>242</v>
+        <v>226</v>
       </c>
     </row>
     <row r="187">
@@ -6474,29 +6474,29 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="C187" s="9" t="n">
+        <v>116</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F187" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="188">
@@ -6506,53 +6506,53 @@
         </is>
       </c>
       <c r="B188" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Cam Ward</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C188" s="10" t="n">
+      <c r="C189" s="10" t="n">
         <v>164</v>
       </c>
-      <c r="D188" s="3" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>C.J. Stroud</t>
         </is>
       </c>
-      <c r="E188" s="3" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="F188" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" s="3" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C189" s="5" t="n">
-        <v>244</v>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>Jack Bech</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
       <c r="F189" s="3" t="n">
         <v>0</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190">
@@ -6570,29 +6570,29 @@
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C190" s="10" t="n">
-        <v>156</v>
+        <v>201</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>259</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="191">
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C191" s="10" t="n">
         <v>134</v>
@@ -6624,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
     </row>
     <row r="192">
@@ -6634,51 +6634,51 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Flournoy</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C192" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Isaac TeSlaa</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" s="3" t="n">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>206</v>
-      </c>
       <c r="C193" s="5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="194">
@@ -6698,53 +6698,53 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="C194" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Pat Freiermuth</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C194" s="4" t="n">
+      <c r="C195" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="D194" s="3" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Dalton Schultz</t>
         </is>
       </c>
-      <c r="E194" s="3" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="F194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" s="3" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="C195" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Ryan Flournoy</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
       <c r="F195" s="3" t="n">
         <v>0</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>244</v>
+        <v>206</v>
       </c>
     </row>
     <row r="196">
@@ -6764,17 +6764,17 @@
       <c r="B196" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C196" s="4" t="n">
-        <v>236</v>
+      <c r="C196" s="5" t="n">
+        <v>244</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -6784,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="197">
@@ -6797,16 +6797,16 @@
         <v>210</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -6816,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="198">
@@ -6829,16 +6829,16 @@
         <v>211</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>193</v>
+        <v>227</v>
       </c>
     </row>
     <row r="199">
@@ -6861,16 +6861,16 @@
         <v>212</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="200">
@@ -6892,17 +6892,17 @@
       <c r="B200" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="C200" s="5" t="n">
-        <v>272</v>
+      <c r="C200" s="4" t="n">
+        <v>205</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="201">
@@ -6924,17 +6924,17 @@
       <c r="B201" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="C201" s="5" t="n">
-        <v>279</v>
+      <c r="C201" s="4" t="n">
+        <v>227</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F201" s="3" t="n">
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202">
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="203">
@@ -6988,17 +6988,17 @@
       <c r="B203" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="C203" s="4" t="n">
-        <v>187</v>
+      <c r="C203" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>230</v>
+        <v>174</v>
       </c>
     </row>
     <row r="204">
@@ -7021,16 +7021,16 @@
         <v>217</v>
       </c>
       <c r="C204" s="10" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>215</v>
+        <v>173</v>
       </c>
     </row>
     <row r="205">
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>221</v>
+        <v>170</v>
       </c>
     </row>
     <row r="206">
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>214</v>
+        <v>187</v>
       </c>
     </row>
     <row r="207">
@@ -7136,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>248</v>
+        <v>197</v>
       </c>
     </row>
     <row r="208">
@@ -7148,17 +7148,17 @@
       <c r="B208" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="C208" s="4" t="n">
-        <v>228</v>
+      <c r="C208" s="5" t="n">
+        <v>272</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>208</v>
+        <v>238</v>
       </c>
     </row>
     <row r="209">
@@ -7178,83 +7178,83 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Demond Claiborne</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C209" s="5" t="n">
-        <v>262</v>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Emmett Johnson</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" s="3" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="n">
+      <c r="C210" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Kimani Vidal</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C210" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>Zachariah Branch</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" s="3" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C211" s="10" t="n">
-        <v>182</v>
+      <c r="C211" s="4" t="n">
+        <v>206</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7264,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212">
@@ -7274,46 +7274,46 @@
         </is>
       </c>
       <c r="B212" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C212" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Samaje Perine</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="n">
-        <v>228</v>
-      </c>
       <c r="C213" s="5" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>197</v>
+        <v>241</v>
       </c>
     </row>
     <row r="214">
@@ -7338,14 +7338,14 @@
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="C214" s="4" t="n">
-        <v>206</v>
+        <v>227</v>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>269</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -7360,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="215">
@@ -7370,19 +7370,19 @@
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C215" s="5" t="n">
-        <v>299</v>
+        <v>228</v>
+      </c>
+      <c r="C215" s="4" t="n">
+        <v>234</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Christian Kirk</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>254</v>
+        <v>208</v>
       </c>
     </row>
     <row r="216">
@@ -7402,19 +7402,19 @@
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Chris Brazzell</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217">
@@ -7434,181 +7434,181 @@
         </is>
       </c>
       <c r="B217" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="C217" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Aiyuk</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hurst</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C217" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H217" s="3" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="12" t="inlineStr">
+      <c r="C220" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Keon Coleman</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B218" s="3" t="n">
+      <c r="B221" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C218" s="10" t="n">
+      <c r="C221" s="10" t="n">
         <v>194</v>
       </c>
-      <c r="D218" s="3" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>Chris Boswell</t>
         </is>
       </c>
-      <c r="E218" s="3" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="F218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H218" s="3" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="12" t="inlineStr">
+      <c r="F221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B219" s="3" t="n">
+      <c r="B222" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="C219" s="10" t="n">
+      <c r="C222" s="10" t="n">
         <v>183</v>
       </c>
-      <c r="D219" s="3" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>Chase McLaughlin</t>
         </is>
       </c>
-      <c r="E219" s="3" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="F219" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" s="3" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C220" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>LeQuint Allen</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" s="3" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C221" s="4" t="n">
-        <v>273</v>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>Jaylen Wright</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" s="3" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C222" s="4" t="n">
-        <v>275</v>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>Ollie Gordon</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="F222" s="3" t="n">
         <v>0</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="223">
@@ -7626,19 +7626,19 @@
         </is>
       </c>
       <c r="B223" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C223" s="4" t="n">
-        <v>263</v>
+        <v>240</v>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>286</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F223" s="3" t="n">
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>202</v>
+        <v>250</v>
       </c>
     </row>
     <row r="224">
@@ -7658,19 +7658,19 @@
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="C224" s="4" t="n">
-        <v>202</v>
+        <v>241</v>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>287</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F224" s="3" t="n">
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="225">
@@ -7690,19 +7690,19 @@
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="226">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C226" s="4" t="n">
         <v>250</v>
@@ -7744,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>164</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227">
@@ -7754,211 +7754,211 @@
         </is>
       </c>
       <c r="B227" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>261</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="C229" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Isaiah Davis</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" s="3" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Emmett Johnson</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Sean Tucker</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C227" s="4" t="n">
-        <v>283</v>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" s="3" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>253</v>
-      </c>
-      <c r="C228" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H228" s="3" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="C229" s="10" t="n">
-        <v>144</v>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>Evan McPherson</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H229" s="3" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C230" s="10" t="n">
-        <v>179</v>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>AJ Barner</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" s="3" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C231" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>Greg Dulcich</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H231" s="3" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C232" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H232" s="3" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>261</v>
-      </c>
       <c r="C233" s="4" t="n">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>DJ Giddens</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>188</v>
+        <v>233</v>
       </c>
     </row>
     <row r="234">
@@ -7978,19 +7978,19 @@
         </is>
       </c>
       <c r="B234" s="3" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -8000,61 +8000,61 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>181</v>
+        <v>217</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A235" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C235" s="4" t="n">
-        <v>276</v>
+        <v>256</v>
+      </c>
+      <c r="C235" s="10" t="n">
+        <v>144</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Evan McPherson</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F235" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" s="3" t="n">
         <v>191</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="C236" s="4" t="n">
-        <v>278</v>
+        <v>258</v>
+      </c>
+      <c r="C236" s="10" t="n">
+        <v>187</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -8064,519 +8064,519 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Greg Dulcich</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="C238" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Pat Bryant</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Tory Horton</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="B237" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C237" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>George Holani</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
+      <c r="B242" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Emanuel Wilson</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F237" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H237" s="3" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C238" s="4" t="n">
-        <v>281</v>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Davis</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C243" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Geno Smith</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>NYJ</t>
         </is>
       </c>
-      <c r="F238" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H238" s="3" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="11" t="inlineStr">
+      <c r="F243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B239" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C239" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" s="3" t="n">
+      <c r="B244" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C244" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Rodgers</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C245" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Treylon Burks</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Marvin Mims</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="3" t="n">
         <v>249</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C240" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="C241" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="C242" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>Jacoby Brissett</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="C243" s="4" t="n">
-        <v>246</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Sarratt</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>243</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Dontayvion Wicks</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Jake Elliott</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="F244" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C245" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>Kayshon Boutte</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H245" s="3" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="C246" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Darius Slayton</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>NYG</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C247" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>DJ Giddens</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="C248" s="4" t="n">
-        <v>203</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>Sean Tucker</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="C249" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>Emanuel Wilson</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C250" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>Jake Elliott</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C251" s="4" t="n">
+      <c r="F252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3" t="n">
         <v>255</v>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="3" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" s="3" t="n">
-        <v>162</v>
       </c>
     </row>
     <row r="253">
@@ -8586,93 +8586,125 @@
         </is>
       </c>
       <c r="B253" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Evan Engram</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="C253" s="4" t="n">
+      <c r="C255" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="D253" s="3" t="inlineStr">
+      <c r="D255" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="E253" s="3" t="inlineStr">
+      <c r="E255" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="F253" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="3" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="11" t="inlineStr">
+      <c r="F255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B255" s="3" t="n">
+      <c r="B256" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C255" s="4" t="n">
+      <c r="C256" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="D255" s="3" t="inlineStr">
+      <c r="D256" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
+      <c r="E256" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F255" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>171</v>
+      <c r="F256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:I256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,11 @@
           <t>PriceRank</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Adjusted Rank Half PPR</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -578,6 +583,9 @@
       <c r="H2" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="I2" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -608,7 +616,10 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -640,6 +651,9 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -674,6 +688,9 @@
       <c r="H5" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="I5" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -706,6 +723,9 @@
       <c r="H6" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -738,6 +758,9 @@
       <c r="H7" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="I7" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -770,6 +793,9 @@
       <c r="H8" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="I8" s="3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -802,6 +828,9 @@
       <c r="H9" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="I9" s="3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -834,6 +863,9 @@
       <c r="H10" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="I10" s="3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -866,6 +898,9 @@
       <c r="H11" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="I11" s="3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -898,6 +933,9 @@
       <c r="H12" s="3" t="n">
         <v>11</v>
       </c>
+      <c r="I12" s="3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -930,6 +968,9 @@
       <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="I13" s="3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -962,6 +1003,9 @@
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="I14" s="3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -994,6 +1038,9 @@
       <c r="H15" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="I15" s="3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1026,6 +1073,9 @@
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="I16" s="3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1058,6 +1108,9 @@
       <c r="H17" s="3" t="n">
         <v>16</v>
       </c>
+      <c r="I17" s="3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1090,6 +1143,9 @@
       <c r="H18" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="I18" s="3" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1122,6 +1178,9 @@
       <c r="H19" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="I19" s="3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1154,6 +1213,9 @@
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
+      <c r="I20" s="3" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1186,6 +1248,9 @@
       <c r="H21" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="I21" s="3" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1218,6 +1283,9 @@
       <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
+      <c r="I22" s="3" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1250,6 +1318,9 @@
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="I23" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1282,6 +1353,9 @@
       <c r="H24" s="3" t="n">
         <v>24</v>
       </c>
+      <c r="I24" s="3" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1314,6 +1388,9 @@
       <c r="H25" s="3" t="n">
         <v>23</v>
       </c>
+      <c r="I25" s="3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1346,6 +1423,9 @@
       <c r="H26" s="3" t="n">
         <v>25</v>
       </c>
+      <c r="I26" s="3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1378,6 +1458,9 @@
       <c r="H27" s="3" t="n">
         <v>26</v>
       </c>
+      <c r="I27" s="3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1410,6 +1493,9 @@
       <c r="H28" s="3" t="n">
         <v>27</v>
       </c>
+      <c r="I28" s="3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1442,6 +1528,9 @@
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
+      <c r="I29" s="3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1474,6 +1563,9 @@
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
+      <c r="I30" s="3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1506,6 +1598,9 @@
       <c r="H31" s="3" t="n">
         <v>30</v>
       </c>
+      <c r="I31" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1538,6 +1633,9 @@
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
+      <c r="I32" s="3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1570,6 +1668,9 @@
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="I33" s="3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1602,6 +1703,9 @@
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
+      <c r="I34" s="3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1634,6 +1738,9 @@
       <c r="H35" s="3" t="n">
         <v>34</v>
       </c>
+      <c r="I35" s="3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1664,7 +1771,10 @@
         <v>30</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="37">
@@ -1698,6 +1808,9 @@
       <c r="H37" s="3" t="n">
         <v>35</v>
       </c>
+      <c r="I37" s="3" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1728,7 +1841,10 @@
         <v>24</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -1762,6 +1878,9 @@
       <c r="H39" s="3" t="n">
         <v>39</v>
       </c>
+      <c r="I39" s="3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1794,6 +1913,9 @@
       <c r="H40" s="3" t="n">
         <v>38</v>
       </c>
+      <c r="I40" s="3" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1826,6 +1948,9 @@
       <c r="H41" s="3" t="n">
         <v>40</v>
       </c>
+      <c r="I41" s="3" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1856,7 +1981,10 @@
         <v>6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="43">
@@ -1888,7 +2016,10 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -1922,6 +2053,9 @@
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
+      <c r="I44" s="3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -1954,6 +2088,9 @@
       <c r="H45" s="3" t="n">
         <v>44</v>
       </c>
+      <c r="I45" s="3" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -1986,6 +2123,9 @@
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
+      <c r="I46" s="3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2018,6 +2158,9 @@
       <c r="H47" s="3" t="n">
         <v>46</v>
       </c>
+      <c r="I47" s="3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2050,6 +2193,9 @@
       <c r="H48" s="3" t="n">
         <v>47</v>
       </c>
+      <c r="I48" s="3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2082,6 +2228,9 @@
       <c r="H49" s="3" t="n">
         <v>48</v>
       </c>
+      <c r="I49" s="3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -2114,6 +2263,9 @@
       <c r="H50" s="3" t="n">
         <v>49</v>
       </c>
+      <c r="I50" s="3" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -2146,6 +2298,9 @@
       <c r="H51" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="I51" s="3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -2178,6 +2333,9 @@
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
+      <c r="I52" s="3" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2208,7 +2366,10 @@
         <v>13</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -2240,7 +2401,10 @@
         <v>10</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="55">
@@ -2274,6 +2438,9 @@
       <c r="H55" s="3" t="n">
         <v>56</v>
       </c>
+      <c r="I55" s="3" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -2306,6 +2473,9 @@
       <c r="H56" s="3" t="n">
         <v>54</v>
       </c>
+      <c r="I56" s="3" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -2336,7 +2506,10 @@
         <v>17</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -2368,7 +2541,10 @@
         <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="59">
@@ -2402,6 +2578,9 @@
       <c r="H59" s="3" t="n">
         <v>59</v>
       </c>
+      <c r="I59" s="3" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2432,7 +2611,10 @@
         <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2646,10 @@
         <v>10</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="62">
@@ -2498,6 +2683,9 @@
       <c r="H62" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="I62" s="3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2528,7 +2716,10 @@
         <v>10</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="64">
@@ -2560,7 +2751,10 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -2592,7 +2786,10 @@
         <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="66">
@@ -2624,7 +2821,10 @@
         <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="67">
@@ -2656,7 +2856,10 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="68">
@@ -2688,7 +2891,10 @@
         <v>7</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="69">
@@ -2720,7 +2926,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="70">
@@ -2752,7 +2961,10 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="71">
@@ -2784,7 +2996,10 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="72">
@@ -2816,7 +3031,10 @@
         <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="73">
@@ -2848,7 +3066,10 @@
         <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="74">
@@ -2882,6 +3103,9 @@
       <c r="H74" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="I74" s="3" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -2912,7 +3136,10 @@
         <v>9</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="76">
@@ -2944,7 +3171,10 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="77">
@@ -2976,7 +3206,10 @@
         <v>11</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -3008,7 +3241,10 @@
         <v>7</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="79">
@@ -3040,7 +3276,10 @@
         <v>15</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="80">
@@ -3072,7 +3311,10 @@
         <v>2</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -3104,7 +3346,10 @@
         <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="82">
@@ -3136,7 +3381,10 @@
         <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="83">
@@ -3168,7 +3416,10 @@
         <v>3</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="84">
@@ -3202,6 +3453,9 @@
       <c r="H84" s="3" t="n">
         <v>84</v>
       </c>
+      <c r="I84" s="3" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -3232,7 +3486,10 @@
         <v>3</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="86">
@@ -3264,7 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="87">
@@ -3296,7 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="88">
@@ -3328,7 +3591,10 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="89">
@@ -3360,7 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="90">
@@ -3392,7 +3661,10 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="91">
@@ -3424,7 +3696,10 @@
         <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="92">
@@ -3456,7 +3731,10 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>89</v>
+        <v>94</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="93">
@@ -3488,7 +3766,10 @@
         <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="94">
@@ -3520,7 +3801,10 @@
         <v>5</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="95">
@@ -3552,7 +3836,10 @@
         <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="96">
@@ -3584,7 +3871,10 @@
         <v>7</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="97">
@@ -3616,7 +3906,10 @@
         <v>6</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>120</v>
+        <v>111</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="98">
@@ -3648,7 +3941,10 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>106</v>
+        <v>118</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="99">
@@ -3682,6 +3978,9 @@
       <c r="H99" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="I99" s="3" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3712,7 +4011,10 @@
         <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>102</v>
+        <v>96</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="101">
@@ -3746,6 +4048,9 @@
       <c r="H101" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="I101" s="3" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -3776,7 +4081,10 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>107</v>
+        <v>99</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="103">
@@ -3808,7 +4116,10 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="104">
@@ -3840,7 +4151,10 @@
         <v>1</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="105">
@@ -3872,7 +4186,10 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>108</v>
+        <v>98</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>131</v>
       </c>
     </row>
     <row r="106">
@@ -3904,7 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>98</v>
+        <v>114</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="107">
@@ -3936,7 +4256,10 @@
         <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>99</v>
+        <v>113</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="108">
@@ -3968,7 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="109">
@@ -4000,7 +4326,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="110">
@@ -4032,7 +4361,10 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="111">
@@ -4064,7 +4396,10 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>96</v>
+        <v>103</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="112">
@@ -4096,7 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>119</v>
+        <v>108</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="113">
@@ -4128,7 +4466,10 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>117</v>
+        <v>120</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="114">
@@ -4160,7 +4501,10 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="115">
@@ -4192,7 +4536,10 @@
         <v>4</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="116">
@@ -4224,7 +4571,10 @@
         <v>3</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>100</v>
+        <v>117</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="117">
@@ -4256,7 +4606,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="118">
@@ -4288,7 +4641,10 @@
         <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>97</v>
+        <v>100</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="119">
@@ -4320,7 +4676,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="120">
@@ -4352,7 +4711,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>113</v>
+        <v>101</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="121">
@@ -4384,7 +4746,10 @@
         <v>1</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="122">
@@ -4416,7 +4781,10 @@
         <v>3</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>123</v>
+        <v>158</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="123">
@@ -4448,7 +4816,10 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>138</v>
+        <v>159</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>147</v>
       </c>
     </row>
     <row r="124">
@@ -4480,7 +4851,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>128</v>
+        <v>141</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="125">
@@ -4512,7 +4886,10 @@
         <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>121</v>
+        <v>160</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="126">
@@ -4544,7 +4921,10 @@
         <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>132</v>
+        <v>152</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="127">
@@ -4576,7 +4956,10 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>141</v>
+        <v>143</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="128">
@@ -4608,7 +4991,10 @@
         <v>2</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>126</v>
+        <v>157</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="129">
@@ -4640,7 +5026,10 @@
         <v>1</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="130">
@@ -4672,7 +5061,10 @@
         <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>135</v>
+        <v>153</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="131">
@@ -4704,7 +5096,10 @@
         <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="132">
@@ -4736,7 +5131,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>146</v>
+        <v>133</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="133">
@@ -4768,7 +5166,10 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>159</v>
+        <v>144</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="134">
@@ -4800,7 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>122</v>
+        <v>149</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="135">
@@ -4832,7 +5236,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>145</v>
+        <v>128</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="136">
@@ -4864,7 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>136</v>
+        <v>148</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="137">
@@ -4896,7 +5306,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>148</v>
+        <v>121</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>178</v>
       </c>
     </row>
     <row r="138">
@@ -4928,7 +5341,10 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>124</v>
+        <v>156</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="139">
@@ -4960,7 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>149</v>
+        <v>130</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="140">
@@ -4992,7 +5411,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>144</v>
+        <v>122</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="141">
@@ -5024,7 +5446,10 @@
         <v>2</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>127</v>
+        <v>154</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="142">
@@ -5056,7 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>137</v>
+        <v>123</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="143">
@@ -5088,7 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>139</v>
+        <v>126</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>156</v>
       </c>
     </row>
     <row r="144">
@@ -5120,6 +5551,9 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="I144" s="3" t="n">
         <v>158</v>
       </c>
     </row>
@@ -5152,7 +5586,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>151</v>
+        <v>135</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="146">
@@ -5184,7 +5621,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>156</v>
+        <v>137</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>181</v>
       </c>
     </row>
     <row r="147">
@@ -5216,7 +5656,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>140</v>
+        <v>125</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="148">
@@ -5248,7 +5691,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>147</v>
+        <v>132</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="149">
@@ -5280,7 +5726,10 @@
         <v>2</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>134</v>
+        <v>151</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="150">
@@ -5312,7 +5761,10 @@
         <v>2</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="151">
@@ -5344,7 +5796,10 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>131</v>
+        <v>147</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="152">
@@ -5376,7 +5831,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>160</v>
+        <v>138</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>223</v>
       </c>
     </row>
     <row r="153">
@@ -5408,7 +5866,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>129</v>
+        <v>142</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>268</v>
       </c>
     </row>
     <row r="154">
@@ -5440,7 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>152</v>
+        <v>129</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="155">
@@ -5472,7 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>150</v>
+        <v>134</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="156">
@@ -5506,6 +5973,9 @@
       <c r="H156" s="3" t="n">
         <v>155</v>
       </c>
+      <c r="I156" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -5536,7 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>157</v>
+        <v>136</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="158">
@@ -5568,7 +6041,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>142</v>
+        <v>124</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="159">
@@ -5600,7 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="160">
@@ -5632,7 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>130</v>
+        <v>140</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="161">
@@ -5664,7 +6146,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>154</v>
+        <v>127</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="162">
@@ -5696,7 +6181,10 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>164</v>
+        <v>167</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>157</v>
       </c>
     </row>
     <row r="163">
@@ -5728,7 +6216,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>177</v>
+        <v>231</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="164">
@@ -5760,7 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>192</v>
+        <v>243</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="165">
@@ -5792,7 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>179</v>
+        <v>233</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="166">
@@ -5824,7 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>240</v>
+        <v>196</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="167">
@@ -5856,7 +6356,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>175</v>
+        <v>218</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="168">
@@ -5888,7 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>201</v>
+        <v>239</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>225</v>
       </c>
     </row>
     <row r="169">
@@ -5920,7 +6426,10 @@
         <v>1</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>161</v>
+        <v>211</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="170">
@@ -5952,7 +6461,10 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>162</v>
+        <v>235</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="171">
@@ -5984,7 +6496,10 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>189</v>
+        <v>220</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="172">
@@ -6016,7 +6531,10 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>167</v>
+        <v>230</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="173">
@@ -6048,7 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>169</v>
+        <v>226</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>164</v>
       </c>
     </row>
     <row r="174">
@@ -6080,7 +6601,10 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>190</v>
+        <v>221</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="175">
@@ -6112,7 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>171</v>
+        <v>227</v>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="176">
@@ -6144,7 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>182</v>
+        <v>254</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="177">
@@ -6176,7 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>188</v>
+        <v>219</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="178">
@@ -6208,7 +6741,10 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>185</v>
+        <v>222</v>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="179">
@@ -6240,7 +6776,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>166</v>
+        <v>228</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="180">
@@ -6272,7 +6811,10 @@
         <v>1</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>165</v>
+        <v>229</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="181">
@@ -6304,7 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>203</v>
+        <v>207</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>228</v>
       </c>
     </row>
     <row r="182">
@@ -6336,7 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>222</v>
+        <v>164</v>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>253</v>
       </c>
     </row>
     <row r="183">
@@ -6368,7 +6916,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>186</v>
+        <v>213</v>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>185</v>
       </c>
     </row>
     <row r="184">
@@ -6400,7 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>216</v>
+        <v>173</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>243</v>
       </c>
     </row>
     <row r="185">
@@ -6432,7 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>215</v>
+        <v>177</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>239</v>
       </c>
     </row>
     <row r="186">
@@ -6464,7 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>226</v>
+        <v>165</v>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="187">
@@ -6496,7 +7056,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>163</v>
+        <v>244</v>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="188">
@@ -6528,7 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>183</v>
+        <v>253</v>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="189">
@@ -6560,7 +7126,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>168</v>
+        <v>225</v>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="190">
@@ -6592,7 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>228</v>
+        <v>170</v>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>274</v>
       </c>
     </row>
     <row r="191">
@@ -6624,7 +7196,10 @@
         <v>1</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>184</v>
+        <v>215</v>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="192">
@@ -6656,7 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>176</v>
+        <v>232</v>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="193">
@@ -6688,7 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>235</v>
+        <v>201</v>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>275</v>
       </c>
     </row>
     <row r="194">
@@ -6720,7 +7301,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>232</v>
+        <v>204</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>272</v>
       </c>
     </row>
     <row r="195">
@@ -6752,7 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>206</v>
+        <v>241</v>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="196">
@@ -6784,7 +7371,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>219</v>
+        <v>171</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="197">
@@ -6816,7 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>193</v>
+        <v>234</v>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>214</v>
       </c>
     </row>
     <row r="198">
@@ -6848,7 +7441,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>227</v>
+        <v>178</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="199">
@@ -6880,7 +7476,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>205</v>
+        <v>236</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="200">
@@ -6912,7 +7511,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>196</v>
+        <v>248</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>211</v>
       </c>
     </row>
     <row r="201">
@@ -6944,7 +7546,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>204</v>
+        <v>237</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="202">
@@ -6978,6 +7583,9 @@
       <c r="H202" s="3" t="n">
         <v>209</v>
       </c>
+      <c r="I202" s="3" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
@@ -7008,7 +7616,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>174</v>
+        <v>217</v>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>173</v>
       </c>
     </row>
     <row r="204">
@@ -7040,7 +7651,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>173</v>
+        <v>214</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="205">
@@ -7072,7 +7686,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>170</v>
+        <v>223</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>167</v>
       </c>
     </row>
     <row r="206">
@@ -7104,7 +7721,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>187</v>
+        <v>216</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>177</v>
       </c>
     </row>
     <row r="207">
@@ -7136,7 +7756,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>197</v>
+        <v>251</v>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="208">
@@ -7168,7 +7791,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>238</v>
+        <v>198</v>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>279</v>
       </c>
     </row>
     <row r="209">
@@ -7200,7 +7826,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>244</v>
+        <v>192</v>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>287</v>
       </c>
     </row>
     <row r="210">
@@ -7232,7 +7861,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>231</v>
+        <v>179</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>252</v>
       </c>
     </row>
     <row r="211">
@@ -7264,7 +7896,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>194</v>
+        <v>247</v>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v>196</v>
       </c>
     </row>
     <row r="212">
@@ -7296,7 +7931,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>239</v>
+        <v>197</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="213">
@@ -7328,7 +7966,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>241</v>
+        <v>195</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="214">
@@ -7360,7 +8001,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>236</v>
+        <v>200</v>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>278</v>
       </c>
     </row>
     <row r="215">
@@ -7394,6 +8038,9 @@
       <c r="H215" s="3" t="n">
         <v>208</v>
       </c>
+      <c r="I215" s="3" t="n">
+        <v>237</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -7424,7 +8071,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>211</v>
+        <v>205</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="217">
@@ -7456,7 +8106,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>210</v>
+        <v>206</v>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="218">
@@ -7488,7 +8141,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>253</v>
+        <v>183</v>
+      </c>
+      <c r="I218" s="3" t="n">
+        <v>246</v>
       </c>
     </row>
     <row r="219">
@@ -7520,7 +8176,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>242</v>
+        <v>193</v>
+      </c>
+      <c r="I219" s="3" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="220">
@@ -7552,7 +8211,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>243</v>
+        <v>181</v>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="221">
@@ -7584,7 +8246,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>181</v>
+        <v>245</v>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>201</v>
       </c>
     </row>
     <row r="222">
@@ -7616,7 +8281,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>178</v>
+        <v>212</v>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v>187</v>
       </c>
     </row>
     <row r="223">
@@ -7648,7 +8316,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>250</v>
+        <v>186</v>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="224">
@@ -7680,7 +8351,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>251</v>
+        <v>185</v>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="225">
@@ -7712,7 +8386,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>198</v>
+        <v>250</v>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="226">
@@ -7744,7 +8421,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>223</v>
+        <v>162</v>
+      </c>
+      <c r="I226" s="3" t="n">
+        <v>193</v>
       </c>
     </row>
     <row r="227">
@@ -7776,7 +8456,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>247</v>
+        <v>189</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="228">
@@ -7808,7 +8491,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>229</v>
+        <v>180</v>
+      </c>
+      <c r="I228" s="3" t="n">
+        <v>266</v>
       </c>
     </row>
     <row r="229">
@@ -7840,7 +8526,10 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>246</v>
+        <v>190</v>
+      </c>
+      <c r="I229" s="3" t="n">
+        <v>289</v>
       </c>
     </row>
     <row r="230">
@@ -7872,7 +8561,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>230</v>
+        <v>194</v>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>265</v>
       </c>
     </row>
     <row r="231">
@@ -7904,7 +8596,10 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>248</v>
+        <v>188</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="232">
@@ -7936,7 +8631,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>199</v>
+        <v>249</v>
+      </c>
+      <c r="I232" s="3" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="233">
@@ -7968,7 +8666,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>233</v>
+        <v>203</v>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>273</v>
       </c>
     </row>
     <row r="234">
@@ -8000,7 +8701,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>217</v>
+        <v>172</v>
+      </c>
+      <c r="I234" s="3" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="235">
@@ -8032,7 +8736,10 @@
         <v>1</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>191</v>
+        <v>224</v>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="236">
@@ -8064,7 +8771,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>172</v>
+        <v>210</v>
+      </c>
+      <c r="I236" s="3" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="237">
@@ -8096,7 +8806,10 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>207</v>
+        <v>242</v>
+      </c>
+      <c r="I237" s="3" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="238">
@@ -8128,7 +8841,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>200</v>
+        <v>238</v>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="239">
@@ -8160,7 +8876,10 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>218</v>
+        <v>169</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="240">
@@ -8192,7 +8911,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>245</v>
+        <v>191</v>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>291</v>
       </c>
     </row>
     <row r="241">
@@ -8224,7 +8946,10 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>220</v>
+        <v>168</v>
+      </c>
+      <c r="I241" s="3" t="n">
+        <v>249</v>
       </c>
     </row>
     <row r="242">
@@ -8256,7 +8981,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>237</v>
+        <v>199</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>277</v>
       </c>
     </row>
     <row r="243">
@@ -8288,7 +9016,10 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>180</v>
+        <v>252</v>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="244">
@@ -8320,7 +9051,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>202</v>
+        <v>240</v>
+      </c>
+      <c r="I244" s="3" t="n">
+        <v>221</v>
       </c>
     </row>
     <row r="245">
@@ -8352,7 +9086,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>212</v>
+        <v>176</v>
+      </c>
+      <c r="I245" s="3" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="246">
@@ -8384,7 +9121,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>214</v>
+        <v>174</v>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="247">
@@ -8416,7 +9156,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>195</v>
+        <v>246</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>212</v>
       </c>
     </row>
     <row r="248">
@@ -8448,7 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>254</v>
+        <v>182</v>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="249">
@@ -8480,7 +9226,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>221</v>
+        <v>166</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="250">
@@ -8512,7 +9261,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>252</v>
+        <v>184</v>
+      </c>
+      <c r="I250" s="3" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="251">
@@ -8544,7 +9296,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>249</v>
+        <v>187</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="252">
@@ -8578,6 +9333,9 @@
       <c r="H252" s="3" t="n">
         <v>255</v>
       </c>
+      <c r="I252" s="3" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
@@ -8608,7 +9366,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>225</v>
+        <v>163</v>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="254">
@@ -8640,7 +9401,10 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>224</v>
+        <v>161</v>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="255">
@@ -8672,7 +9436,10 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>234</v>
+        <v>202</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="256">
@@ -8704,7 +9471,10 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>213</v>
+        <v>175</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I256"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>54</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>5</v>
@@ -737,7 +737,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>6</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
         <v>52</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6</v>
@@ -807,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>52</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>51</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>9</v>
@@ -877,7 +877,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -892,8 +892,8 @@
       <c r="F11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>45</v>
+      <c r="G11" s="4" t="n">
+        <v>48</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>10</v>
@@ -911,8 +911,8 @@
       <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>9</v>
+      <c r="C12" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>46</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
@@ -982,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
@@ -1052,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1067,8 +1067,8 @@
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>38</v>
+      <c r="G16" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
@@ -1121,8 +1121,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>32</v>
+      <c r="C18" s="5" t="n">
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1137,8 +1137,8 @@
       <c r="F18" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>25</v>
+      <c r="G18" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1157,7 +1157,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>37</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
@@ -1192,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1297,7 +1297,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
@@ -1331,8 +1331,8 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>34</v>
+      <c r="C24" s="7" t="n">
+        <v>38</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>23</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>36</v>
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>18</v>
@@ -1402,7 +1402,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1417,8 +1417,8 @@
       <c r="F26" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="10" t="n">
-        <v>35</v>
+      <c r="G26" s="4" t="n">
+        <v>34</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
@@ -1436,8 +1436,8 @@
       <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>40</v>
+      <c r="C27" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1452,11 +1452,11 @@
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>20</v>
+      <c r="G27" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>40</v>
@@ -1472,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
       <c r="F28" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="10" t="n">
-        <v>34</v>
+      <c r="G28" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>23</v>
@@ -1507,7 +1507,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1522,8 +1522,8 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>22</v>
+      <c r="G29" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
@@ -1541,8 +1541,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>23</v>
+      <c r="C30" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
@@ -1577,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1627,8 +1627,8 @@
       <c r="F32" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>26</v>
+      <c r="G32" s="5" t="n">
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
@@ -1646,8 +1646,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>24</v>
+      <c r="C33" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>25</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
@@ -1681,8 +1681,8 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="5" t="n">
-        <v>39</v>
+      <c r="C34" s="4" t="n">
+        <v>34</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1732,8 +1732,8 @@
       <c r="F35" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>22</v>
+      <c r="G35" s="10" t="n">
+        <v>29</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
@@ -1751,8 +1751,8 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="10" t="n">
-        <v>26</v>
+      <c r="C36" s="4" t="n">
+        <v>27</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>30</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>26</v>
@@ -1786,8 +1786,8 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="10" t="n">
-        <v>28</v>
+      <c r="C37" s="4" t="n">
+        <v>36</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1802,11 +1802,11 @@
       <c r="F37" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="10" t="n">
-        <v>29</v>
+      <c r="G37" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>29</v>
@@ -1821,8 +1821,8 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="9" t="n">
-        <v>33</v>
+      <c r="C38" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1837,11 +1837,11 @@
       <c r="F38" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>24</v>
+      <c r="G38" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>35</v>
@@ -1857,7 +1857,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1873,10 +1873,10 @@
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>38</v>
@@ -1911,7 +1911,7 @@
         <v>19</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>43</v>
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1942,8 +1942,8 @@
       <c r="F41" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>10</v>
+      <c r="G41" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>69</v>
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>36</v>
+      <c r="C43" s="10" t="n">
+        <v>30</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2012,11 +2012,11 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>22</v>
+      <c r="G43" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>34</v>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
@@ -2101,8 +2101,8 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="4" t="n">
-        <v>48</v>
+      <c r="C46" s="5" t="n">
+        <v>49</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2117,8 +2117,8 @@
       <c r="F46" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G46" s="4" t="n">
-        <v>14</v>
+      <c r="G46" s="5" t="n">
+        <v>13</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
@@ -2137,7 +2137,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>15</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>31</v>
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>27</v>
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2242,7 +2242,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2257,11 +2257,11 @@
       <c r="F50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>17</v>
+      <c r="G50" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>41</v>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>58</v>
@@ -2312,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
@@ -2347,7 +2347,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>11</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>52</v>
@@ -2382,7 +2382,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2397,8 +2397,8 @@
       <c r="F54" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G54" s="4" t="n">
-        <v>10</v>
+      <c r="G54" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>53</v>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>56</v>
@@ -2452,7 +2452,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         <v>10</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>59</v>
@@ -2486,8 +2486,8 @@
       <c r="B57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C57" s="10" t="n">
-        <v>45</v>
+      <c r="C57" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         <v>10</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>45</v>
@@ -2521,8 +2521,8 @@
       <c r="B58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>61</v>
+      <c r="C58" s="7" t="n">
+        <v>70</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2537,8 +2537,8 @@
       <c r="F58" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>8</v>
+      <c r="G58" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>55</v>
@@ -2556,8 +2556,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="4" t="n">
-        <v>62</v>
+      <c r="C59" s="7" t="n">
+        <v>71</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,10 +2573,10 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>62</v>
@@ -2592,7 +2592,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>60</v>
@@ -2646,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>57</v>
@@ -2662,7 +2662,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2696,8 +2696,8 @@
       <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C63" s="9" t="n">
-        <v>55</v>
+      <c r="C63" s="10" t="n">
+        <v>56</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>71</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>108</v>
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>109</v>
@@ -2872,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         <v>7</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>65</v>
@@ -2907,7 +2907,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>75</v>
@@ -2942,7 +2942,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>84</v>
@@ -2977,7 +2977,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>76</v>
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>78</v>
@@ -3066,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>81</v>
@@ -3082,7 +3082,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>79</v>
@@ -3116,8 +3116,8 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="9" t="n">
-        <v>59</v>
+      <c r="C75" s="10" t="n">
+        <v>62</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>60</v>
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>11</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>53</v>
@@ -3221,8 +3221,8 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="4" t="n">
-        <v>66</v>
+      <c r="C78" s="10" t="n">
+        <v>54</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         <v>5</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>66</v>
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>85</v>
@@ -3292,7 +3292,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>100</v>
@@ -3327,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>99</v>
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>73</v>
@@ -3396,8 +3396,8 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="4" t="n">
-        <v>94</v>
+      <c r="C83" s="7" t="n">
+        <v>103</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3413,10 +3413,10 @@
         <v>4</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>97</v>
@@ -3432,7 +3432,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>4</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3466,8 +3466,8 @@
       <c r="B85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="4" t="n">
-        <v>95</v>
+      <c r="C85" s="7" t="n">
+        <v>102</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>4</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>82</v>
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>106</v>
@@ -3536,8 +3536,8 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="4" t="n">
-        <v>97</v>
+      <c r="C87" s="7" t="n">
+        <v>107</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>98</v>
@@ -3572,7 +3572,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3607,7 +3607,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>149</v>
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>136</v>
@@ -3677,7 +3677,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>87</v>
@@ -3712,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>85</v>
@@ -3747,7 +3747,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>89</v>
@@ -3781,8 +3781,8 @@
       <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="10" t="n">
-        <v>77</v>
+      <c r="C94" s="4" t="n">
+        <v>82</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>77</v>
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>118</v>
@@ -3852,7 +3852,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3887,7 +3887,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>70</v>
@@ -3922,7 +3922,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>111</v>
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>137</v>
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>86</v>
@@ -4027,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>138</v>
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>130</v>
@@ -4097,7 +4097,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>80</v>
@@ -4132,7 +4132,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
         <v>2</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>121</v>
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>131</v>
@@ -4202,7 +4202,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>87</v>
@@ -4236,8 +4236,8 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="9" t="n">
-        <v>93</v>
+      <c r="C107" s="10" t="n">
+        <v>96</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -4253,10 +4253,10 @@
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>93</v>
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>82</v>
@@ -4307,7 +4307,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>103</v>
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>152</v>
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>122</v>
@@ -4412,7 +4412,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>217</v>
@@ -4447,7 +4447,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>102</v>
@@ -4536,7 +4536,7 @@
         <v>4</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>90</v>
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>95</v>
@@ -4587,7 +4587,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>260</v>
@@ -4622,7 +4622,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         <v>2</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>129</v>
@@ -4657,7 +4657,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="10" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>116</v>
@@ -4691,8 +4691,8 @@
       <c r="B120" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C120" s="7" t="n">
-        <v>186</v>
+      <c r="C120" s="4" t="n">
+        <v>144</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -4708,10 +4708,10 @@
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>183</v>
@@ -4726,8 +4726,8 @@
       <c r="B121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="4" t="n">
-        <v>123</v>
+      <c r="C121" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>88</v>
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>94</v>
@@ -4797,7 +4797,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>147</v>
@@ -4831,8 +4831,8 @@
       <c r="B124" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="C124" s="7" t="n">
-        <v>238</v>
+      <c r="C124" s="4" t="n">
+        <v>174</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>190</v>
@@ -4866,8 +4866,8 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="10" t="n">
-        <v>88</v>
+      <c r="C125" s="9" t="n">
+        <v>77</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>83</v>
@@ -4902,7 +4902,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>125</v>
@@ -4936,8 +4936,8 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="7" t="n">
-        <v>156</v>
+      <c r="C127" s="5" t="n">
+        <v>135</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>150</v>
@@ -4971,8 +4971,8 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="4" t="n">
-        <v>105</v>
+      <c r="C128" s="10" t="n">
+        <v>93</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>101</v>
@@ -5006,8 +5006,8 @@
       <c r="B129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="5" t="n">
-        <v>135</v>
+      <c r="C129" s="4" t="n">
+        <v>134</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>135</v>
@@ -5042,7 +5042,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>124</v>
@@ -5077,7 +5077,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>110</v>
@@ -5112,7 +5112,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="7" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>198</v>
@@ -5147,7 +5147,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>134</v>
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         <v>1</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>120</v>
@@ -5217,7 +5217,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>166</v>
@@ -5251,8 +5251,8 @@
       <c r="B136" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C136" s="4" t="n">
-        <v>115</v>
+      <c r="C136" s="10" t="n">
+        <v>110</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>114</v>
@@ -5287,7 +5287,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>178</v>
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>104</v>
@@ -5357,7 +5357,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>186</v>
@@ -5392,7 +5392,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>171</v>
@@ -5427,7 +5427,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="9" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>112</v>
@@ -5462,7 +5462,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>170</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>156</v>
@@ -5531,8 +5531,8 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="5" t="n">
-        <v>155</v>
+      <c r="C144" s="7" t="n">
+        <v>172</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         <v>1</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>158</v>
@@ -5567,7 +5567,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>216</v>
@@ -5601,8 +5601,8 @@
       <c r="B146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="7" t="n">
-        <v>225</v>
+      <c r="C146" s="4" t="n">
+        <v>146</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
@@ -5618,10 +5618,10 @@
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>181</v>
@@ -5637,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>151</v>
@@ -5672,7 +5672,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>197</v>
@@ -5707,7 +5707,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>126</v>
@@ -5741,8 +5741,8 @@
       <c r="B150" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C150" s="9" t="n">
-        <v>118</v>
+      <c r="C150" s="10" t="n">
+        <v>124</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>119</v>
@@ -5777,7 +5777,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>133</v>
@@ -5812,7 +5812,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>223</v>
@@ -5847,7 +5847,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>268</v>
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>213</v>
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>192</v>
@@ -5951,8 +5951,8 @@
       <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C156" s="4" t="n">
-        <v>153</v>
+      <c r="C156" s="10" t="n">
+        <v>148</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>155</v>
@@ -5987,7 +5987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>209</v>
@@ -6022,7 +6022,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>169</v>
@@ -6057,7 +6057,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>194</v>
@@ -6091,8 +6091,8 @@
       <c r="B160" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="C160" s="5" t="n">
-        <v>232</v>
+      <c r="C160" s="4" t="n">
+        <v>230</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>235</v>
@@ -6126,8 +6126,8 @@
       <c r="B161" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C161" s="4" t="n">
-        <v>173</v>
+      <c r="C161" s="10" t="n">
+        <v>156</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
         <v>1</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>172</v>
@@ -6162,7 +6162,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>157</v>
@@ -6197,7 +6197,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>199</v>
@@ -6232,7 +6232,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>215</v>
@@ -6267,7 +6267,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>200</v>
@@ -6302,7 +6302,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>262</v>
@@ -6336,8 +6336,8 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="4" t="n">
-        <v>171</v>
+      <c r="C167" s="5" t="n">
+        <v>210</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>195</v>
@@ -6372,7 +6372,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>225</v>
@@ -6407,7 +6407,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="9" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>123</v>
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>107</v>
@@ -6477,7 +6477,7 @@
         <v>182</v>
       </c>
       <c r="C171" s="9" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>140</v>
@@ -6511,8 +6511,8 @@
       <c r="B172" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="C172" s="10" t="n">
-        <v>150</v>
+      <c r="C172" s="4" t="n">
+        <v>161</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6528,10 +6528,10 @@
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>153</v>
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>164</v>
@@ -6581,8 +6581,8 @@
       <c r="B174" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="C174" s="9" t="n">
-        <v>139</v>
+      <c r="C174" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>141</v>
@@ -6617,7 +6617,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>163</v>
@@ -6652,7 +6652,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>202</v>
@@ -6687,7 +6687,7 @@
         <v>188</v>
       </c>
       <c r="C177" s="9" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>139</v>
@@ -6722,7 +6722,7 @@
         <v>189</v>
       </c>
       <c r="C178" s="9" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>145</v>
@@ -6756,8 +6756,8 @@
       <c r="B179" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="C179" s="10" t="n">
-        <v>161</v>
+      <c r="C179" s="4" t="n">
+        <v>163</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>162</v>
@@ -6792,7 +6792,7 @@
         <v>191</v>
       </c>
       <c r="C180" s="10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -6808,10 +6808,10 @@
         <v>0</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>161</v>
@@ -6826,8 +6826,8 @@
       <c r="B181" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C181" s="5" t="n">
-        <v>221</v>
+      <c r="C181" s="4" t="n">
+        <v>186</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>228</v>
@@ -6862,7 +6862,7 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>253</v>
@@ -6897,7 +6897,7 @@
         <v>194</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>185</v>
@@ -6932,7 +6932,7 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>243</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>239</v>
@@ -7002,26 +7002,26 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Zachariah Branch</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3" t="n">
         <v>256</v>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>Zachariah Branch</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" s="3" t="n">
-        <v>165</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>250</v>
@@ -7037,7 +7037,7 @@
         <v>198</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>115</v>
@@ -7072,7 +7072,7 @@
         <v>199</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>206</v>
@@ -7106,8 +7106,8 @@
       <c r="B189" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C189" s="10" t="n">
-        <v>164</v>
+      <c r="C189" s="4" t="n">
+        <v>192</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>165</v>
@@ -7142,7 +7142,7 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>274</v>
@@ -7176,8 +7176,8 @@
       <c r="B191" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C191" s="10" t="n">
-        <v>134</v>
+      <c r="C191" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
@@ -7186,17 +7186,17 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>92</v>
@@ -7211,8 +7211,8 @@
       <c r="B192" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C192" s="4" t="n">
-        <v>191</v>
+      <c r="C192" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>180</v>
@@ -7247,7 +7247,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>275</v>
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>272</v>
@@ -7317,7 +7317,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>219</v>
@@ -7349,19 +7349,19 @@
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>244</v>
+        <v>306</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -7371,11 +7371,9 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I196" s="3" t="n">
-        <v>244</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -7384,19 +7382,19 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="C197" s="4" t="n">
         <v>209</v>
       </c>
+      <c r="C197" s="5" t="n">
+        <v>266</v>
+      </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7406,10 +7404,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198">
@@ -7419,67 +7417,67 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Isaac TeSlaa</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C198" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
+      <c r="C199" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Chris Bell</t>
         </is>
       </c>
-      <c r="E198" s="3" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="F198" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="I198" s="3" t="n">
+      <c r="F199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I199" s="3" t="n">
         <v>269</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="C199" s="4" t="n">
-        <v>228</v>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Jonah Coleman</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="I199" s="3" t="n">
-        <v>210</v>
       </c>
     </row>
     <row r="200">
@@ -7489,19 +7487,19 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -7511,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="201">
@@ -7524,67 +7522,67 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C201" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Kaelon Black</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="C201" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="C202" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Kaytron Allen</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="F201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="I201" s="3" t="n">
+      <c r="F202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="I202" s="3" t="n">
         <v>224</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="C202" s="4" t="n">
-        <v>233</v>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Gunnar Helm</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" s="3" t="n">
-        <v>209</v>
-      </c>
-      <c r="I202" s="3" t="n">
-        <v>236</v>
       </c>
     </row>
     <row r="203">
@@ -7594,19 +7592,19 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="C203" s="10" t="n">
-        <v>172</v>
+        <v>215</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>229</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Gunnar Helm</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
@@ -7616,10 +7614,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>173</v>
+        <v>236</v>
       </c>
     </row>
     <row r="204">
@@ -7629,67 +7627,67 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="C204" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Chig Okonkwo</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C204" s="10" t="n">
-        <v>179</v>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="C205" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>AJ Barner</t>
         </is>
       </c>
-      <c r="E204" s="3" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F204" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" s="3" t="n">
-        <v>214</v>
-      </c>
-      <c r="I204" s="3" t="n">
+      <c r="F205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I205" s="3" t="n">
         <v>184</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="C205" s="10" t="n">
-        <v>166</v>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>Sam Darnold</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="I205" s="3" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="206">
@@ -7699,19 +7697,19 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C206" s="10" t="n">
-        <v>177</v>
+        <v>218</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>194</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7721,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="207">
@@ -7734,67 +7732,67 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Young</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="C207" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="C208" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>Fernando Mendoza</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="F207" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="I207" s="3" t="n">
+      <c r="F208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="I208" s="3" t="n">
         <v>208</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C208" s="5" t="n">
-        <v>272</v>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Nicholas Singleton</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="I208" s="3" t="n">
-        <v>279</v>
       </c>
     </row>
     <row r="209">
@@ -7804,32 +7802,32 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Nicholas Singleton</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="I209" s="3" t="n">
         <v>279</v>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Demond Claiborne</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="I209" s="3" t="n">
-        <v>287</v>
       </c>
     </row>
     <row r="210">
@@ -7839,102 +7837,102 @@
         </is>
       </c>
       <c r="B210" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Demond Claiborne</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C210" s="5" t="n">
-        <v>263</v>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
+      <c r="C211" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>Kimani Vidal</t>
         </is>
       </c>
-      <c r="E210" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="F210" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="I210" s="3" t="n">
+      <c r="F211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="I211" s="3" t="n">
         <v>252</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="6" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="B211" s="3" t="n">
+      <c r="B212" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C211" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="C212" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>Malik Washington</t>
         </is>
       </c>
-      <c r="E211" s="3" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="F211" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" s="3" t="n">
-        <v>247</v>
-      </c>
-      <c r="I211" s="3" t="n">
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="I212" s="3" t="n">
         <v>196</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C212" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Jaylen Wright</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="I212" s="3" t="n">
-        <v>280</v>
       </c>
     </row>
     <row r="213">
@@ -7944,67 +7942,67 @@
         </is>
       </c>
       <c r="B213" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C213" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="C214" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>Ollie Gordon</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="F213" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="I213" s="3" t="n">
+      <c r="F214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="I214" s="3" t="n">
         <v>281</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="C214" s="5" t="n">
-        <v>269</v>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Tolbert</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H214" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="I214" s="3" t="n">
-        <v>278</v>
       </c>
     </row>
     <row r="215">
@@ -8014,19 +8012,19 @@
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C215" s="4" t="n">
-        <v>234</v>
+        <v>227</v>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>291</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -8036,10 +8034,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
     </row>
     <row r="216">
@@ -8049,19 +8047,19 @@
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C216" s="4" t="n">
-        <v>235</v>
+        <v>228</v>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>265</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -8071,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="217">
@@ -8084,19 +8082,19 @@
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F217" s="3" t="n">
@@ -8106,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>248</v>
+        <v>222</v>
       </c>
     </row>
     <row r="218">
@@ -8119,19 +8117,19 @@
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8141,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="219">
@@ -8154,19 +8152,19 @@
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C219" s="5" t="n">
-        <v>276</v>
+        <v>231</v>
+      </c>
+      <c r="C219" s="4" t="n">
+        <v>262</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8176,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>283</v>
+        <v>248</v>
       </c>
     </row>
     <row r="220">
@@ -8189,172 +8187,172 @@
         </is>
       </c>
       <c r="B220" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="C220" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hurst</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C220" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
+      <c r="C222" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>Keon Coleman</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>BUF</t>
         </is>
       </c>
-      <c r="F220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="I220" s="3" t="n">
+      <c r="F222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="I222" s="3" t="n">
         <v>288</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="12" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B221" s="3" t="n">
+      <c r="B223" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C221" s="10" t="n">
-        <v>194</v>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
+      <c r="C223" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>Chris Boswell</t>
         </is>
       </c>
-      <c r="E221" s="3" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="F221" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I221" s="3" t="n">
+      <c r="F223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="I223" s="3" t="n">
         <v>201</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="12" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B222" s="3" t="n">
+      <c r="B224" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="C222" s="10" t="n">
+      <c r="C224" s="10" t="n">
         <v>183</v>
       </c>
-      <c r="D222" s="3" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>Chase McLaughlin</t>
         </is>
       </c>
-      <c r="E222" s="3" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="F222" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H222" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="I222" s="3" t="n">
+      <c r="F224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="I224" s="3" t="n">
         <v>187</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C223" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>Samaje Perine</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="I223" s="3" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C224" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>LeQuint Allen</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="I224" s="3" t="n">
-        <v>286</v>
       </c>
     </row>
     <row r="225">
@@ -8364,19 +8362,19 @@
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>202</v>
+        <v>239</v>
+      </c>
+      <c r="C225" s="5" t="n">
+        <v>297</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -8386,11 +8384,9 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="I225" s="3" t="n">
-        <v>168</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8399,19 +8395,19 @@
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>250</v>
+        <v>240</v>
+      </c>
+      <c r="C226" s="5" t="n">
+        <v>326</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -8421,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>193</v>
+        <v>285</v>
       </c>
     </row>
     <row r="227">
@@ -8434,19 +8430,19 @@
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -8456,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="228">
@@ -8469,19 +8465,19 @@
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="C228" s="4" t="n">
-        <v>261</v>
+        <v>242</v>
+      </c>
+      <c r="C228" s="10" t="n">
+        <v>166</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -8491,10 +8487,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="229">
@@ -8504,19 +8500,19 @@
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -8526,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>289</v>
+        <v>193</v>
       </c>
     </row>
     <row r="230">
@@ -8539,19 +8535,19 @@
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="C230" s="4" t="n">
-        <v>262</v>
+        <v>244</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>289</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -8561,10 +8557,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="231">
@@ -8574,19 +8570,19 @@
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="C231" s="4" t="n">
-        <v>283</v>
+        <v>245</v>
+      </c>
+      <c r="C231" s="5" t="n">
+        <v>293</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Chris Brooks</t>
+          <t>Ty Johnson</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -8596,11 +8592,9 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="I231" s="3" t="n">
-        <v>290</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="I231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8609,19 +8603,19 @@
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -8631,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>191</v>
+        <v>266</v>
       </c>
     </row>
     <row r="233">
@@ -8644,207 +8638,207 @@
         </is>
       </c>
       <c r="B233" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="C233" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Isaiah Davis</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Emmett Johnson</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I234" s="3" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C236" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Sean Tucker</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="I236" s="3" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C233" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
+      <c r="C237" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens</t>
         </is>
       </c>
-      <c r="E233" s="3" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="F233" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H233" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="I233" s="3" t="n">
+      <c r="F237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="I237" s="3" t="n">
         <v>273</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="6" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="B234" s="3" t="n">
+      <c r="B238" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C234" s="4" t="n">
-        <v>243</v>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
+      <c r="C238" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
         <is>
           <t>Dontayvion Wicks</t>
         </is>
       </c>
-      <c r="E234" s="3" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="F234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H234" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="I234" s="3" t="n">
+      <c r="F238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="I238" s="3" t="n">
         <v>179</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="C235" s="10" t="n">
-        <v>144</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Evan McPherson</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>224</v>
-      </c>
-      <c r="I235" s="3" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C236" s="10" t="n">
-        <v>187</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>Oronde Gadsden</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H236" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="I236" s="3" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C237" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>Greg Dulcich</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H237" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="I237" s="3" t="n">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C238" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H238" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="I238" s="3" t="n">
-        <v>227</v>
       </c>
     </row>
     <row r="239">
@@ -8854,277 +8848,273 @@
         </is>
       </c>
       <c r="B239" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="C239" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Savion Williams</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="I239" s="3" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="C240" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Evan McPherson</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Nick Folk</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="I241" s="3" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Oronde Gadsden</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C243" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Greg Dulcich</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="C244" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="I244" s="3" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C239" s="4" t="n">
+      <c r="C245" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Pat Bryant</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="I245" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="6" t="inlineStr">
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="B240" s="3" t="n">
+      <c r="B246" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C240" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
+      <c r="C246" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>Tory Horton</t>
         </is>
       </c>
-      <c r="E240" s="3" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F240" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="I240" s="3" t="n">
+      <c r="F246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="I246" s="3" t="n">
         <v>291</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C241" s="4" t="n">
-        <v>246</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Sarratt</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I241" s="3" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C242" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>Emanuel Wilson</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="I242" s="3" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C243" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="I243" s="3" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="I244" s="3" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="C245" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>Jacoby Brissett</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H245" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="I245" s="3" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="C246" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>242</v>
       </c>
     </row>
     <row r="247">
@@ -9134,346 +9124,919 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C248" s="5" t="n">
+        <v>343</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Malik Davis</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="I248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Emanuel Wilson</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Geno Smith</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>NYJ</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="I250" s="3" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Rodgers</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="C247" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
+      <c r="C254" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
         <is>
           <t>Darius Slayton</t>
         </is>
       </c>
-      <c r="E247" s="3" t="inlineStr">
+      <c r="E254" s="3" t="inlineStr">
         <is>
           <t>NYG</t>
         </is>
       </c>
-      <c r="F247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="3" t="n">
+      <c r="F254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="C255" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Treylon Burks</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C258" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Jahan Dotson</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="I258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C259" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>Devin Singletary</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="I259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="C260" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>Tahj Brooks</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="I260" s="3" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="C261" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>Trevor Etienne</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="I261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C262" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>Seth McGowan</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="I262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Kendre Miller</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="I263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Jawhar Jordan</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="C265" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Marvin Mims</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Trey Smack</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="C267" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Jake Elliott</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="C268" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C269" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Evan Engram</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="I269" s="3" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C270" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>David Njoku</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="I270" s="3" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Michael Mayer</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Jake Tonges</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I272" s="3" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="I247" s="3" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C248" s="4" t="n">
-        <v>293</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>Treylon Burks</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="I248" s="3" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C249" s="4" t="n">
-        <v>248</v>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>Tyquan Thornton</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I249" s="3" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="C250" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="I250" s="3" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="C251" s="4" t="n">
-        <v>284</v>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>Marvin Mims</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="I251" s="3" t="n">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>Jake Elliott</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F253" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I253" s="3" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="C255" s="4" t="n">
-        <v>267</v>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>David Njoku</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="F255" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="I256" s="3" t="n">
+      <c r="I273" s="3" t="n">
         <v>241</v>
       </c>
     </row>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -616,7 +616,7 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2</v>
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -1351,7 +1351,7 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>36</v>
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>18</v>
@@ -1771,7 +1771,7 @@
         <v>30</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>26</v>
@@ -1806,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>29</v>
@@ -1876,7 +1876,7 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>38</v>
@@ -1911,7 +1911,7 @@
         <v>19</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>43</v>
@@ -2156,7 +2156,7 @@
         <v>26</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>31</v>
@@ -2191,7 +2191,7 @@
         <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>27</v>
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>41</v>
@@ -2296,7 +2296,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>58</v>
@@ -2366,7 +2366,7 @@
         <v>12</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>50</v>
@@ -2401,7 +2401,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>51</v>
@@ -2436,7 +2436,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>52</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>59</v>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>45</v>
@@ -2541,7 +2541,7 @@
         <v>6</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>61</v>
@@ -2576,7 +2576,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>62</v>
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>72</v>
@@ -2646,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>57</v>
@@ -2681,7 +2681,7 @@
         <v>13</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>49</v>
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>63</v>
@@ -2786,7 +2786,7 @@
         <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>71</v>
@@ -2821,7 +2821,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>108</v>
@@ -2856,7 +2856,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>109</v>
@@ -2926,7 +2926,7 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>75</v>
@@ -2961,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>84</v>
@@ -2996,7 +2996,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>76</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>78</v>
@@ -3066,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>81</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>79</v>
@@ -3136,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>60</v>
@@ -3171,7 +3171,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>105</v>
@@ -3241,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>66</v>
@@ -3276,7 +3276,7 @@
         <v>14</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>47</v>
@@ -3311,7 +3311,7 @@
         <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>100</v>
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>97</v>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>96</v>
@@ -3556,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>98</v>
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>149</v>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>136</v>
@@ -3696,7 +3696,7 @@
         <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>91</v>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>85</v>
@@ -3836,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>118</v>
@@ -3871,7 +3871,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3906,7 +3906,7 @@
         <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>70</v>
@@ -3941,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>111</v>
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>137</v>
@@ -4011,7 +4011,7 @@
         <v>3</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>86</v>
@@ -4046,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>138</v>
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>130</v>
@@ -4116,7 +4116,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>80</v>
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>121</v>
@@ -4186,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>131</v>
@@ -4221,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>87</v>
@@ -4256,7 +4256,7 @@
         <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>93</v>
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>82</v>
@@ -4326,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>103</v>
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>152</v>
@@ -4396,7 +4396,7 @@
         <v>2</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>122</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>217</v>
@@ -4466,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>148</v>
@@ -4501,7 +4501,7 @@
         <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>102</v>
@@ -4536,7 +4536,7 @@
         <v>4</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>90</v>
@@ -4571,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>95</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>260</v>
@@ -4641,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>129</v>
@@ -4676,7 +4676,7 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>116</v>
@@ -4711,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>183</v>
@@ -4746,7 +4746,7 @@
         <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>88</v>
@@ -4781,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>94</v>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>147</v>
@@ -4886,7 +4886,7 @@
         <v>5</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>83</v>
@@ -4921,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>125</v>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>150</v>
@@ -4971,30 +4971,30 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="10" t="n">
-        <v>93</v>
+      <c r="C128" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129">
@@ -5006,30 +5006,30 @@
       <c r="B129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="4" t="n">
-        <v>134</v>
+      <c r="C129" s="10" t="n">
+        <v>93</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="130">
@@ -5042,16 +5042,16 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -5061,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131">
@@ -5077,29 +5077,29 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132">
@@ -5111,30 +5111,30 @@
       <c r="B132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="7" t="n">
-        <v>191</v>
+      <c r="C132" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>198</v>
+        <v>110</v>
       </c>
     </row>
     <row r="133">
@@ -5146,30 +5146,30 @@
       <c r="B133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C133" s="4" t="n">
-        <v>131</v>
+      <c r="C133" s="7" t="n">
+        <v>191</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>134</v>
+        <v>198</v>
       </c>
     </row>
     <row r="134">
@@ -5201,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>120</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>166</v>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>114</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>178</v>
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>104</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>186</v>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>171</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>170</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>156</v>
@@ -5531,30 +5531,30 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="7" t="n">
-        <v>172</v>
+      <c r="C144" s="4" t="n">
+        <v>131</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145">
@@ -5567,16 +5567,16 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -5589,7 +5589,7 @@
         <v>155</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>216</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146">
@@ -5601,30 +5601,30 @@
       <c r="B146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="4" t="n">
-        <v>146</v>
+      <c r="C146" s="7" t="n">
+        <v>231</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>181</v>
+        <v>216</v>
       </c>
     </row>
     <row r="147">
@@ -5636,17 +5636,17 @@
       <c r="B147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="5" t="n">
-        <v>158</v>
+      <c r="C147" s="4" t="n">
+        <v>146</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -5656,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>151</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148">
@@ -5671,30 +5671,30 @@
       <c r="B148" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C148" s="7" t="n">
-        <v>190</v>
+      <c r="C148" s="5" t="n">
+        <v>158</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149">
@@ -5706,30 +5706,30 @@
       <c r="B149" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C149" s="4" t="n">
-        <v>129</v>
+      <c r="C149" s="7" t="n">
+        <v>190</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="150">
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>119</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>133</v>
@@ -5811,30 +5811,30 @@
       <c r="B152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="5" t="n">
-        <v>255</v>
+      <c r="C152" s="4" t="n">
+        <v>129</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>223</v>
+        <v>126</v>
       </c>
     </row>
     <row r="153">
@@ -5847,16 +5847,16 @@
         <v>152</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>268</v>
+        <v>223</v>
       </c>
     </row>
     <row r="154">
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>213</v>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>192</v>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>155</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>209</v>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>169</v>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>194</v>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>235</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>172</v>
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>157</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>199</v>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>215</v>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>200</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>262</v>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>195</v>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>225</v>
@@ -6426,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>123</v>
@@ -6461,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>107</v>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>140</v>
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>153</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>164</v>
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>141</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>163</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>202</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>139</v>
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>145</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>162</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>161</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>228</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>253</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>185</v>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>243</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>239</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>250</v>
@@ -7056,7 +7056,7 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>115</v>
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>206</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>165</v>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>274</v>
@@ -7174,32 +7174,32 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C191" s="9" t="n">
-        <v>84</v>
+        <v>203</v>
+      </c>
+      <c r="C191" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="192">
@@ -7211,17 +7211,17 @@
       <c r="B192" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C192" s="10" t="n">
-        <v>171</v>
+      <c r="C192" s="5" t="n">
+        <v>268</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>180</v>
+        <v>268</v>
       </c>
     </row>
     <row r="193">
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>183</v>
+        <v>269</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>275</v>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>272</v>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>219</v>
@@ -7371,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="I196" s="3" t="inlineStr"/>
     </row>
@@ -7404,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="I197" s="3" t="n">
         <v>244</v>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>214</v>
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="I199" s="3" t="n">
         <v>269</v>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>210</v>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>211</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>224</v>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>236</v>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>173</v>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>184</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>167</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>177</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>208</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>279</v>
@@ -7840,7 +7840,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="I211" s="3" t="n">
         <v>252</v>
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>196</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>179</v>
+        <v>271</v>
       </c>
       <c r="I213" s="3" t="n">
         <v>280</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>281</v>
@@ -8034,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>175</v>
+        <v>265</v>
       </c>
       <c r="I215" s="3" t="n">
         <v>278</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="I216" s="3" t="n">
         <v>237</v>
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="I217" s="3" t="n">
         <v>222</v>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>238</v>
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>248</v>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>246</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>261</v>
+        <v>165</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>283</v>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>288</v>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I223" s="3" t="n">
         <v>201</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>187</v>
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>257</v>
+        <v>163</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>285</v>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>286</v>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>168</v>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I229" s="3" t="n">
         <v>193</v>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="I230" s="3" t="n">
         <v>276</v>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>182</v>
+        <v>267</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="I232" s="3" t="n">
         <v>266</v>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>265</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>260</v>
+        <v>162</v>
       </c>
       <c r="I235" s="3" t="n">
         <v>290</v>
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>191</v>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="I237" s="3" t="n">
         <v>273</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>179</v>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>271</v>
+        <v>174</v>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
@@ -8903,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="I240" s="3" t="n">
         <v>146</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="I242" s="3" t="n">
         <v>220</v>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="I243" s="3" t="n">
         <v>218</v>
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>227</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="I245" s="3" t="n">
         <v>245</v>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>291</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="I247" s="3" t="n">
         <v>249</v>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>269</v>
+        <v>176</v>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="I249" s="3" t="n">
         <v>277</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>207</v>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="I251" s="3" t="n">
         <v>221</v>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="I252" s="3" t="n">
         <v>240</v>
@@ -9354,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="I253" s="3" t="n">
         <v>242</v>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I254" s="3" t="n">
         <v>212</v>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="I255" s="3" t="n">
         <v>293</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="I256" s="3" t="n">
         <v>264</v>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="I257" s="3" t="n">
         <v>263</v>
@@ -9510,7 +9510,7 @@
         <v>275</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9576,7 +9576,7 @@
         <v>279</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>259</v>
+        <v>161</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9661,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I265" s="3" t="n">
         <v>292</v>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="I266" s="3" t="inlineStr"/>
     </row>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="I267" s="3" t="n">
         <v>229</v>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>261</v>
@@ -9898,7 +9898,7 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="I269" s="3" t="n">
         <v>257</v>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>256</v>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="I271" s="3" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
@@ -10034,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="I273" s="3" t="n">
         <v>241</v>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -911,8 +911,8 @@
       <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>15</v>
+      <c r="C12" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         <v>48</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -962,8 +962,8 @@
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>45</v>
+      <c r="G13" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
@@ -982,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1074,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1138,13 +1138,13 @@
         <v>38</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1157,7 +1157,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1332,7 +1332,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>36</v>
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>18</v>
@@ -1402,7 +1402,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1417,14 +1417,14 @@
       <c r="F26" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>34</v>
+      <c r="G26" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1452,14 +1452,14 @@
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>25</v>
+      <c r="G27" s="5" t="n">
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -1472,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         <v>30</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1506,8 +1506,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>33</v>
+      <c r="C29" s="7" t="n">
+        <v>44</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>24</v>
+      <c r="G29" s="7" t="n">
+        <v>17</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1542,7 +1542,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -1577,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
@@ -1647,7 +1647,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>25</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,13 +1698,13 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         <v>23</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -1752,7 +1752,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1768,13 +1768,13 @@
         <v>22</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
@@ -1787,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -1822,7 +1822,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         <v>22</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>37</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -1857,7 +1857,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1873,13 +1873,13 @@
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
@@ -1914,7 +1914,7 @@
         <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1942,14 +1942,14 @@
       <c r="F41" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="7" t="n">
-        <v>9</v>
+      <c r="G41" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
@@ -1961,8 +1961,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>68</v>
+      <c r="C42" s="4" t="n">
+        <v>62</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1978,13 +1978,13 @@
         <v>19</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43">
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="10" t="n">
-        <v>30</v>
+      <c r="C43" s="4" t="n">
+        <v>32</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>41</v>
@@ -2031,8 +2031,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="5" t="n">
-        <v>53</v>
+      <c r="C44" s="7" t="n">
+        <v>59</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2082,14 +2082,14 @@
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>17</v>
+      <c r="G45" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47">
@@ -2159,7 +2159,7 @@
         <v>46</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>47</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>41</v>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2292,14 +2292,14 @@
       <c r="F51" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G51" s="5" t="n">
-        <v>9</v>
+      <c r="G51" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52">
@@ -2312,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
@@ -2347,7 +2347,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         <v>11</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -2382,7 +2382,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2397,14 +2397,14 @@
       <c r="F54" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G54" s="10" t="n">
-        <v>15</v>
+      <c r="G54" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55">
@@ -2436,7 +2436,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>52</v>
@@ -2451,8 +2451,8 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="4" t="n">
-        <v>61</v>
+      <c r="C56" s="7" t="n">
+        <v>68</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="F56" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>8</v>
+      <c r="G56" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -2487,7 +2487,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>45</v>
@@ -2521,8 +2521,8 @@
       <c r="B58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>70</v>
+      <c r="C58" s="4" t="n">
+        <v>61</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2537,14 +2537,14 @@
       <c r="F58" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>6</v>
+      <c r="G58" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -2556,8 +2556,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="7" t="n">
-        <v>71</v>
+      <c r="C59" s="5" t="n">
+        <v>69</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>62</v>
@@ -2592,7 +2592,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>58</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
@@ -2627,7 +2627,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
@@ -2661,8 +2661,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>50</v>
+      <c r="C62" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>62</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -2732,7 +2732,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         <v>7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>71</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>7</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>65</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68">
@@ -2871,8 +2871,8 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="4" t="n">
-        <v>63</v>
+      <c r="C68" s="7" t="n">
+        <v>93</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>8</v>
+      <c r="G68" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -2907,7 +2907,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70">
@@ -2942,7 +2942,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2958,10 +2958,10 @@
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>84</v>
@@ -2976,8 +2976,8 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="5" t="n">
-        <v>74</v>
+      <c r="C71" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2993,13 +2993,13 @@
         <v>6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72">
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73">
@@ -3047,7 +3047,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -3082,7 +3082,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3098,13 +3098,13 @@
         <v>6</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75">
@@ -3117,7 +3117,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3133,13 +3133,13 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76">
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77">
@@ -3187,7 +3187,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>53</v>
@@ -3221,8 +3221,8 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="10" t="n">
-        <v>54</v>
+      <c r="C78" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -3237,14 +3237,14 @@
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>10</v>
+      <c r="G78" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3273,10 +3273,10 @@
         <v>4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>47</v>
@@ -3291,8 +3291,8 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="7" t="n">
-        <v>94</v>
+      <c r="C80" s="4" t="n">
+        <v>78</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
@@ -3327,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3343,13 +3343,13 @@
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82">
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3378,13 +3378,13 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
@@ -3397,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>82</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84">
@@ -3432,7 +3432,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3467,7 +3467,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86">
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87">
@@ -3537,7 +3537,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88">
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3629,7 +3629,7 @@
         <v>95</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>94</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="91">
@@ -3677,7 +3677,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>91</v>
@@ -3712,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -3747,7 +3747,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>91</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -3782,7 +3782,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95">
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3833,13 +3833,13 @@
         <v>3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96">
@@ -3852,7 +3852,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3887,7 +3887,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98">
@@ -3922,7 +3922,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99">
@@ -3979,7 +3979,7 @@
         <v>118</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100">
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>86</v>
@@ -4049,7 +4049,7 @@
         <v>116</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102">
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4078,13 +4078,13 @@
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103">
@@ -4097,7 +4097,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104">
@@ -4132,7 +4132,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105">
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,10 +4186,10 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106">
@@ -4202,7 +4202,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -4221,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107">
@@ -4256,10 +4256,10 @@
         <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="108">
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109">
@@ -4306,8 +4306,8 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="9" t="n">
-        <v>97</v>
+      <c r="C109" s="10" t="n">
+        <v>99</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110">
@@ -4364,7 +4364,7 @@
         <v>115</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111">
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4393,13 +4393,13 @@
         <v>2</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112">
@@ -4434,7 +4434,7 @@
         <v>113</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113">
@@ -4447,7 +4447,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>117</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114">
@@ -4482,7 +4482,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4498,13 +4498,13 @@
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115">
@@ -4517,7 +4517,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4533,13 +4533,13 @@
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116">
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
@@ -4587,7 +4587,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -4621,8 +4621,8 @@
       <c r="B118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C118" s="4" t="n">
-        <v>118</v>
+      <c r="C118" s="10" t="n">
+        <v>108</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119">
@@ -4656,8 +4656,8 @@
       <c r="B119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="10" t="n">
-        <v>111</v>
+      <c r="C119" s="9" t="n">
+        <v>102</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>109</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120">
@@ -4714,7 +4714,7 @@
         <v>114</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="121">
@@ -4727,7 +4727,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>88</v>
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="123">
@@ -4819,7 +4819,7 @@
         <v>135</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="124">
@@ -4832,7 +4832,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125">
@@ -4867,7 +4867,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="9" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>83</v>
@@ -4902,7 +4902,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4918,13 +4918,13 @@
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127">
@@ -4936,8 +4936,8 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="5" t="n">
-        <v>135</v>
+      <c r="C127" s="7" t="n">
+        <v>158</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="128">
@@ -4972,7 +4972,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>4</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>92</v>
@@ -5007,7 +5007,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="10" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5026,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130">
@@ -5042,7 +5042,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -5058,13 +5058,13 @@
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="131">
@@ -5077,7 +5077,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
         <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132">
@@ -5112,7 +5112,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
         <v>2</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133">
@@ -5147,7 +5147,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="134">
@@ -5181,8 +5181,8 @@
       <c r="B134" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C134" s="4" t="n">
-        <v>125</v>
+      <c r="C134" s="10" t="n">
+        <v>113</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         <v>1</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135">
@@ -5239,7 +5239,7 @@
         <v>154</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136">
@@ -5252,7 +5252,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="10" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137">
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="138">
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>136</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5357,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="140">
@@ -5411,10 +5411,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141">
@@ -5427,7 +5427,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
         <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142">
@@ -5462,7 +5462,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="143">
@@ -5519,7 +5519,7 @@
         <v>128</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144">
@@ -5532,7 +5532,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145">
@@ -5567,7 +5567,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5586,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="146">
@@ -5602,7 +5602,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="7" t="n">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="147">
@@ -5637,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>181</v>
+        <v>151</v>
       </c>
     </row>
     <row r="148">
@@ -5671,8 +5671,8 @@
       <c r="B148" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C148" s="5" t="n">
-        <v>158</v>
+      <c r="C148" s="4" t="n">
+        <v>146</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -5691,10 +5691,10 @@
         <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149">
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>197</v>
@@ -5742,7 +5742,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="10" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5761,10 +5761,10 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="151">
@@ -5799,7 +5799,7 @@
         <v>129</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="152">
@@ -5812,7 +5812,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="153">
@@ -5847,7 +5847,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>146</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="154">
@@ -5901,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="155">
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156">
@@ -5974,7 +5974,7 @@
         <v>132</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="157">
@@ -5987,7 +5987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158">
@@ -6044,7 +6044,7 @@
         <v>131</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159">
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>194</v>
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="161">
@@ -6149,7 +6149,7 @@
         <v>156</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="162">
@@ -6181,10 +6181,10 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163">
@@ -6197,7 +6197,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="164">
@@ -6232,7 +6232,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="165">
@@ -6267,7 +6267,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>202</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="166">
@@ -6302,7 +6302,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>262</v>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="169">
@@ -6407,7 +6407,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="9" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -6426,10 +6426,10 @@
         <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="170">
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="171">
@@ -6496,10 +6496,10 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="172">
@@ -6531,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="173">
@@ -6566,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="174">
@@ -6601,10 +6601,10 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="175">
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="176">
@@ -6671,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="177">
@@ -6706,10 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="178">
@@ -6744,7 +6744,7 @@
         <v>186</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="179">
@@ -6776,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180">
@@ -6814,7 +6814,7 @@
         <v>184</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="181">
@@ -6849,7 +6849,7 @@
         <v>196</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="182">
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="183">
@@ -6897,7 +6897,7 @@
         <v>194</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184">
@@ -6932,7 +6932,7 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="185">
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="186">
@@ -7002,7 +7002,7 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="187">
@@ -7037,7 +7037,7 @@
         <v>198</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188">
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="189">
@@ -7129,7 +7129,7 @@
         <v>193</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190">
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>272</v>
+        <v>162</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>274</v>
@@ -7199,7 +7199,7 @@
         <v>192</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="192">
@@ -7212,7 +7212,7 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>268</v>
@@ -7247,7 +7247,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>275</v>
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>272</v>
@@ -7339,7 +7339,7 @@
         <v>210</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="196">
@@ -7352,7 +7352,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I196" s="3" t="inlineStr"/>
     </row>
@@ -7385,7 +7385,7 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
@@ -7404,10 +7404,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="198">
@@ -7419,8 +7419,8 @@
       <c r="B198" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C198" s="4" t="n">
-        <v>202</v>
+      <c r="C198" s="5" t="n">
+        <v>254</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -7439,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="199">
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I199" s="3" t="n">
         <v>269</v>
@@ -7512,7 +7512,7 @@
         <v>215</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201">
@@ -7547,7 +7547,7 @@
         <v>240</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="202">
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="203">
@@ -7594,8 +7594,8 @@
       <c r="B203" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="C203" s="4" t="n">
-        <v>229</v>
+      <c r="C203" s="5" t="n">
+        <v>257</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="204">
@@ -7652,7 +7652,7 @@
         <v>185</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="205">
@@ -7665,7 +7665,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
@@ -7684,10 +7684,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="206">
@@ -7719,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="207">
@@ -7757,7 +7757,7 @@
         <v>211</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="208">
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="209">
@@ -7805,7 +7805,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>279</v>
@@ -7840,7 +7840,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7894,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="212">
@@ -7910,7 +7910,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>196</v>
@@ -7945,7 +7945,7 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I213" s="3" t="n">
         <v>280</v>
@@ -7979,8 +7979,8 @@
       <c r="B214" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C214" s="4" t="n">
-        <v>215</v>
+      <c r="C214" s="5" t="n">
+        <v>298</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>281</v>
@@ -8015,7 +8015,7 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I215" s="3" t="n">
         <v>278</v>
@@ -8050,7 +8050,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
@@ -8069,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="217">
@@ -8085,7 +8085,7 @@
         <v>229</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
@@ -8104,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="I217" s="3" t="n">
         <v>223</v>
-      </c>
-      <c r="I217" s="3" t="n">
-        <v>222</v>
       </c>
     </row>
     <row r="218">
@@ -8120,7 +8120,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="219">
@@ -8155,7 +8155,7 @@
         <v>231</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>242</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="220">
@@ -8190,7 +8190,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
@@ -8209,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>246</v>
+        <v>200</v>
       </c>
     </row>
     <row r="221">
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>283</v>
@@ -8259,8 +8259,8 @@
       <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C222" s="5" t="n">
-        <v>270</v>
+      <c r="C222" s="4" t="n">
+        <v>269</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>288</v>
@@ -8317,7 +8317,7 @@
         <v>197</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="224">
@@ -8349,10 +8349,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="225">
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8398,7 +8398,7 @@
         <v>240</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>285</v>
@@ -8433,7 +8433,7 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>286</v>
@@ -8487,10 +8487,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="229">
@@ -8502,8 +8502,8 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="4" t="n">
-        <v>203</v>
+      <c r="C229" s="10" t="n">
+        <v>174</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="230">
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I230" s="3" t="n">
         <v>276</v>
@@ -8573,7 +8573,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I232" s="3" t="n">
         <v>266</v>
@@ -8641,7 +8641,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>265</v>
@@ -8710,8 +8710,8 @@
       <c r="B235" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C235" s="5" t="n">
-        <v>299</v>
+      <c r="C235" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="I235" s="3" t="n">
         <v>290</v>
@@ -8745,8 +8745,8 @@
       <c r="B236" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="C236" s="10" t="n">
-        <v>196</v>
+      <c r="C236" s="4" t="n">
+        <v>209</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8765,10 +8765,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="237">
@@ -8781,7 +8781,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I237" s="3" t="n">
         <v>273</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239">
@@ -8851,7 +8851,7 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
@@ -8903,10 +8903,10 @@
         <v>1</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="241">
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8952,7 +8952,7 @@
         <v>258</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="243">
@@ -9006,10 +9006,10 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="244">
@@ -9022,7 +9022,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9041,10 +9041,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245">
@@ -9057,7 +9057,7 @@
         <v>261</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>225</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="246">
@@ -9092,7 +9092,7 @@
         <v>262</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>291</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I247" s="3" t="n">
         <v>249</v>
@@ -9162,7 +9162,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
@@ -9195,7 +9195,7 @@
         <v>266</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I249" s="3" t="n">
         <v>277</v>
@@ -9249,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251">
@@ -9284,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="I251" s="3" t="n">
         <v>222</v>
-      </c>
-      <c r="I251" s="3" t="n">
-        <v>221</v>
       </c>
     </row>
     <row r="252">
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="253">
@@ -9357,7 +9357,7 @@
         <v>234</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="254">
@@ -9370,7 +9370,7 @@
         <v>271</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
@@ -9389,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="255">
@@ -9404,8 +9404,8 @@
       <c r="B255" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="C255" s="4" t="n">
-        <v>310</v>
+      <c r="C255" s="5" t="n">
+        <v>338</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I255" s="3" t="n">
         <v>293</v>
@@ -9440,7 +9440,7 @@
         <v>273</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I256" s="3" t="n">
         <v>264</v>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I257" s="3" t="n">
         <v>263</v>
@@ -9510,7 +9510,7 @@
         <v>275</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9543,7 +9543,7 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9576,7 +9576,7 @@
         <v>279</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9642,7 +9642,7 @@
         <v>281</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9675,7 +9675,7 @@
         <v>282</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9708,7 +9708,7 @@
         <v>283</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9741,7 +9741,7 @@
         <v>284</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="I265" s="3" t="n">
         <v>292</v>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I266" s="3" t="inlineStr"/>
     </row>
@@ -9828,10 +9828,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="268">
@@ -9844,7 +9844,7 @@
         <v>289</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>261</v>
@@ -9879,7 +9879,7 @@
         <v>290</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
@@ -9898,10 +9898,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>257</v>
+        <v>238</v>
       </c>
     </row>
     <row r="270">
@@ -9914,7 +9914,7 @@
         <v>291</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>239</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="271">
@@ -9949,7 +9949,7 @@
         <v>292</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I271" s="3" t="inlineStr"/>
     </row>
@@ -9982,7 +9982,7 @@
         <v>293</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
@@ -10034,10 +10034,10 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -616,7 +616,7 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2</v>
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -912,7 +912,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         <v>48</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -962,14 +962,14 @@
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>42</v>
+      <c r="G13" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -981,8 +981,8 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>27</v>
+      <c r="C14" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1052,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         <v>42</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1208,13 +1208,13 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1249,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1278,13 +1278,13 @@
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1332,7 +1332,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1348,13 +1348,13 @@
         <v>32</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>18</v>
@@ -1402,7 +1402,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1417,8 +1417,8 @@
       <c r="F26" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="10" t="n">
-        <v>35</v>
+      <c r="G26" s="4" t="n">
+        <v>34</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>30</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
@@ -1472,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>30</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>22</v>
@@ -1506,8 +1506,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>44</v>
+      <c r="C29" s="5" t="n">
+        <v>34</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="7" t="n">
-        <v>17</v>
+      <c r="G29" s="4" t="n">
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1541,8 +1541,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>21</v>
+      <c r="C30" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
@@ -1577,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         <v>27</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1646,8 +1646,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="10" t="n">
-        <v>23</v>
+      <c r="C33" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1662,8 +1662,8 @@
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G33" s="10" t="n">
-        <v>32</v>
+      <c r="G33" s="9" t="n">
+        <v>35</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,13 +1698,13 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>23</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
@@ -1806,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>28</v>
@@ -1822,7 +1822,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         <v>22</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
@@ -1879,7 +1879,7 @@
         <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
@@ -1892,7 +1892,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1907,14 +1907,14 @@
       <c r="F40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>19</v>
+      <c r="G40" s="5" t="n">
+        <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1942,8 +1942,8 @@
       <c r="F41" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>18</v>
+      <c r="G41" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1981,7 +1981,7 @@
         <v>8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>65</v>
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>32</v>
+      <c r="C43" s="10" t="n">
+        <v>31</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2032,7 +2032,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2082,14 +2082,14 @@
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>22</v>
+      <c r="G45" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47">
@@ -2137,7 +2137,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>46</v>
@@ -2171,8 +2171,8 @@
       <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="9" t="n">
-        <v>28</v>
+      <c r="C48" s="10" t="n">
+        <v>33</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>47</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>41</v>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>56</v>
@@ -2366,7 +2366,7 @@
         <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>49</v>
@@ -2382,7 +2382,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>11</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I54" s="3" t="n">
         <v>53</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>57</v>
       </c>
     </row>
     <row r="55">
@@ -2436,10 +2436,10 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56">
@@ -2451,8 +2451,8 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>68</v>
+      <c r="C56" s="5" t="n">
+        <v>66</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2467,14 +2467,14 @@
       <c r="F56" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>6</v>
+      <c r="G56" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -2487,7 +2487,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>45</v>
@@ -2541,7 +2541,7 @@
         <v>8</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>60</v>
@@ -2556,8 +2556,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>69</v>
+      <c r="C59" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>60</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -2592,7 +2592,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>58</v>
@@ -2661,8 +2661,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="10" t="n">
-        <v>55</v>
+      <c r="C62" s="9" t="n">
+        <v>52</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>48</v>
@@ -2696,8 +2696,8 @@
       <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C63" s="10" t="n">
-        <v>56</v>
+      <c r="C63" s="9" t="n">
+        <v>54</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>55</v>
@@ -2732,7 +2732,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>63</v>
@@ -2786,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>71</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>64</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68">
@@ -2872,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>3</v>
+      <c r="G68" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69">
@@ -2929,7 +2929,7 @@
         <v>73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70">
@@ -2942,7 +2942,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2958,13 +2958,13 @@
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71">
@@ -2977,7 +2977,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>68</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72">
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>77</v>
@@ -3066,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>80</v>
@@ -3136,7 +3136,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>59</v>
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         <v>2</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77">
@@ -3186,8 +3186,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="9" t="n">
-        <v>50</v>
+      <c r="C77" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>75</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78">
@@ -3241,7 +3241,7 @@
         <v>17</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>50</v>
@@ -3276,7 +3276,7 @@
         <v>13</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>47</v>
@@ -3292,7 +3292,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>81</v>
@@ -3327,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82">
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>85</v>
@@ -3397,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84">
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3467,7 +3467,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86">
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87">
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88">
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3607,7 +3607,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>137</v>
@@ -3677,7 +3677,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3693,13 +3693,13 @@
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -3712,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>82</v>
@@ -3766,10 +3766,10 @@
         <v>3</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94">
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>76</v>
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96">
@@ -3887,7 +3887,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>69</v>
@@ -3941,10 +3941,10 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99">
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>138</v>
@@ -4011,10 +4011,10 @@
         <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101">
@@ -4027,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>139</v>
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         <v>2</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103">
@@ -4116,7 +4116,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>79</v>
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>132</v>
@@ -4202,7 +4202,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -4221,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107">
@@ -4236,8 +4236,8 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="10" t="n">
-        <v>96</v>
+      <c r="C107" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>101</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108">
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="109">
@@ -4307,7 +4307,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="10" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>105</v>
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111">
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>131</v>
@@ -4412,7 +4412,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>216</v>
@@ -4466,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>136</v>
@@ -4482,7 +4482,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>104</v>
@@ -4517,7 +4517,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4536,10 +4536,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>260</v>
@@ -4641,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>116</v>
@@ -4657,7 +4657,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>112</v>
@@ -4692,7 +4692,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>184</v>
@@ -4727,7 +4727,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122">
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>144</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="123">
@@ -4797,7 +4797,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>148</v>
@@ -4832,7 +4832,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>171</v>
@@ -4866,8 +4866,8 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="9" t="n">
-        <v>84</v>
+      <c r="C125" s="4" t="n">
+        <v>94</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4883,13 +4883,13 @@
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126">
@@ -4902,7 +4902,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>127</v>
@@ -4937,7 +4937,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="128">
@@ -4972,7 +4972,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         <v>4</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="129">
@@ -5006,8 +5006,8 @@
       <c r="B129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="10" t="n">
-        <v>92</v>
+      <c r="C129" s="9" t="n">
+        <v>85</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5023,13 +5023,13 @@
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130">
@@ -5042,7 +5042,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -5061,10 +5061,10 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131">
@@ -5077,7 +5077,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>126</v>
@@ -5112,7 +5112,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="I132" s="3" t="n">
         <v>125</v>
-      </c>
-      <c r="I132" s="3" t="n">
-        <v>109</v>
       </c>
     </row>
     <row r="133">
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>199</v>
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="135">
@@ -5217,7 +5217,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>169</v>
@@ -5271,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137">
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>180</v>
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5357,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>189</v>
@@ -5392,7 +5392,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>173</v>
@@ -5427,7 +5427,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="9" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>113</v>
@@ -5462,7 +5462,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>172</v>
@@ -5497,7 +5497,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>157</v>
@@ -5532,7 +5532,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>135</v>
@@ -5586,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>161</v>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>215</v>
@@ -5637,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148">
@@ -5672,7 +5672,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -5691,10 +5691,10 @@
         <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="149">
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>197</v>
@@ -5741,8 +5741,8 @@
       <c r="B150" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C150" s="10" t="n">
-        <v>126</v>
+      <c r="C150" s="4" t="n">
+        <v>130</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5761,10 +5761,10 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="I150" s="3" t="n">
         <v>122</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="151">
@@ -5777,7 +5777,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>134</v>
@@ -5812,7 +5812,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>128</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>224</v>
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>214</v>
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="156">
@@ -5951,8 +5951,8 @@
       <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C156" s="10" t="n">
-        <v>148</v>
+      <c r="C156" s="9" t="n">
+        <v>144</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5971,10 +5971,10 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="157">
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>211</v>
@@ -6022,7 +6022,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>159</v>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>194</v>
@@ -6092,7 +6092,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>145</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="161">
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>160</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>198</v>
@@ -6232,7 +6232,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>201</v>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>202</v>
@@ -6302,7 +6302,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>262</v>
@@ -6337,7 +6337,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>195</v>
@@ -6372,7 +6372,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>230</v>
@@ -6426,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>114</v>
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>111</v>
@@ -6512,7 +6512,7 @@
         <v>183</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6531,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="173">
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>167</v>
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>142</v>
@@ -6617,7 +6617,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>166</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>204</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>140</v>
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>146</v>
@@ -6757,7 +6757,7 @@
         <v>190</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>165</v>
@@ -6791,8 +6791,8 @@
       <c r="B180" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C180" s="10" t="n">
-        <v>162</v>
+      <c r="C180" s="4" t="n">
+        <v>166</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>164</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>231</v>
@@ -6862,7 +6862,7 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>254</v>
@@ -6897,7 +6897,7 @@
         <v>194</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>186</v>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>249</v>
+        <v>161</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>245</v>
@@ -6966,8 +6966,8 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>237</v>
+      <c r="C185" s="4" t="n">
+        <v>210</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>241</v>
@@ -7002,7 +7002,7 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>247</v>
@@ -7056,10 +7056,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188">
@@ -7072,7 +7072,7 @@
         <v>199</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>208</v>
@@ -7107,7 +7107,7 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>168</v>
@@ -7142,7 +7142,7 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>274</v>
@@ -7177,7 +7177,7 @@
         <v>203</v>
       </c>
       <c r="C191" s="10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>182</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>268</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>275</v>
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>272</v>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>218</v>
@@ -7352,7 +7352,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="I196" s="3" t="inlineStr"/>
     </row>
@@ -7385,7 +7385,7 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="I197" s="3" t="n">
         <v>251</v>
@@ -7420,7 +7420,7 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>228</v>
@@ -7455,7 +7455,7 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="I199" s="3" t="n">
         <v>269</v>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>212</v>
@@ -7525,7 +7525,7 @@
         <v>213</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>213</v>
@@ -7560,7 +7560,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>229</v>
@@ -7595,7 +7595,7 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>240</v>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>175</v>
@@ -7665,7 +7665,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>185</v>
@@ -7700,7 +7700,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>170</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>179</v>
@@ -7770,7 +7770,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>210</v>
@@ -7805,7 +7805,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>279</v>
@@ -7840,7 +7840,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7875,7 +7875,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="I211" s="3" t="n">
         <v>253</v>
@@ -7910,7 +7910,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="10" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>196</v>
@@ -7945,7 +7945,7 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I213" s="3" t="n">
         <v>280</v>
@@ -7980,7 +7980,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>163</v>
+        <v>262</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>281</v>
@@ -8015,7 +8015,7 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="I215" s="3" t="n">
         <v>278</v>
@@ -8050,7 +8050,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>246</v>
+        <v>167</v>
       </c>
       <c r="I216" s="3" t="n">
         <v>227</v>
@@ -8085,7 +8085,7 @@
         <v>229</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="I217" s="3" t="n">
         <v>223</v>
@@ -8119,8 +8119,8 @@
       <c r="B218" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C218" s="5" t="n">
-        <v>266</v>
+      <c r="C218" s="4" t="n">
+        <v>235</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>226</v>
@@ -8155,7 +8155,7 @@
         <v>231</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>252</v>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>200</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>283</v>
@@ -8259,8 +8259,8 @@
       <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C222" s="4" t="n">
-        <v>269</v>
+      <c r="C222" s="5" t="n">
+        <v>274</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>288</v>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="I223" s="3" t="n">
         <v>203</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>190</v>
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>161</v>
+        <v>261</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8398,7 +8398,7 @@
         <v>240</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>285</v>
@@ -8433,7 +8433,7 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>286</v>
@@ -8468,7 +8468,7 @@
         <v>242</v>
       </c>
       <c r="C228" s="10" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>158</v>
@@ -8503,7 +8503,7 @@
         <v>243</v>
       </c>
       <c r="C229" s="10" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="230">
@@ -8538,7 +8538,7 @@
         <v>244</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="I230" s="3" t="n">
         <v>276</v>
@@ -8573,7 +8573,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8606,7 +8606,7 @@
         <v>246</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="I232" s="3" t="n">
         <v>266</v>
@@ -8641,7 +8641,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8676,7 +8676,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>265</v>
@@ -8711,7 +8711,7 @@
         <v>249</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>258</v>
+        <v>183</v>
       </c>
       <c r="I235" s="3" t="n">
         <v>290</v>
@@ -8746,7 +8746,7 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>193</v>
@@ -8781,7 +8781,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>251</v>
+        <v>173</v>
       </c>
       <c r="I237" s="3" t="n">
         <v>273</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>181</v>
@@ -8851,7 +8851,7 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
@@ -8884,7 +8884,7 @@
         <v>256</v>
       </c>
       <c r="C240" s="10" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
@@ -8900,10 +8900,10 @@
         <v>0</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="I240" s="3" t="n">
         <v>147</v>
@@ -8919,7 +8919,7 @@
         <v>257</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8952,7 +8952,7 @@
         <v>258</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="243">
@@ -8987,7 +8987,7 @@
         <v>259</v>
       </c>
       <c r="C243" s="10" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="I243" s="3" t="n">
         <v>217</v>
@@ -9022,7 +9022,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>239</v>
@@ -9057,7 +9057,7 @@
         <v>261</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="I245" s="3" t="n">
         <v>246</v>
@@ -9092,7 +9092,7 @@
         <v>262</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>291</v>
@@ -9127,7 +9127,7 @@
         <v>263</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="I247" s="3" t="n">
         <v>249</v>
@@ -9162,7 +9162,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
@@ -9195,7 +9195,7 @@
         <v>266</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I249" s="3" t="n">
         <v>277</v>
@@ -9230,7 +9230,7 @@
         <v>267</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>209</v>
@@ -9265,7 +9265,7 @@
         <v>268</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="I251" s="3" t="n">
         <v>222</v>
@@ -9300,7 +9300,7 @@
         <v>269</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="I252" s="3" t="n">
         <v>242</v>
@@ -9335,7 +9335,7 @@
         <v>270</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="I253" s="3" t="n">
         <v>244</v>
@@ -9370,7 +9370,7 @@
         <v>271</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I254" s="3" t="n">
         <v>225</v>
@@ -9405,7 +9405,7 @@
         <v>272</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>164</v>
+        <v>267</v>
       </c>
       <c r="I255" s="3" t="n">
         <v>293</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="I256" s="3" t="n">
         <v>264</v>
@@ -9475,7 +9475,7 @@
         <v>274</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="I257" s="3" t="n">
         <v>263</v>
@@ -9510,7 +9510,7 @@
         <v>275</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9576,7 +9576,7 @@
         <v>279</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9609,7 +9609,7 @@
         <v>280</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9642,7 +9642,7 @@
         <v>281</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9675,7 +9675,7 @@
         <v>282</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9708,7 +9708,7 @@
         <v>283</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>167</v>
+        <v>270</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9741,7 +9741,7 @@
         <v>284</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>170</v>
+        <v>266</v>
       </c>
       <c r="I265" s="3" t="n">
         <v>292</v>
@@ -9776,7 +9776,7 @@
         <v>287</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="I266" s="3" t="inlineStr"/>
     </row>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I267" s="3" t="n">
         <v>232</v>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>261</v>
@@ -9898,7 +9898,7 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I269" s="3" t="n">
         <v>238</v>
@@ -9914,7 +9914,7 @@
         <v>291</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>257</v>
@@ -9949,7 +9949,7 @@
         <v>292</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="I271" s="3" t="inlineStr"/>
     </row>
@@ -9982,7 +9982,7 @@
         <v>293</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
@@ -10015,7 +10015,7 @@
         <v>296</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="I273" s="3" t="n">
         <v>243</v>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -616,10 +616,10 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -651,10 +651,10 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>43</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1121,8 +1121,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>27</v>
+      <c r="C18" s="7" t="n">
+        <v>41</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
       <c r="F18" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>30</v>
+      <c r="G18" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -1214,7 +1214,7 @@
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1351,10 +1351,10 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>18</v>
@@ -1402,7 +1402,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>31</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1452,14 +1452,14 @@
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>22</v>
+      <c r="G27" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -1472,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         <v>30</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -1506,8 +1506,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>34</v>
+      <c r="C29" s="7" t="n">
+        <v>42</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>23</v>
+      <c r="G29" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
@@ -1541,8 +1541,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>22</v>
+      <c r="C30" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
@@ -1634,7 +1634,7 @@
         <v>31</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1647,7 +1647,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>25</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,13 +1698,13 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -1739,7 +1739,7 @@
         <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
@@ -1774,7 +1774,7 @@
         <v>35</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -1806,10 +1806,10 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -1841,10 +1841,10 @@
         <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -1879,7 +1879,7 @@
         <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -1949,7 +1949,7 @@
         <v>40</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
@@ -1981,7 +1981,7 @@
         <v>8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>65</v>
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="10" t="n">
-        <v>31</v>
+      <c r="C43" s="4" t="n">
+        <v>32</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2082,8 +2082,8 @@
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>19</v>
+      <c r="G45" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -2156,10 +2156,10 @@
         <v>27</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
@@ -2171,8 +2171,8 @@
       <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="10" t="n">
-        <v>33</v>
+      <c r="C48" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2241,8 +2241,8 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="10" t="n">
-        <v>41</v>
+      <c r="C50" s="9" t="n">
+        <v>27</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2257,14 +2257,14 @@
       <c r="F50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>19</v>
+      <c r="G50" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -2299,7 +2299,7 @@
         <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52">
@@ -2366,10 +2366,10 @@
         <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -2382,7 +2382,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>11</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
@@ -2436,7 +2436,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>51</v>
@@ -2471,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>62</v>
@@ -2506,10 +2506,10 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58">
@@ -2522,7 +2522,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2538,13 +2538,13 @@
         <v>10</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59">
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -2611,7 +2611,7 @@
         <v>6</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>70</v>
@@ -2627,7 +2627,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>66</v>
@@ -2684,7 +2684,7 @@
         <v>61</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -2716,10 +2716,10 @@
         <v>10</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>63</v>
@@ -2786,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>71</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>7</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
         <v>7</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68">
@@ -2872,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69">
@@ -2961,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>83</v>
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>77</v>
@@ -3066,10 +3066,10 @@
         <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -3082,7 +3082,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
@@ -3117,7 +3117,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3133,13 +3133,13 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76">
@@ -3174,7 +3174,7 @@
         <v>77</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77">
@@ -3222,7 +3222,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         <v>5</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>50</v>
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>13</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>47</v>
@@ -3311,10 +3311,10 @@
         <v>5</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81">
@@ -3327,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3343,13 +3343,13 @@
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82">
@@ -3381,10 +3381,10 @@
         <v>4</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>97</v>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>96</v>
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87">
@@ -3537,7 +3537,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88">
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91">
@@ -3696,10 +3696,10 @@
         <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>82</v>
@@ -3747,7 +3747,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3763,13 +3763,13 @@
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94">
@@ -3801,10 +3801,10 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95">
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96">
@@ -3852,7 +3852,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3906,7 +3906,7 @@
         <v>6</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>69</v>
@@ -3922,7 +3922,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99">
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100">
@@ -4011,7 +4011,7 @@
         <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>85</v>
@@ -4046,10 +4046,10 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102">
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4078,13 +4078,13 @@
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103">
@@ -4116,10 +4116,10 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="104">
@@ -4132,7 +4132,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>117</v>
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         <v>2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>132</v>
@@ -4221,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107">
@@ -4256,10 +4256,10 @@
         <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108">
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>86</v>
@@ -4326,10 +4326,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>154</v>
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112">
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="113">
@@ -4466,10 +4466,10 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114">
@@ -4482,7 +4482,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4498,13 +4498,13 @@
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115">
@@ -4517,7 +4517,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4536,10 +4536,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116">
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>260</v>
@@ -4621,8 +4621,8 @@
       <c r="B118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C118" s="10" t="n">
-        <v>108</v>
+      <c r="C118" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119">
@@ -4656,8 +4656,8 @@
       <c r="B119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="9" t="n">
-        <v>103</v>
+      <c r="C119" s="10" t="n">
+        <v>108</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120">
@@ -4711,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>184</v>
@@ -4746,7 +4746,7 @@
         <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>87</v>
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="123">
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124">
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>171</v>
@@ -4867,7 +4867,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>84</v>
@@ -4921,10 +4921,10 @@
         <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127">
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>153</v>
@@ -4972,7 +4972,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         <v>4</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129">
@@ -5007,7 +5007,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5023,13 +5023,13 @@
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="130">
@@ -5061,10 +5061,10 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="131">
@@ -5077,7 +5077,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -5093,13 +5093,13 @@
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="132">
@@ -5112,7 +5112,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133">
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>199</v>
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135">
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>169</v>
@@ -5271,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137">
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>180</v>
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5357,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>189</v>
@@ -5392,7 +5392,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>173</v>
@@ -5427,7 +5427,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="9" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142">
@@ -5462,7 +5462,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>172</v>
@@ -5516,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>157</v>
@@ -5532,7 +5532,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145">
@@ -5586,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>161</v>
@@ -5602,7 +5602,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="7" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="147">
@@ -5637,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5653,13 +5653,13 @@
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148">
@@ -5691,10 +5691,10 @@
         <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149">
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>197</v>
@@ -5761,10 +5761,10 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="151">
@@ -5796,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152">
@@ -5812,7 +5812,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153">
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="154">
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="155">
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>187</v>
@@ -5971,10 +5971,10 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="157">
@@ -5987,7 +5987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>211</v>
@@ -6022,7 +6022,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>159</v>
@@ -6057,7 +6057,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>194</v>
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="161">
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>174</v>
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>160</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>198</v>
@@ -6232,7 +6232,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>201</v>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>202</v>
@@ -6302,7 +6302,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>262</v>
@@ -6337,26 +6337,26 @@
         <v>166</v>
       </c>
       <c r="C167" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Tyjae Spears</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="n">
         <v>209</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Tyjae Spears</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="3" t="n">
-        <v>228</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>195</v>
@@ -6372,7 +6372,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="169">
@@ -6407,7 +6407,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -6426,10 +6426,10 @@
         <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="170">
@@ -6461,10 +6461,10 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="171">
@@ -6499,7 +6499,7 @@
         <v>187</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="172">
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>155</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>167</v>
@@ -6601,10 +6601,10 @@
         <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="175">
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>166</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>204</v>
@@ -6706,10 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="178">
@@ -6744,7 +6744,7 @@
         <v>185</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="179">
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>165</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>164</v>
@@ -6846,10 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="182">
@@ -6862,7 +6862,7 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>254</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>186</v>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="185">
@@ -6966,8 +6966,8 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="4" t="n">
-        <v>210</v>
+      <c r="C185" s="5" t="n">
+        <v>238</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="186">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="187">
@@ -7056,10 +7056,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188">
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>208</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>168</v>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>274</v>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>182</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>182</v>
+        <v>259</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>268</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>180</v>
+        <v>262</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>275</v>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>272</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="196">
@@ -7352,7 +7352,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="I196" s="3" t="inlineStr"/>
     </row>
@@ -7404,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="I197" s="3" t="n">
         <v>251</v>
@@ -7420,7 +7420,7 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -7439,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="199">
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="I199" s="3" t="n">
         <v>269</v>
@@ -7490,7 +7490,7 @@
         <v>212</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>212</v>
@@ -7525,7 +7525,7 @@
         <v>213</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>213</v>
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="203">
@@ -7614,10 +7614,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="204">
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>175</v>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>185</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>170</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>179</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>210</v>
@@ -7805,7 +7805,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>279</v>
@@ -7840,7 +7840,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7875,7 +7875,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="I211" s="3" t="n">
         <v>253</v>
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>196</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="I213" s="3" t="n">
         <v>280</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>262</v>
+        <v>175</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>281</v>
@@ -8034,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="I215" s="3" t="n">
         <v>278</v>
@@ -8050,7 +8050,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
@@ -8069,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="217">
@@ -8085,7 +8085,7 @@
         <v>229</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
@@ -8104,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="218">
@@ -8120,7 +8120,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="4" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="219">
@@ -8155,7 +8155,7 @@
         <v>231</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>252</v>
@@ -8190,7 +8190,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>200</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>283</v>
@@ -8260,7 +8260,7 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>170</v>
+        <v>258</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>288</v>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="I223" s="3" t="n">
         <v>203</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>190</v>
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>285</v>
@@ -8433,7 +8433,7 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>200</v>
+        <v>263</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>286</v>
@@ -8468,7 +8468,7 @@
         <v>242</v>
       </c>
       <c r="C228" s="10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>158</v>
@@ -8503,7 +8503,7 @@
         <v>243</v>
       </c>
       <c r="C229" s="10" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="I229" s="3" t="n">
         <v>188</v>
@@ -8538,7 +8538,7 @@
         <v>244</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="I230" s="3" t="n">
         <v>276</v>
@@ -8573,7 +8573,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="I232" s="3" t="n">
         <v>266</v>
@@ -8641,7 +8641,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8676,7 +8676,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>265</v>
@@ -8711,7 +8711,7 @@
         <v>249</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="I235" s="3" t="n">
         <v>290</v>
@@ -8746,7 +8746,7 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>193</v>
@@ -8781,7 +8781,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="I237" s="3" t="n">
         <v>273</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>181</v>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="241">
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="243">
@@ -9006,10 +9006,10 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="244">
@@ -9022,7 +9022,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9041,10 +9041,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="245">
@@ -9057,7 +9057,7 @@
         <v>261</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
@@ -9076,10 +9076,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
     </row>
     <row r="246">
@@ -9092,7 +9092,7 @@
         <v>262</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>291</v>
@@ -9127,7 +9127,7 @@
         <v>263</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="I247" s="3" t="n">
         <v>249</v>
@@ -9162,7 +9162,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>268</v>
+        <v>164</v>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
@@ -9195,7 +9195,7 @@
         <v>266</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="I249" s="3" t="n">
         <v>277</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>209</v>
@@ -9284,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="252">
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="I252" s="3" t="n">
         <v>244</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>242</v>
       </c>
     </row>
     <row r="253">
@@ -9354,10 +9354,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="254">
@@ -9370,7 +9370,7 @@
         <v>271</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
@@ -9389,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="255">
@@ -9405,7 +9405,7 @@
         <v>272</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="I255" s="3" t="n">
         <v>293</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="I256" s="3" t="n">
         <v>264</v>
@@ -9475,7 +9475,7 @@
         <v>274</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="I257" s="3" t="n">
         <v>263</v>
@@ -9510,7 +9510,7 @@
         <v>275</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9543,7 +9543,7 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>257</v>
+        <v>163</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9576,7 +9576,7 @@
         <v>279</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9642,7 +9642,7 @@
         <v>281</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9708,7 +9708,7 @@
         <v>283</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9741,7 +9741,7 @@
         <v>284</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="I265" s="3" t="n">
         <v>292</v>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="I266" s="3" t="inlineStr"/>
     </row>
@@ -9828,10 +9828,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="268">
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>261</v>
@@ -9879,29 +9879,29 @@
         <v>290</v>
       </c>
       <c r="C269" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Evan Engram</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F269" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" s="3" t="n">
-        <v>231</v>
-      </c>
       <c r="I269" s="3" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="270">
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>257</v>
@@ -9949,7 +9949,7 @@
         <v>292</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="I271" s="3" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>269</v>
+        <v>166</v>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
@@ -10034,10 +10034,10 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -632,16 +632,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -654,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -667,16 +667,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -689,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -982,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1052,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>40</v>
+      <c r="G16" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -1156,30 +1156,30 @@
       <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>24</v>
+      <c r="C19" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>32</v>
+      <c r="G19" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -1192,29 +1192,29 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1227,29 +1227,29 @@
         <v>20</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1262,29 +1262,29 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kenneth Walker</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1296,30 +1296,30 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>10</v>
+      <c r="C23" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Kenneth Walker</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -1331,30 +1331,30 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>40</v>
+      <c r="C24" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>20</v>
+      <c r="G24" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="H24" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>23</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -1386,10 +1386,10 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -1424,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1452,8 +1452,8 @@
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>24</v>
+      <c r="G27" s="5" t="n">
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>26</v>
@@ -1494,7 +1494,7 @@
         <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -1564,7 +1564,7 @@
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1576,30 +1576,30 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="9" t="n">
-        <v>26</v>
+      <c r="C31" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>30</v>
+      <c r="G31" s="5" t="n">
+        <v>20</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -1669,7 +1669,7 @@
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>28</v>
@@ -1806,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1841,7 +1841,7 @@
         <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>38</v>
@@ -1876,7 +1876,7 @@
         <v>21</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>32</v>
@@ -1911,7 +1911,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>44</v>
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
@@ -1961,8 +1961,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>62</v>
+      <c r="C42" s="7" t="n">
+        <v>64</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>19</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>42</v>
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>32</v>
+      <c r="C43" s="10" t="n">
+        <v>31</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>41</v>
@@ -2031,8 +2031,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>58</v>
+      <c r="C44" s="5" t="n">
+        <v>51</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>46</v>
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2223,13 +2223,13 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -2312,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
         <v>12</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53">
@@ -2347,7 +2347,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2362,14 +2362,14 @@
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>14</v>
+      <c r="G53" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
@@ -2401,7 +2401,7 @@
         <v>13</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>55</v>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>56</v>
@@ -2474,7 +2474,7 @@
         <v>55</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>49</v>
@@ -2541,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -2592,29 +2592,29 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>60</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61">
@@ -2626,30 +2626,30 @@
       <c r="B61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="4" t="n">
-        <v>64</v>
+      <c r="C61" s="9" t="n">
+        <v>52</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>58</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
@@ -2661,30 +2661,30 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>52</v>
+      <c r="C62" s="4" t="n">
+        <v>69</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -2697,7 +2697,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2713,10 +2713,10 @@
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>53</v>
@@ -2751,10 +2751,10 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -2789,7 +2789,7 @@
         <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66">
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>7</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2852,14 +2852,14 @@
       <c r="F67" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>3</v>
+      <c r="G67" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68">
@@ -2891,10 +2891,10 @@
         <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69">
@@ -2907,7 +2907,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
@@ -2941,8 +2941,8 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="7" t="n">
-        <v>84</v>
+      <c r="C70" s="5" t="n">
+        <v>78</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71">
@@ -2976,8 +2976,8 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="4" t="n">
-        <v>59</v>
+      <c r="C71" s="5" t="n">
+        <v>77</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2993,13 +2993,13 @@
         <v>6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72">
@@ -3031,10 +3031,10 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73">
@@ -3066,10 +3066,10 @@
         <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74">
@@ -3104,7 +3104,7 @@
         <v>72</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75">
@@ -3136,10 +3136,10 @@
         <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76">
@@ -3174,7 +3174,7 @@
         <v>77</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77">
@@ -3187,7 +3187,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78">
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80">
@@ -3291,8 +3291,8 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="4" t="n">
-        <v>77</v>
+      <c r="C80" s="10" t="n">
+        <v>58</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
@@ -3326,8 +3326,8 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="7" t="n">
-        <v>97</v>
+      <c r="C81" s="5" t="n">
+        <v>86</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3343,13 +3343,13 @@
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82">
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3378,13 +3378,13 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83">
@@ -3419,7 +3419,7 @@
         <v>85</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84">
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3486,10 +3486,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86">
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87">
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
@@ -3607,7 +3607,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91">
@@ -3677,29 +3677,29 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
@@ -3712,16 +3712,16 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -3731,10 +3731,10 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93">
@@ -3746,30 +3746,30 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="4" t="n">
-        <v>86</v>
+      <c r="C93" s="7" t="n">
+        <v>124</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94">
@@ -3801,10 +3801,10 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95">
@@ -3839,7 +3839,7 @@
         <v>95</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96">
@@ -3852,7 +3852,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>102</v>
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100">
@@ -3991,8 +3991,8 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="9" t="n">
-        <v>80</v>
+      <c r="C100" s="4" t="n">
+        <v>127</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101">
@@ -4027,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         <v>2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102">
@@ -4081,10 +4081,10 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103">
@@ -4116,10 +4116,10 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104">
@@ -4151,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="105">
@@ -4189,7 +4189,7 @@
         <v>104</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="106">
@@ -4237,7 +4237,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108">
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109">
@@ -4306,8 +4306,8 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="10" t="n">
-        <v>98</v>
+      <c r="C109" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110">
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>154</v>
@@ -4396,10 +4396,10 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112">
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="113">
@@ -4446,30 +4446,30 @@
       <c r="B113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C113" s="7" t="n">
-        <v>134</v>
+      <c r="C113" s="4" t="n">
+        <v>93</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114">
@@ -4482,16 +4482,16 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -4504,7 +4504,7 @@
         <v>120</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115">
@@ -4517,7 +4517,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4536,10 +4536,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116">
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>94</v>
@@ -4606,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118">
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119">
@@ -4676,10 +4676,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120">
@@ -4714,7 +4714,7 @@
         <v>116</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="121">
@@ -4727,7 +4727,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>106</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="122">
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>93</v>
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124">
@@ -4832,7 +4832,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125">
@@ -4867,7 +4867,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4883,13 +4883,13 @@
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126">
@@ -4901,8 +4901,8 @@
       <c r="B126" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="4" t="n">
-        <v>123</v>
+      <c r="C126" s="5" t="n">
+        <v>135</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="127">
@@ -4937,7 +4937,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128">
@@ -4971,8 +4971,8 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="9" t="n">
-        <v>85</v>
+      <c r="C128" s="10" t="n">
+        <v>92</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4988,13 +4988,13 @@
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129">
@@ -5007,7 +5007,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="9" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5023,13 +5023,13 @@
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130">
@@ -5042,7 +5042,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -5061,10 +5061,10 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131">
@@ -5077,7 +5077,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
         <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132">
@@ -5131,10 +5131,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133">
@@ -5147,7 +5147,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134">
@@ -5201,10 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="135">
@@ -5239,7 +5239,7 @@
         <v>153</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="136">
@@ -5271,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137">
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138">
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="139">
@@ -5379,7 +5379,7 @@
         <v>155</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="140">
@@ -5392,7 +5392,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
     </row>
     <row r="141">
@@ -5426,8 +5426,8 @@
       <c r="B141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="9" t="n">
-        <v>127</v>
+      <c r="C141" s="4" t="n">
+        <v>161</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="142">
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="143">
@@ -5516,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>157</v>
@@ -5532,7 +5532,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="145">
@@ -5567,7 +5567,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5583,13 +5583,13 @@
         <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="146">
@@ -5624,7 +5624,7 @@
         <v>145</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="147">
@@ -5636,8 +5636,8 @@
       <c r="B147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="4" t="n">
-        <v>120</v>
+      <c r="C147" s="10" t="n">
+        <v>106</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
         <v>2</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148">
@@ -5691,10 +5691,10 @@
         <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149">
@@ -5729,7 +5729,7 @@
         <v>158</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="150">
@@ -5764,7 +5764,7 @@
         <v>160</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="151">
@@ -5796,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="152">
@@ -5811,8 +5811,8 @@
       <c r="B152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="4" t="n">
-        <v>137</v>
+      <c r="C152" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         <v>1</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153">
@@ -5847,7 +5847,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>147</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="154">
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>146</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="155">
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156">
@@ -5952,7 +5952,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="9" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5968,13 +5968,13 @@
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157">
@@ -5987,7 +5987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158">
@@ -6022,7 +6022,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -6041,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159">
@@ -6057,7 +6057,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160">
@@ -6114,7 +6114,7 @@
         <v>159</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="161">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="162">
@@ -6162,7 +6162,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -6178,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="163">
@@ -6219,7 +6219,7 @@
         <v>193</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="164">
@@ -6232,7 +6232,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="165">
@@ -6289,7 +6289,7 @@
         <v>201</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="166">
@@ -6302,16 +6302,16 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>262</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167">
@@ -6336,8 +6336,8 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="5" t="n">
-        <v>208</v>
+      <c r="C167" s="9" t="n">
+        <v>128</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -6353,13 +6353,13 @@
         <v>0</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168">
@@ -6372,7 +6372,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="169">
@@ -6406,8 +6406,8 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="9" t="n">
-        <v>117</v>
+      <c r="C169" s="4" t="n">
+        <v>144</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -6423,13 +6423,13 @@
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170">
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6458,13 +6458,13 @@
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="171">
@@ -6499,7 +6499,7 @@
         <v>187</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="172">
@@ -6511,8 +6511,8 @@
       <c r="B172" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="C172" s="4" t="n">
-        <v>165</v>
+      <c r="C172" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6528,13 +6528,13 @@
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173">
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
     </row>
     <row r="174">
@@ -6581,8 +6581,8 @@
       <c r="B174" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="C174" s="10" t="n">
-        <v>150</v>
+      <c r="C174" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
     </row>
     <row r="175">
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="176">
@@ -6652,7 +6652,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6671,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>204</v>
+        <v>298</v>
       </c>
     </row>
     <row r="177">
@@ -6686,8 +6686,8 @@
       <c r="B177" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="C177" s="9" t="n">
-        <v>142</v>
+      <c r="C177" s="10" t="n">
+        <v>151</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
@@ -6706,10 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="178">
@@ -6721,8 +6721,8 @@
       <c r="B178" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="C178" s="9" t="n">
-        <v>151</v>
+      <c r="C178" s="4" t="n">
+        <v>182</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6738,13 +6738,13 @@
         <v>0</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179">
@@ -6757,7 +6757,7 @@
         <v>190</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6776,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="180">
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181">
@@ -6827,7 +6827,7 @@
         <v>192</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>233</v>
+        <v>155</v>
       </c>
     </row>
     <row r="182">
@@ -6862,7 +6862,7 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="183">
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="184">
@@ -6932,7 +6932,7 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="185">
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186">
@@ -7001,17 +7001,17 @@
       <c r="B186" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C186" s="5" t="n">
-        <v>256</v>
+      <c r="C186" s="4" t="n">
+        <v>173</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>248</v>
+        <v>182</v>
       </c>
     </row>
     <row r="187">
@@ -7056,10 +7056,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="188">
@@ -7071,8 +7071,8 @@
       <c r="B188" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C188" s="4" t="n">
-        <v>217</v>
+      <c r="C188" s="5" t="n">
+        <v>231</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="189">
@@ -7129,7 +7129,7 @@
         <v>203</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="190">
@@ -7142,16 +7142,16 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="191">
@@ -7174,19 +7174,19 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C191" s="10" t="n">
-        <v>172</v>
+        <v>202</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>256</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -7196,10 +7196,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>182</v>
+        <v>249</v>
       </c>
     </row>
     <row r="192">
@@ -7209,19 +7209,19 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="193">
@@ -7246,17 +7246,17 @@
       <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C193" s="5" t="n">
-        <v>286</v>
+      <c r="C193" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>275</v>
+        <v>183</v>
       </c>
     </row>
     <row r="194">
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="195">
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="196">
@@ -7352,16 +7352,16 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -7371,9 +7371,11 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="I196" s="3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>269</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -7385,16 +7387,16 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7404,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>251</v>
+        <v>276</v>
       </c>
     </row>
     <row r="198">
@@ -7420,16 +7422,16 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -7439,11 +7441,9 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I198" s="3" t="n">
-        <v>230</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="200">
@@ -7525,7 +7525,7 @@
         <v>213</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="202">
@@ -7560,7 +7560,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="203">
@@ -7617,7 +7617,7 @@
         <v>239</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="204">
@@ -7649,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="205">
@@ -7684,10 +7684,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="206">
@@ -7719,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="207">
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="208">
@@ -7770,7 +7770,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="209">
@@ -7805,7 +7805,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="210">
@@ -7839,8 +7839,8 @@
       <c r="B210" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C210" s="5" t="n">
-        <v>298</v>
+      <c r="C210" s="4" t="n">
+        <v>254</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7875,7 +7875,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="212">
@@ -7909,17 +7909,17 @@
       <c r="B212" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C212" s="10" t="n">
-        <v>171</v>
+      <c r="C212" s="5" t="n">
+        <v>263</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7929,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213">
@@ -7945,7 +7945,7 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="214">
@@ -7980,7 +7980,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="215">
@@ -8015,11 +8015,11 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
@@ -8034,10 +8034,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="216">
@@ -8049,17 +8049,17 @@
       <c r="B216" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C216" s="5" t="n">
-        <v>267</v>
+      <c r="C216" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -8069,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="217">
@@ -8084,12 +8084,12 @@
       <c r="B217" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C217" s="4" t="n">
-        <v>224</v>
+      <c r="C217" s="5" t="n">
+        <v>297</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -8104,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>217</v>
+        <v>279</v>
       </c>
     </row>
     <row r="218">
@@ -8119,17 +8119,17 @@
       <c r="B218" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C218" s="4" t="n">
-        <v>236</v>
+      <c r="C218" s="5" t="n">
+        <v>265</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="219">
@@ -8155,16 +8155,16 @@
         <v>231</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8174,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="220">
@@ -8190,16 +8190,16 @@
         <v>232</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -8209,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>200</v>
+        <v>229</v>
       </c>
     </row>
     <row r="221">
@@ -8224,17 +8224,17 @@
       <c r="B221" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C221" s="5" t="n">
-        <v>300</v>
+      <c r="C221" s="4" t="n">
+        <v>266</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>283</v>
+        <v>253</v>
       </c>
     </row>
     <row r="222">
@@ -8260,16 +8260,16 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -8279,10 +8279,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="223">
@@ -8295,7 +8295,7 @@
         <v>237</v>
       </c>
       <c r="C223" s="10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
@@ -8314,10 +8314,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>203</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224">
@@ -8330,7 +8330,7 @@
         <v>238</v>
       </c>
       <c r="C224" s="10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="225">
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8397,8 +8397,8 @@
       <c r="B226" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C226" s="5" t="n">
-        <v>293</v>
+      <c r="C226" s="4" t="n">
+        <v>209</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>285</v>
+        <v>213</v>
       </c>
     </row>
     <row r="227">
@@ -8433,7 +8433,7 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>286</v>
@@ -8468,7 +8468,7 @@
         <v>242</v>
       </c>
       <c r="C228" s="10" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>158</v>
@@ -8502,8 +8502,8 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="10" t="n">
-        <v>177</v>
+      <c r="C229" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="230">
@@ -8560,7 +8560,7 @@
         <v>264</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="231">
@@ -8573,7 +8573,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8605,8 +8605,8 @@
       <c r="B232" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C232" s="4" t="n">
-        <v>274</v>
+      <c r="C232" s="5" t="n">
+        <v>287</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
@@ -8625,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="233">
@@ -8641,7 +8641,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8676,7 +8676,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
@@ -8695,10 +8695,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="235">
@@ -8711,7 +8711,7 @@
         <v>249</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="I235" s="3" t="n">
         <v>290</v>
@@ -8746,7 +8746,7 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8765,10 +8765,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="237">
@@ -8781,7 +8781,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8800,10 +8800,10 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238">
@@ -8815,17 +8815,17 @@
       <c r="B238" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C238" s="10" t="n">
-        <v>173</v>
+      <c r="C238" s="4" t="n">
+        <v>277</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>181</v>
+        <v>288</v>
       </c>
     </row>
     <row r="239">
@@ -8851,7 +8851,7 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>256</v>
       </c>
       <c r="C240" s="10" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="241">
@@ -8919,7 +8919,7 @@
         <v>257</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8951,17 +8951,17 @@
       <c r="B242" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C242" s="4" t="n">
-        <v>234</v>
+      <c r="C242" s="10" t="n">
+        <v>193</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F242" s="3" t="n">
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I242" s="3" t="n">
         <v>222</v>
-      </c>
-      <c r="I242" s="3" t="n">
-        <v>224</v>
       </c>
     </row>
     <row r="243">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C243" s="10" t="n">
-        <v>193</v>
+        <v>260</v>
+      </c>
+      <c r="C243" s="4" t="n">
+        <v>234</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F243" s="3" t="n">
@@ -9006,32 +9006,32 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F244" s="3" t="n">
@@ -9041,10 +9041,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="245">
@@ -9054,19 +9054,19 @@
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F245" s="3" t="n">
@@ -9076,10 +9076,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>215</v>
+        <v>291</v>
       </c>
     </row>
     <row r="246">
@@ -9089,19 +9089,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9111,10 +9111,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>291</v>
+        <v>228</v>
       </c>
     </row>
     <row r="247">
@@ -9124,32 +9124,32 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C247" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="I247" s="3" t="n">
         <v>265</v>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Sarratt</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="I247" s="3" t="n">
-        <v>249</v>
       </c>
     </row>
     <row r="248">
@@ -9162,7 +9162,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
@@ -9195,7 +9195,7 @@
         <v>266</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
@@ -9214,10 +9214,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="250">
@@ -9252,7 +9252,7 @@
         <v>216</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="251">
@@ -9284,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="252">
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="253">
@@ -9354,10 +9354,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="254">
@@ -9370,16 +9370,16 @@
         <v>271</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -9389,11 +9389,9 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>227</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -9404,17 +9402,17 @@
       <c r="B255" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="C255" s="5" t="n">
-        <v>336</v>
+      <c r="C255" s="4" t="n">
+        <v>306</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9424,10 +9422,10 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="256">
@@ -9437,19 +9435,19 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>268</v>
+        <v>274</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>336</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9459,11 +9457,9 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="I256" s="3" t="n">
-        <v>264</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9472,19 +9468,19 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
@@ -9494,32 +9490,32 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>263</v>
+        <v>300</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
@@ -9529,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9540,19 +9536,19 @@
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F259" s="3" t="n">
@@ -9573,19 +9569,19 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="C260" s="4" t="n">
-        <v>270</v>
+        <v>280</v>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>323</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Trevor Etienne</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F260" s="3" t="n">
@@ -9595,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9606,19 +9602,19 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Seth McGowan</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F261" s="3" t="n">
@@ -9628,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9639,19 +9635,19 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Seth McGowan</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F262" s="3" t="n">
@@ -9661,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9672,19 +9668,19 @@
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>282</v>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>306</v>
+        <v>283</v>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>346</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Jawhar Jordan</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F263" s="3" t="n">
@@ -9694,30 +9690,30 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A264" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="C264" s="5" t="n">
-        <v>344</v>
+        <v>287</v>
+      </c>
+      <c r="C264" s="10" t="n">
+        <v>185</v>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Jawhar Jordan</t>
+          <t>Trey Smack</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F264" s="3" t="n">
@@ -9727,30 +9723,32 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="I264" s="3" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="I264" s="3" t="n">
+        <v>208</v>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A265" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Jake Elliott</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F265" s="3" t="n">
@@ -9760,65 +9758,65 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I265" s="3" t="n">
-        <v>292</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="I265" s="3" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C266" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="I266" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>Trey Smack</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F266" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="I266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C267" s="10" t="n">
-        <v>187</v>
+        <v>290</v>
+      </c>
+      <c r="C267" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F267" s="3" t="n">
@@ -9828,10 +9826,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
     </row>
     <row r="268">
@@ -9841,19 +9839,19 @@
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Mike Gesicki</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F268" s="3" t="n">
@@ -9863,10 +9861,10 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>261</v>
+        <v>241</v>
       </c>
     </row>
     <row r="269">
@@ -9876,19 +9874,19 @@
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>Evan Engram</t>
+          <t>David Njoku</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F269" s="3" t="n">
@@ -9898,10 +9896,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="270">
@@ -9911,19 +9909,19 @@
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="C270" s="4" t="n">
-        <v>260</v>
+        <v>293</v>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>358</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F270" s="3" t="n">
@@ -9933,32 +9931,30 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="I270" s="3" t="n">
-        <v>257</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="I270" s="3" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="C271" s="5" t="n">
-        <v>359</v>
+        <v>294</v>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>255</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Andrei Iosivas</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F271" s="3" t="n">
@@ -9968,30 +9964,32 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I271" s="3" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C272" s="5" t="n">
-        <v>339</v>
+        <v>295</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>328</v>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Jake Tonges</t>
+          <t>Ashton Dulin</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F272" s="3" t="n">
@@ -10001,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
@@ -10034,10 +10032,10 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -1351,7 +1351,7 @@
         <v>31</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>23</v>
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>19</v>
@@ -1456,7 +1456,7 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>39</v>
@@ -1491,7 +1491,7 @@
         <v>33</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>25</v>
@@ -1806,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1841,7 +1841,7 @@
         <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>38</v>
@@ -1876,7 +1876,7 @@
         <v>21</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>32</v>
@@ -1911,7 +1911,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>44</v>
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>65</v>
@@ -2016,7 +2016,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>37</v>
@@ -2261,7 +2261,7 @@
         <v>30</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>35</v>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>54</v>
@@ -2436,7 +2436,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>51</v>
@@ -2471,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>61</v>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>49</v>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>60</v>
@@ -2611,7 +2611,7 @@
         <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>66</v>
@@ -2646,7 +2646,7 @@
         <v>11</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>45</v>
@@ -2716,7 +2716,7 @@
         <v>11</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>53</v>
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>62</v>
@@ -2786,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>76</v>
@@ -2821,7 +2821,7 @@
         <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>112</v>
@@ -2856,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>115</v>
@@ -2891,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>113</v>
@@ -2961,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>82</v>
@@ -2996,7 +2996,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>80</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>73</v>
@@ -3066,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>75</v>
@@ -3101,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>72</v>
@@ -3136,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>59</v>
@@ -3241,7 +3241,7 @@
         <v>15</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>50</v>
@@ -3276,7 +3276,7 @@
         <v>17</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>46</v>
@@ -3311,7 +3311,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>78</v>
@@ -3346,7 +3346,7 @@
         <v>4</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>87</v>
@@ -3381,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>79</v>
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>98</v>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>97</v>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>117</v>
@@ -3556,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>100</v>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>142</v>
@@ -3696,7 +3696,7 @@
         <v>4</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>81</v>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>86</v>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>140</v>
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>71</v>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>129</v>
@@ -3871,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3906,7 +3906,7 @@
         <v>6</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>69</v>
@@ -3941,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>102</v>
@@ -3976,7 +3976,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>144</v>
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>103</v>
@@ -4046,7 +4046,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>145</v>
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>121</v>
@@ -4116,7 +4116,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>74</v>
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>119</v>
@@ -4186,7 +4186,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>133</v>
@@ -4221,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>95</v>
@@ -4256,7 +4256,7 @@
         <v>4</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>83</v>
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>84</v>
@@ -4326,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>101</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>134</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>221</v>
@@ -4466,7 +4466,7 @@
         <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>110</v>
@@ -4501,7 +4501,7 @@
         <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>91</v>
@@ -4536,7 +4536,7 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>111</v>
@@ -4571,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>94</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>261</v>
@@ -4641,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>120</v>
@@ -4676,7 +4676,7 @@
         <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>106</v>
@@ -4711,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>185</v>
@@ -4746,7 +4746,7 @@
         <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>85</v>
@@ -4781,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>93</v>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>151</v>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>169</v>
@@ -4886,7 +4886,7 @@
         <v>2</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>89</v>
@@ -4921,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>126</v>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>162</v>
@@ -4991,7 +4991,7 @@
         <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>92</v>
@@ -5026,7 +5026,7 @@
         <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>109</v>
@@ -5061,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>114</v>
@@ -5096,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>125</v>
@@ -5131,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>128</v>
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>206</v>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>99</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>173</v>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>122</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>181</v>
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>96</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>190</v>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>191</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>171</v>
@@ -5516,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>157</v>
@@ -5551,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>139</v>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>220</v>
@@ -5656,7 +5656,7 @@
         <v>2</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>127</v>
@@ -5691,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>141</v>
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>130</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>138</v>
@@ -5831,7 +5831,7 @@
         <v>3</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>90</v>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>215</v>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>188</v>
@@ -5971,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>153</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>159</v>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>170</v>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>196</v>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>225</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>175</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>161</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>202</v>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>204</v>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>205</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>203</v>
@@ -6356,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>152</v>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>233</v>
@@ -6426,7 +6426,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>105</v>
@@ -6461,7 +6461,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>108</v>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>135</v>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>136</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>192</v>
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>107</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>167</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>298</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>149</v>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>179</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>150</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>165</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>155</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>255</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>187</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>244</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>182</v>
@@ -7056,7 +7056,7 @@
         <v>2</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>123</v>
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>201</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>172</v>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>249</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>275</v>
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>273</v>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>223</v>
@@ -7422,7 +7422,7 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I198" s="3" t="inlineStr"/>
     </row>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>212</v>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>214</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>232</v>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>176</v>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>186</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>174</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>180</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>199</v>
@@ -7839,8 +7839,8 @@
       <c r="B210" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C210" s="4" t="n">
-        <v>254</v>
+      <c r="C210" s="5" t="n">
+        <v>256</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I211" s="3" t="n">
         <v>254</v>
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>231</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>282</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I216" s="3" t="n">
         <v>197</v>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>230</v>
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>216</v>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>229</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I221" s="3" t="n">
         <v>253</v>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>284</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>207</v>
@@ -8365,7 +8365,7 @@
         <v>239</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>213</v>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>158</v>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I230" s="3" t="n">
         <v>277</v>
@@ -8573,7 +8573,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
     </row>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I233" s="3" t="n">
         <v>289</v>
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>195</v>
@@ -8851,7 +8851,7 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I240" s="3" t="n">
         <v>166</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I242" s="3" t="n">
         <v>222</v>
@@ -8984,67 +8984,65 @@
         </is>
       </c>
       <c r="B243" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Darren Waller</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="I243" s="3" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C243" s="4" t="n">
+      <c r="C244" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="D243" s="3" t="inlineStr">
+      <c r="D244" s="3" t="inlineStr">
         <is>
           <t>Oronde Gadsden</t>
         </is>
       </c>
-      <c r="E243" s="3" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="F243" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="I243" s="3" t="n">
+      <c r="F244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="I244" s="3" t="n">
         <v>226</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="I244" s="3" t="n">
-        <v>219</v>
       </c>
     </row>
     <row r="245">
@@ -9054,19 +9052,19 @@
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F245" s="3" t="n">
@@ -9076,10 +9074,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>291</v>
+        <v>219</v>
       </c>
     </row>
     <row r="246">
@@ -9089,19 +9087,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9111,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>228</v>
+        <v>291</v>
       </c>
     </row>
     <row r="247">
@@ -9124,66 +9122,68 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="C247" s="4" t="n">
+      <c r="C248" s="4" t="n">
         <v>283</v>
       </c>
-      <c r="D247" s="3" t="inlineStr">
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>Tyquan Thornton</t>
         </is>
       </c>
-      <c r="E247" s="3" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="F247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="3" t="n">
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="I247" s="3" t="n">
+      <c r="I248" s="3" t="n">
         <v>265</v>
       </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C248" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>Malik Davis</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="I248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -9192,67 +9192,65 @@
         </is>
       </c>
       <c r="B249" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Malik Davis</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="I249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="C249" s="4" t="n">
+      <c r="C250" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="D249" s="3" t="inlineStr">
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>Emanuel Wilson</t>
         </is>
       </c>
-      <c r="E249" s="3" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F249" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="I249" s="3" t="n">
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="I250" s="3" t="n">
         <v>278</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C250" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="I250" s="3" t="n">
-        <v>200</v>
       </c>
     </row>
     <row r="251">
@@ -9262,19 +9260,19 @@
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F251" s="3" t="n">
@@ -9284,10 +9282,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>227</v>
+        <v>200</v>
       </c>
     </row>
     <row r="252">
@@ -9297,19 +9295,19 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F252" s="3" t="n">
@@ -9319,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
     </row>
     <row r="253">
@@ -9332,66 +9330,68 @@
         </is>
       </c>
       <c r="B253" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="C253" s="4" t="n">
+      <c r="C254" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="D253" s="3" t="inlineStr">
+      <c r="D254" s="3" t="inlineStr">
         <is>
           <t>Deshaun Watson</t>
         </is>
       </c>
-      <c r="E253" s="3" t="inlineStr">
+      <c r="E254" s="3" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="F253" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="3" t="n">
+      <c r="F254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="I253" s="3" t="n">
+      <c r="I254" s="3" t="n">
         <v>247</v>
       </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>267</v>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>Jahan Dotson</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -9400,19 +9400,19 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9422,11 +9422,9 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>292</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -9435,19 +9433,19 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="C256" s="5" t="n">
-        <v>336</v>
+        <v>272</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>306</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9457,9 +9455,11 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I256" s="3" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9468,66 +9468,66 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>338</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>DeMario Douglas</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="I257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="C257" s="4" t="n">
+      <c r="C258" s="4" t="n">
         <v>291</v>
       </c>
-      <c r="D257" s="3" t="inlineStr">
+      <c r="D258" s="3" t="inlineStr">
         <is>
           <t>Devaughn Vele</t>
         </is>
       </c>
-      <c r="E257" s="3" t="inlineStr">
+      <c r="E258" s="3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F257" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" s="3" t="n">
+      <c r="F258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="I257" s="3" t="n">
+      <c r="I258" s="3" t="n">
         <v>300</v>
       </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="C258" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>Devin Singletary</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>NYG</t>
-        </is>
-      </c>
-      <c r="F258" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H258" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="I258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -9536,19 +9536,19 @@
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F259" s="3" t="n">
@@ -9558,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="C260" s="5" t="n">
-        <v>323</v>
+        <v>279</v>
+      </c>
+      <c r="C260" s="4" t="n">
+        <v>297</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F260" s="3" t="n">
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9602,19 +9602,19 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="C261" s="4" t="n">
-        <v>283</v>
+        <v>280</v>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>323</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Seth McGowan</t>
+          <t>Trevor Etienne</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F261" s="3" t="n">
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9635,19 +9635,19 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Seth McGowan</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F262" s="3" t="n">
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>171</v>
+        <v>259</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9668,54 +9668,54 @@
         </is>
       </c>
       <c r="B263" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Kendre Miller</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="I263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C263" s="5" t="n">
-        <v>346</v>
-      </c>
-      <c r="D263" s="3" t="inlineStr">
+      <c r="C264" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
         <is>
           <t>Jawhar Jordan</t>
         </is>
       </c>
-      <c r="E263" s="3" t="inlineStr">
+      <c r="E264" s="3" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="F263" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="I263" s="3" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="C264" s="10" t="n">
-        <v>185</v>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>Trey Smack</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
       <c r="F264" s="3" t="n">
         <v>0</v>
       </c>
@@ -9723,11 +9723,9 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="I264" s="3" t="n">
-        <v>208</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="12" t="inlineStr">
@@ -9736,66 +9734,66 @@
         </is>
       </c>
       <c r="B265" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C265" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Trey Smack</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="C265" s="4" t="n">
+      <c r="C266" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="D265" s="3" t="inlineStr">
+      <c r="D266" s="3" t="inlineStr">
         <is>
           <t>Jake Elliott</t>
         </is>
       </c>
-      <c r="E265" s="3" t="inlineStr">
+      <c r="E266" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="F265" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="I265" s="3" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C266" s="4" t="n">
+      <c r="F266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F266" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="I266" s="3" t="n">
-        <v>242</v>
-      </c>
+      <c r="I266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="8" t="inlineStr">
@@ -9804,19 +9802,19 @@
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>280</v>
+        <v>221</v>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Mike Gesicki</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F267" s="3" t="n">
@@ -9826,10 +9824,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
     </row>
     <row r="268">
@@ -9839,19 +9837,19 @@
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Evan Engram</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F268" s="3" t="n">
@@ -9861,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="269">
@@ -9874,19 +9872,19 @@
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F269" s="3" t="n">
@@ -9896,10 +9894,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="I269" s="3" t="n">
         <v>241</v>
-      </c>
-      <c r="I269" s="3" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="270">
@@ -9909,54 +9907,56 @@
         </is>
       </c>
       <c r="B270" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="C270" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>David Njoku</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I270" s="3" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="C270" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
+      <c r="C271" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
         <is>
           <t>Michael Mayer</t>
         </is>
       </c>
-      <c r="E270" s="3" t="inlineStr">
+      <c r="E271" s="3" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="F270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H270" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I270" s="3" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C271" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F271" s="3" t="n">
         <v>0</v>
       </c>
@@ -9964,11 +9964,9 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="I271" s="3" t="n">
-        <v>264</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
@@ -9977,64 +9975,99 @@
         </is>
       </c>
       <c r="B272" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="C272" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
+      <c r="C273" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>Ashton Dulin</t>
         </is>
       </c>
-      <c r="E272" s="3" t="inlineStr">
+      <c r="E273" s="3" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="F272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="I272" s="3" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="11" t="inlineStr">
+      <c r="F273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B273" s="3" t="n">
+      <c r="B274" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C273" s="4" t="n">
+      <c r="C274" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="D273" s="3" t="inlineStr">
+      <c r="D274" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E273" s="3" t="inlineStr">
+      <c r="E274" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F273" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" s="3" t="n">
+      <c r="F274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="I273" s="3" t="n">
+      <c r="I274" s="3" t="n">
         <v>246</v>
       </c>
     </row>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I274"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,7 +759,7 @@
         <v>6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -791,10 +791,10 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -969,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1074,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -1351,7 +1351,7 @@
         <v>31</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>23</v>
@@ -1386,7 +1386,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>19</v>
@@ -1456,10 +1456,10 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
@@ -1491,7 +1491,7 @@
         <v>33</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>25</v>
@@ -1506,30 +1506,30 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>42</v>
+      <c r="C29" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>19</v>
+      <c r="G29" s="10" t="n">
+        <v>36</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -1541,30 +1541,30 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>21</v>
+      <c r="C30" s="7" t="n">
+        <v>42</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>34</v>
+      <c r="G30" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1647,29 +1647,29 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1704,7 +1704,7 @@
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
@@ -1739,7 +1739,7 @@
         <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -1806,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1822,29 +1822,29 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Travis Etienne</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>18</v>
+      <c r="G38" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -1857,29 +1857,29 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Travis Etienne</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>65</v>
@@ -2016,10 +2016,10 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -2054,7 +2054,7 @@
         <v>43</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
@@ -2159,7 +2159,7 @@
         <v>47</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -2194,7 +2194,7 @@
         <v>46</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
@@ -2207,29 +2207,29 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -2261,10 +2261,10 @@
         <v>30</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>54</v>
@@ -2311,30 +2311,30 @@
       <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="7" t="n">
-        <v>96</v>
+      <c r="C52" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="5" t="n">
-        <v>2</v>
+      <c r="G52" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -2347,29 +2347,29 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="10" t="n">
-        <v>15</v>
+      <c r="G53" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>53</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -2416,30 +2416,30 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="4" t="n">
-        <v>48</v>
+      <c r="C55" s="7" t="n">
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>14</v>
+      <c r="G55" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
@@ -2471,10 +2471,10 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -2509,7 +2509,7 @@
         <v>56</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58">
@@ -2544,7 +2544,7 @@
         <v>55</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59">
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -2611,7 +2611,7 @@
         <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>66</v>
@@ -2646,7 +2646,7 @@
         <v>11</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>45</v>
@@ -2661,30 +2661,30 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>69</v>
+      <c r="C62" s="9" t="n">
+        <v>53</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
@@ -2696,30 +2696,30 @@
       <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C63" s="9" t="n">
-        <v>53</v>
+      <c r="C63" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64">
@@ -2732,29 +2732,29 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>63</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -2767,29 +2767,29 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66">
@@ -2821,10 +2821,10 @@
         <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
@@ -2856,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
@@ -2891,10 +2891,10 @@
         <v>1</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69">
@@ -2961,10 +2961,10 @@
         <v>4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71">
@@ -2976,30 +2976,30 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="5" t="n">
-        <v>77</v>
+      <c r="C71" s="9" t="n">
+        <v>46</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>5</v>
+      <c r="G71" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72">
@@ -3031,10 +3031,10 @@
         <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73">
@@ -3066,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>75</v>
@@ -3101,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>72</v>
@@ -3136,10 +3136,10 @@
         <v>8</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76">
@@ -3174,7 +3174,7 @@
         <v>77</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77">
@@ -3206,10 +3206,10 @@
         <v>9</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78">
@@ -3221,30 +3221,30 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="9" t="n">
-        <v>46</v>
+      <c r="C78" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="9" t="n">
-        <v>15</v>
+      <c r="G78" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79">
@@ -3276,10 +3276,10 @@
         <v>17</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
@@ -3311,7 +3311,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>78</v>
@@ -3346,10 +3346,10 @@
         <v>4</v>
       </c>
       <c r="H81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="I81" s="3" t="n">
         <v>86</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>87</v>
       </c>
     </row>
     <row r="82">
@@ -3381,10 +3381,10 @@
         <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>98</v>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>97</v>
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87">
@@ -3556,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>100</v>
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>142</v>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>143</v>
@@ -3699,7 +3699,7 @@
         <v>88</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92">
@@ -3731,10 +3731,10 @@
         <v>4</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>140</v>
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>71</v>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>129</v>
@@ -3871,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3886,30 +3886,30 @@
       <c r="B97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="9" t="n">
-        <v>68</v>
+      <c r="C97" s="4" t="n">
+        <v>99</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98">
@@ -3921,30 +3921,30 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="4" t="n">
-        <v>99</v>
+      <c r="C98" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99">
@@ -3976,7 +3976,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>144</v>
@@ -3991,12 +3991,12 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="4" t="n">
-        <v>127</v>
+      <c r="C100" s="9" t="n">
+        <v>80</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
@@ -4027,29 +4027,29 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>145</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102">
@@ -4061,30 +4061,30 @@
       <c r="B102" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C102" s="4" t="n">
-        <v>125</v>
+      <c r="C102" s="9" t="n">
+        <v>81</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103">
@@ -4096,30 +4096,30 @@
       <c r="B103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="9" t="n">
-        <v>81</v>
+      <c r="C103" s="4" t="n">
+        <v>125</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104">
@@ -4151,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105">
@@ -4186,10 +4186,10 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106">
@@ -4202,16 +4202,16 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -4221,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="107">
@@ -4236,30 +4236,30 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="9" t="n">
-        <v>80</v>
+      <c r="C107" s="10" t="n">
+        <v>101</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="108">
@@ -4272,16 +4272,16 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
@@ -4307,16 +4307,16 @@
         <v>108</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -4326,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110">
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>154</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>134</v>
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113">
@@ -4466,10 +4466,10 @@
         <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114">
@@ -4482,29 +4482,29 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115">
@@ -4517,16 +4517,16 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -4536,10 +4536,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
     </row>
     <row r="116">
@@ -4551,17 +4551,17 @@
       <c r="B116" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C116" s="9" t="n">
-        <v>101</v>
+      <c r="C116" s="4" t="n">
+        <v>116</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -4571,10 +4571,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117">
@@ -4586,30 +4586,30 @@
       <c r="B117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C117" s="7" t="n">
-        <v>279</v>
+      <c r="C117" s="4" t="n">
+        <v>119</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>261</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118">
@@ -4621,17 +4621,17 @@
       <c r="B118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C118" s="4" t="n">
-        <v>119</v>
+      <c r="C118" s="10" t="n">
+        <v>108</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="119">
@@ -4656,30 +4656,30 @@
       <c r="B119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="10" t="n">
-        <v>108</v>
+      <c r="C119" s="7" t="n">
+        <v>279</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>106</v>
+        <v>262</v>
       </c>
     </row>
     <row r="120">
@@ -4711,10 +4711,10 @@
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121">
@@ -4727,29 +4727,29 @@
         <v>120</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="122">
@@ -4781,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>93</v>
@@ -4796,30 +4796,30 @@
       <c r="B123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="4" t="n">
-        <v>145</v>
+      <c r="C123" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
     <row r="124">
@@ -4832,29 +4832,29 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="125">
@@ -4866,30 +4866,30 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="4" t="n">
-        <v>97</v>
+      <c r="C125" s="7" t="n">
+        <v>158</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
     </row>
     <row r="126">
@@ -4901,30 +4901,30 @@
       <c r="B126" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="5" t="n">
-        <v>135</v>
+      <c r="C126" s="10" t="n">
+        <v>92</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="127">
@@ -4936,30 +4936,30 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="7" t="n">
-        <v>158</v>
+      <c r="C127" s="10" t="n">
+        <v>94</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128">
@@ -4971,30 +4971,30 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="10" t="n">
-        <v>92</v>
+      <c r="C128" s="5" t="n">
+        <v>135</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129">
@@ -5026,7 +5026,7 @@
         <v>4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>109</v>
@@ -5061,10 +5061,10 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131">
@@ -5076,30 +5076,30 @@
       <c r="B131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="4" t="n">
-        <v>123</v>
+      <c r="C131" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="132">
@@ -5112,16 +5112,16 @@
         <v>131</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -5131,10 +5131,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="133">
@@ -5146,30 +5146,30 @@
       <c r="B133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C133" s="7" t="n">
-        <v>202</v>
+      <c r="C133" s="4" t="n">
+        <v>136</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>206</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134">
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>99</v>
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="136">
@@ -5271,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137">
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>181</v>
@@ -5321,30 +5321,30 @@
       <c r="B138" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C138" s="9" t="n">
-        <v>102</v>
+      <c r="C138" s="4" t="n">
+        <v>176</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139">
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="140">
@@ -5391,30 +5391,30 @@
       <c r="B140" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C140" s="4" t="n">
-        <v>204</v>
+      <c r="C140" s="9" t="n">
+        <v>128</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>191</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141">
@@ -5446,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="142">
@@ -5461,27 +5461,27 @@
       <c r="B142" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C142" s="4" t="n">
-        <v>197</v>
+      <c r="C142" s="9" t="n">
+        <v>117</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>171</v>
@@ -5497,29 +5497,29 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144">
@@ -5566,30 +5566,30 @@
       <c r="B145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C145" s="7" t="n">
-        <v>159</v>
+      <c r="C145" s="10" t="n">
+        <v>106</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>160</v>
+        <v>126</v>
       </c>
     </row>
     <row r="146">
@@ -5602,16 +5602,16 @@
         <v>145</v>
       </c>
       <c r="C146" s="7" t="n">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -5621,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="147">
@@ -5636,30 +5636,30 @@
       <c r="B147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="10" t="n">
-        <v>106</v>
+      <c r="C147" s="7" t="n">
+        <v>159</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="148">
@@ -5671,30 +5671,30 @@
       <c r="B148" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C148" s="4" t="n">
-        <v>148</v>
+      <c r="C148" s="7" t="n">
+        <v>225</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
     </row>
     <row r="149">
@@ -5707,16 +5707,16 @@
         <v>148</v>
       </c>
       <c r="C149" s="7" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -5726,10 +5726,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="150">
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>130</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>138</v>
@@ -5811,30 +5811,30 @@
       <c r="B152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="9" t="n">
-        <v>87</v>
+      <c r="C152" s="5" t="n">
+        <v>190</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>90</v>
+        <v>198</v>
       </c>
     </row>
     <row r="153">
@@ -5846,30 +5846,30 @@
       <c r="B153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="5" t="n">
-        <v>257</v>
+      <c r="C153" s="4" t="n">
+        <v>148</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>217</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154">
@@ -5901,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="155">
@@ -5917,16 +5917,16 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156">
@@ -5952,29 +5952,29 @@
         <v>155</v>
       </c>
       <c r="C156" s="9" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
     </row>
     <row r="157">
@@ -5987,16 +5987,16 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>159</v>
+        <v>214</v>
       </c>
     </row>
     <row r="158">
@@ -6022,29 +6022,29 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="159">
@@ -6057,16 +6057,16 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="160">
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="161">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162">
@@ -6181,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163">
@@ -6197,16 +6197,16 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="164">
@@ -6232,11 +6232,11 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="165">
@@ -6266,17 +6266,17 @@
       <c r="B165" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C165" s="5" t="n">
-        <v>200</v>
+      <c r="C165" s="4" t="n">
+        <v>173</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
@@ -6286,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="166">
@@ -6302,16 +6302,16 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>199</v>
+        <v>257</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="167">
@@ -6336,30 +6336,30 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="9" t="n">
-        <v>128</v>
+      <c r="C167" s="5" t="n">
+        <v>208</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="168">
@@ -6371,17 +6371,17 @@
       <c r="B168" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="5" t="n">
-        <v>269</v>
+      <c r="C168" s="4" t="n">
+        <v>162</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>233</v>
+        <v>158</v>
       </c>
     </row>
     <row r="169">
@@ -6406,30 +6406,30 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="4" t="n">
-        <v>144</v>
+      <c r="C169" s="5" t="n">
+        <v>269</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>105</v>
+        <v>196</v>
       </c>
     </row>
     <row r="170">
@@ -6461,7 +6461,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>108</v>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>135</v>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>136</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>192</v>
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>107</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176">
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>298</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>149</v>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>179</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>150</v>
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="181">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>155</v>
@@ -6861,17 +6861,17 @@
       <c r="B182" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="C182" s="5" t="n">
-        <v>271</v>
+      <c r="C182" s="4" t="n">
+        <v>210</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>255</v>
+        <v>191</v>
       </c>
     </row>
     <row r="183">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>187</v>
@@ -6932,16 +6932,16 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="185">
@@ -6966,17 +6966,17 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>238</v>
+      <c r="C185" s="4" t="n">
+        <v>178</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>244</v>
+        <v>157</v>
       </c>
     </row>
     <row r="186">
@@ -7002,16 +7002,16 @@
         <v>197</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="187">
@@ -7059,7 +7059,7 @@
         <v>161</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="188">
@@ -7071,17 +7071,17 @@
       <c r="B188" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C188" s="5" t="n">
-        <v>231</v>
+      <c r="C188" s="4" t="n">
+        <v>194</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>201</v>
+        <v>173</v>
       </c>
     </row>
     <row r="189">
@@ -7107,16 +7107,16 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -7126,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="190">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
     <row r="191">
@@ -7174,19 +7174,19 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C191" s="5" t="n">
-        <v>256</v>
+        <v>203</v>
+      </c>
+      <c r="C191" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -7196,10 +7196,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>249</v>
+        <v>184</v>
       </c>
     </row>
     <row r="192">
@@ -7209,19 +7209,19 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
     </row>
     <row r="193">
@@ -7246,17 +7246,17 @@
       <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C193" s="10" t="n">
-        <v>171</v>
+      <c r="C193" s="4" t="n">
+        <v>191</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>183</v>
+        <v>206</v>
       </c>
     </row>
     <row r="194">
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="196">
@@ -7352,16 +7352,16 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -7371,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
     </row>
     <row r="197">
@@ -7386,17 +7386,17 @@
       <c r="B197" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C197" s="5" t="n">
-        <v>286</v>
+      <c r="C197" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7406,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>276</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198">
@@ -7422,16 +7422,16 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -7441,9 +7441,11 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="I198" s="3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -7455,16 +7457,16 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -7474,11 +7476,9 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="I199" s="3" t="n">
-        <v>252</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7489,17 +7489,17 @@
       <c r="B200" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C200" s="4" t="n">
-        <v>210</v>
+      <c r="C200" s="5" t="n">
+        <v>271</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Jordan James</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -7509,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>212</v>
+        <v>267</v>
       </c>
     </row>
     <row r="201">
@@ -7547,7 +7547,7 @@
         <v>228</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="202">
@@ -7559,17 +7559,17 @@
       <c r="B202" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="C202" s="4" t="n">
-        <v>240</v>
+      <c r="C202" s="5" t="n">
+        <v>272</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F202" s="3" t="n">
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
     </row>
     <row r="203">
@@ -7617,7 +7617,7 @@
         <v>239</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="204">
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>176</v>
@@ -7684,10 +7684,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="206">
@@ -7700,16 +7700,16 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7719,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="207">
@@ -7735,16 +7735,16 @@
         <v>219</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>180</v>
+        <v>228</v>
       </c>
     </row>
     <row r="208">
@@ -7770,16 +7770,16 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
     </row>
     <row r="209">
@@ -7805,16 +7805,16 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="210">
@@ -7840,16 +7840,16 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>287</v>
@@ -7874,17 +7874,17 @@
       <c r="B211" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C211" s="5" t="n">
-        <v>272</v>
+      <c r="C211" s="4" t="n">
+        <v>209</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7894,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>254</v>
+        <v>233</v>
       </c>
     </row>
     <row r="212">
@@ -7910,16 +7910,16 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7929,11 +7929,9 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="I212" s="3" t="n">
-        <v>231</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7945,16 +7943,16 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Ty Johnson</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
@@ -7964,11 +7962,9 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="I213" s="3" t="n">
-        <v>281</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="I213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7980,16 +7976,16 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Ollie Gordon</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -7999,10 +7995,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="215">
@@ -8014,17 +8010,17 @@
       <c r="B215" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="C215" s="5" t="n">
-        <v>285</v>
+      <c r="C215" s="4" t="n">
+        <v>236</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -8034,10 +8030,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="216">
@@ -8049,12 +8045,12 @@
       <c r="B216" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C216" s="10" t="n">
-        <v>172</v>
+      <c r="C216" s="5" t="n">
+        <v>297</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -8069,10 +8065,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>197</v>
+        <v>280</v>
       </c>
     </row>
     <row r="217">
@@ -8085,11 +8081,11 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -8104,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="218">
@@ -8120,16 +8116,16 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8139,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>230</v>
+        <v>300</v>
       </c>
     </row>
     <row r="219">
@@ -8154,17 +8150,17 @@
       <c r="B219" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C219" s="4" t="n">
-        <v>201</v>
+      <c r="C219" s="5" t="n">
+        <v>268</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8174,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>216</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220">
@@ -8189,17 +8185,17 @@
       <c r="B220" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C220" s="4" t="n">
-        <v>254</v>
+      <c r="C220" s="5" t="n">
+        <v>283</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -8209,10 +8205,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>229</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221">
@@ -8224,17 +8220,17 @@
       <c r="B221" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C221" s="4" t="n">
-        <v>266</v>
+      <c r="C221" s="5" t="n">
+        <v>286</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -8244,10 +8240,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>253</v>
+        <v>277</v>
       </c>
     </row>
     <row r="222">
@@ -8260,16 +8256,16 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -8279,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>284</v>
+        <v>204</v>
       </c>
     </row>
     <row r="223">
@@ -8314,10 +8310,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224">
@@ -8349,10 +8345,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="225">
@@ -8364,17 +8360,17 @@
       <c r="B225" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C225" s="5" t="n">
-        <v>289</v>
+      <c r="C225" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Adam Randall</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -8384,9 +8380,11 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="I225" s="3" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>189</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8398,16 +8396,16 @@
         <v>240</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -8417,10 +8415,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>213</v>
+        <v>245</v>
       </c>
     </row>
     <row r="227">
@@ -8433,16 +8431,16 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>LeQuint Allen</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -8452,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="228">
@@ -8467,17 +8465,17 @@
       <c r="B228" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C228" s="10" t="n">
-        <v>178</v>
+      <c r="C228" s="4" t="n">
+        <v>255</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -8487,10 +8485,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>158</v>
+        <v>288</v>
       </c>
     </row>
     <row r="229">
@@ -8502,17 +8500,17 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="4" t="n">
-        <v>203</v>
+      <c r="C229" s="5" t="n">
+        <v>287</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -8522,11 +8520,9 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="I229" s="3" t="n">
-        <v>189</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="I229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8537,17 +8533,17 @@
       <c r="B230" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C230" s="5" t="n">
-        <v>288</v>
+      <c r="C230" s="4" t="n">
+        <v>273</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -8557,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>277</v>
+        <v>213</v>
       </c>
     </row>
     <row r="231">
@@ -8573,16 +8569,16 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Ty Johnson</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -8592,9 +8588,11 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I231" s="3" t="inlineStr"/>
+        <v>270</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8606,16 +8604,16 @@
         <v>246</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -8625,10 +8623,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="233">
@@ -8640,17 +8638,17 @@
       <c r="B233" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="C233" s="5" t="n">
-        <v>299</v>
+      <c r="C233" s="4" t="n">
+        <v>211</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -8660,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>289</v>
+        <v>215</v>
       </c>
     </row>
     <row r="234">
@@ -8676,16 +8674,16 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -8695,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="235">
@@ -8710,30 +8708,30 @@
       <c r="B235" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C235" s="4" t="n">
+      <c r="C235" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="I235" s="3" t="n">
         <v>268</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>247</v>
-      </c>
-      <c r="I235" s="3" t="n">
-        <v>290</v>
       </c>
     </row>
     <row r="236">
@@ -8746,16 +8744,16 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -8765,10 +8763,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>195</v>
+        <v>290</v>
       </c>
     </row>
     <row r="237">
@@ -8803,7 +8801,7 @@
         <v>255</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238">
@@ -8816,16 +8814,16 @@
         <v>252</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8835,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>288</v>
+        <v>232</v>
       </c>
     </row>
     <row r="239">
@@ -8850,17 +8848,17 @@
       <c r="B239" s="3" t="n">
         <v>253</v>
       </c>
-      <c r="C239" s="5" t="n">
-        <v>358</v>
+      <c r="C239" s="4" t="n">
+        <v>222</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8870,9 +8868,11 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="I239" s="3" t="inlineStr"/>
+        <v>217</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="241">
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="243">
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
     </row>
@@ -9020,16 +9020,16 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F244" s="3" t="n">
@@ -9039,10 +9039,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>226</v>
+        <v>244</v>
       </c>
     </row>
     <row r="245">
@@ -9054,12 +9054,12 @@
       <c r="B245" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C245" s="4" t="n">
-        <v>222</v>
+      <c r="C245" s="5" t="n">
+        <v>306</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -9074,10 +9074,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246">
@@ -9087,19 +9087,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I246" s="3" t="n">
         <v>252</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>291</v>
       </c>
     </row>
     <row r="247">
@@ -9122,19 +9122,19 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F247" s="3" t="n">
@@ -9144,32 +9144,32 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>228</v>
+        <v>291</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F248" s="3" t="n">
@@ -9179,32 +9179,32 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C249" s="5" t="n">
-        <v>312</v>
+        <v>267</v>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>218</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F249" s="3" t="n">
@@ -9214,30 +9214,32 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I249" s="3" t="inlineStr"/>
+        <v>215</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F250" s="3" t="n">
@@ -9247,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>278</v>
+        <v>199</v>
       </c>
     </row>
     <row r="251">
@@ -9260,19 +9262,19 @@
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F251" s="3" t="n">
@@ -9282,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="252">
@@ -9295,19 +9297,19 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F252" s="3" t="n">
@@ -9317,32 +9319,32 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>237</v>
+        <v>300</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F253" s="3" t="n">
@@ -9352,32 +9354,32 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>245</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>252</v>
+        <v>272</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>328</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Ashton Dulin</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -9387,11 +9389,9 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>247</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="I254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -9400,19 +9400,19 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9422,9 +9422,11 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="I255" s="3" t="inlineStr"/>
+        <v>272</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>276</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -9433,19 +9435,19 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>306</v>
+        <v>274</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>339</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9455,11 +9457,9 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="I256" s="3" t="n">
-        <v>292</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9468,19 +9468,19 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
@@ -9490,30 +9490,30 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
@@ -9523,11 +9523,9 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="I258" s="3" t="n">
-        <v>300</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="I258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -9558,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9569,7 +9567,7 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C260" s="4" t="n">
         <v>297</v>
@@ -9591,7 +9589,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9602,10 +9600,10 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9624,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9635,7 +9633,7 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C262" s="4" t="n">
         <v>283</v>
@@ -9668,10 +9666,10 @@
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9690,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9701,157 +9699,157 @@
         </is>
       </c>
       <c r="B264" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Jawhar Jordan</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C264" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>Jawhar Jordan</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="I264" s="3" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="12" t="inlineStr">
+      <c r="C265" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Kaleb Johnson</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="I265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>261</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Malachi Fields</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="I266" s="3" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B265" s="3" t="n">
+      <c r="B267" s="3" t="n">
         <v>287</v>
       </c>
-      <c r="C265" s="10" t="n">
+      <c r="C267" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="D265" s="3" t="inlineStr">
+      <c r="D267" s="3" t="inlineStr">
         <is>
           <t>Trey Smack</t>
         </is>
       </c>
-      <c r="E265" s="3" t="inlineStr">
+      <c r="E267" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F265" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="I265" s="3" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="12" t="inlineStr">
+      <c r="F267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="12" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B266" s="3" t="n">
+      <c r="B268" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="C266" s="4" t="n">
+      <c r="C268" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="D266" s="3" t="inlineStr">
+      <c r="D268" s="3" t="inlineStr">
         <is>
           <t>Jake Elliott</t>
         </is>
       </c>
-      <c r="E266" s="3" t="inlineStr">
+      <c r="E268" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="F266" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="I266" s="3" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C267" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F267" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H267" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="I267" s="3" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C268" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F268" s="3" t="n">
         <v>0</v>
       </c>
@@ -9859,11 +9857,9 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I268" s="3" t="n">
-        <v>262</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="8" t="inlineStr">
@@ -9872,7 +9868,7 @@
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C269" s="4" t="n">
         <v>233</v>
@@ -9897,7 +9893,7 @@
         <v>223</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="270">
@@ -9907,7 +9903,7 @@
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C270" s="4" t="n">
         <v>260</v>
@@ -9932,7 +9928,7 @@
         <v>240</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="271">
@@ -9942,133 +9938,170 @@
         </is>
       </c>
       <c r="B271" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Oronde Gadsden</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="C271" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="D271" s="3" t="inlineStr">
+      <c r="C273" s="5" t="n">
+        <v>362</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>Michael Mayer</t>
         </is>
       </c>
-      <c r="E271" s="3" t="inlineStr">
+      <c r="E273" s="3" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="F271" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="I271" s="3" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="inlineStr">
+      <c r="F273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="B272" s="3" t="n">
+      <c r="B274" s="3" t="n">
         <v>294</v>
       </c>
-      <c r="C272" s="4" t="n">
+      <c r="C274" s="4" t="n">
         <v>255</v>
       </c>
-      <c r="D272" s="3" t="inlineStr">
+      <c r="D274" s="3" t="inlineStr">
         <is>
           <t>Andrei Iosivas</t>
         </is>
       </c>
-      <c r="E272" s="3" t="inlineStr">
+      <c r="E274" s="3" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="F272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="I272" s="3" t="n">
+      <c r="F274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="I274" s="3" t="n">
         <v>264</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>329</v>
-      </c>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>Ashton Dulin</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="F273" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="I273" s="3" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="11" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B274" s="3" t="n">
+      <c r="B275" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C274" s="4" t="n">
+      <c r="C275" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="D274" s="3" t="inlineStr">
+      <c r="D275" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E274" s="3" t="inlineStr">
+      <c r="E275" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" s="3" t="n">
+      <c r="F275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="I274" s="3" t="n">
-        <v>246</v>
+      <c r="I275" s="3" t="n">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>54</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>5</v>
@@ -737,7 +737,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>6</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -981,30 +981,30 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>24</v>
+      <c r="C14" s="4" t="n">
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>32</v>
+      <c r="G14" s="5" t="n">
+        <v>40</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1051,30 +1051,30 @@
       <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>17</v>
+      <c r="C16" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>38</v>
+      <c r="G16" s="7" t="n">
+        <v>31</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1121,8 +1121,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>41</v>
+      <c r="C18" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
       <c r="F18" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>19</v>
+      <c r="G18" s="5" t="n">
+        <v>29</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1192,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1208,13 +1208,13 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1249,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1296,8 +1296,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>26</v>
+      <c r="C23" s="7" t="n">
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1312,14 +1312,14 @@
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>30</v>
+      <c r="G23" s="7" t="n">
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -1332,7 +1332,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1348,13 +1348,13 @@
         <v>32</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1424,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1436,30 +1436,30 @@
       <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>34</v>
+      <c r="C27" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>23</v>
+      <c r="G27" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1471,30 +1471,30 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>22</v>
+      <c r="C28" s="5" t="n">
+        <v>35</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>33</v>
+      <c r="G28" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1506,30 +1506,30 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>19</v>
+      <c r="C29" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -1541,30 +1541,30 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>42</v>
+      <c r="C30" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>19</v>
+      <c r="G30" s="10" t="n">
+        <v>36</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1577,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1669,7 +1669,7 @@
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1697,14 +1697,14 @@
       <c r="F34" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>24</v>
+      <c r="G34" s="10" t="n">
+        <v>30</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1732,14 +1732,14 @@
       <c r="F35" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>29</v>
+      <c r="G35" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -1771,10 +1771,10 @@
         <v>28</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
@@ -1787,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>22</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1822,7 +1822,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>35</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -1879,7 +1879,7 @@
         <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -1892,7 +1892,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1961,8 +1961,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>64</v>
+      <c r="C42" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>7</v>
+      <c r="G42" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43">
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="10" t="n">
-        <v>31</v>
+      <c r="C43" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>41</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -2031,8 +2031,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="5" t="n">
-        <v>51</v>
+      <c r="C44" s="7" t="n">
+        <v>57</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47">
@@ -2136,8 +2136,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="9" t="n">
-        <v>30</v>
+      <c r="C47" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2152,14 +2152,14 @@
       <c r="F47" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G47" s="9" t="n">
-        <v>27</v>
+      <c r="G47" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>35</v>
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         <v>13</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
@@ -2312,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
         <v>12</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2366,10 +2366,10 @@
         <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -2401,10 +2401,10 @@
         <v>13</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55">
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         <v>10</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>87</v>
@@ -2471,10 +2471,10 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -2487,7 +2487,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         <v>10</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>51</v>
@@ -2541,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -2592,7 +2592,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>66</v>
@@ -2627,7 +2627,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="9" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
@@ -2661,8 +2661,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>53</v>
+      <c r="C62" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>61</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
@@ -2697,7 +2697,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>62</v>
@@ -2732,7 +2732,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         <v>7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>69</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2817,14 +2817,14 @@
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>3</v>
+      <c r="G66" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2852,14 +2852,14 @@
       <c r="F67" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="4" t="n">
-        <v>1</v>
+      <c r="G67" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68">
@@ -2871,30 +2871,30 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="7" t="n">
-        <v>122</v>
+      <c r="C68" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69">
@@ -2907,16 +2907,16 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Marvin Harrison</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -2926,10 +2926,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
@@ -2941,30 +2941,30 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="5" t="n">
-        <v>78</v>
+      <c r="C70" s="9" t="n">
+        <v>47</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G70" s="4" t="n">
-        <v>4</v>
+      <c r="G70" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -2976,30 +2976,30 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="9" t="n">
-        <v>46</v>
+      <c r="C71" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>15</v>
+      <c r="G71" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72">
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73">
@@ -3047,7 +3047,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>69</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3081,8 +3081,8 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>70</v>
+      <c r="C74" s="10" t="n">
+        <v>69</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75">
@@ -3116,8 +3116,8 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="10" t="n">
-        <v>61</v>
+      <c r="C75" s="4" t="n">
+        <v>64</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3133,13 +3133,13 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76">
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3168,13 +3168,13 @@
         <v>5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77">
@@ -3186,8 +3186,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>59</v>
+      <c r="C77" s="10" t="n">
+        <v>54</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78">
@@ -3221,30 +3221,30 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="4" t="n">
-        <v>77</v>
+      <c r="C78" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>92</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79">
@@ -3256,12 +3256,12 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="9" t="n">
-        <v>45</v>
+      <c r="C79" s="4" t="n">
+        <v>73</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3272,14 +3272,14 @@
       <c r="F79" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>17</v>
+      <c r="G79" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
@@ -3291,30 +3291,30 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="10" t="n">
-        <v>58</v>
+      <c r="C80" s="5" t="n">
+        <v>83</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81">
@@ -3326,30 +3326,30 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="5" t="n">
-        <v>86</v>
+      <c r="C81" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
@@ -3361,12 +3361,12 @@
       <c r="B82" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C82" s="4" t="n">
-        <v>76</v>
+      <c r="C82" s="7" t="n">
+        <v>140</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3378,13 +3378,13 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83">
@@ -3397,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -3432,7 +3432,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3467,7 +3467,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>85</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86">
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3518,13 +3518,13 @@
         <v>4</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87">
@@ -3537,7 +3537,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88">
@@ -3572,7 +3572,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3607,16 +3607,16 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90">
@@ -3641,30 +3641,30 @@
       <c r="B90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="7" t="n">
-        <v>149</v>
+      <c r="C90" s="4" t="n">
+        <v>85</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
@@ -3676,30 +3676,30 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="4" t="n">
-        <v>79</v>
+      <c r="C91" s="7" t="n">
+        <v>137</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92">
@@ -3712,29 +3712,29 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93">
@@ -3747,29 +3747,29 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>92</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94">
@@ -3782,7 +3782,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96">
@@ -3874,7 +3874,7 @@
         <v>91</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97">
@@ -3887,7 +3887,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98">
@@ -3921,8 +3921,8 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="9" t="n">
-        <v>74</v>
+      <c r="C98" s="10" t="n">
+        <v>92</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>84</v>
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100">
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101">
@@ -4027,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         <v>2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102">
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="9" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4078,13 +4078,13 @@
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
@@ -4096,8 +4096,8 @@
       <c r="B103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="4" t="n">
-        <v>125</v>
+      <c r="C103" s="10" t="n">
+        <v>97</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
@@ -4113,13 +4113,13 @@
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>99</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104">
@@ -4131,8 +4131,8 @@
       <c r="B104" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C104" s="4" t="n">
-        <v>103</v>
+      <c r="C104" s="10" t="n">
+        <v>98</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105">
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,10 +4186,10 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106">
@@ -4202,7 +4202,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -4221,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107">
@@ -4236,8 +4236,8 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="10" t="n">
-        <v>101</v>
+      <c r="C107" s="4" t="n">
+        <v>111</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
         <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108">
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>85</v>
@@ -4306,8 +4306,8 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="9" t="n">
-        <v>90</v>
+      <c r="C109" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110">
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111">
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112">
@@ -4412,7 +4412,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="113">
@@ -4447,16 +4447,16 @@
         <v>112</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -4466,10 +4466,10 @@
         <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>111</v>
+        <v>93</v>
       </c>
     </row>
     <row r="114">
@@ -4481,30 +4481,30 @@
       <c r="B114" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C114" s="4" t="n">
-        <v>107</v>
+      <c r="C114" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115">
@@ -4516,30 +4516,30 @@
       <c r="B115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C115" s="4" t="n">
-        <v>97</v>
+      <c r="C115" s="7" t="n">
+        <v>170</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
     </row>
     <row r="116">
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4568,13 +4568,13 @@
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117">
@@ -4587,7 +4587,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         <v>2</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118">
@@ -4621,8 +4621,8 @@
       <c r="B118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C118" s="10" t="n">
-        <v>108</v>
+      <c r="C118" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119">
@@ -4676,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120">
@@ -4691,8 +4691,8 @@
       <c r="B120" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C120" s="4" t="n">
-        <v>146</v>
+      <c r="C120" s="7" t="n">
+        <v>174</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -4708,13 +4708,13 @@
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>116</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121">
@@ -4726,8 +4726,8 @@
       <c r="B121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="9" t="n">
-        <v>102</v>
+      <c r="C121" s="4" t="n">
+        <v>126</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4743,13 +4743,13 @@
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="I121" s="3" t="n">
         <v>113</v>
-      </c>
-      <c r="I121" s="3" t="n">
-        <v>103</v>
       </c>
     </row>
     <row r="122">
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123">
@@ -4796,8 +4796,8 @@
       <c r="B123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="9" t="n">
-        <v>91</v>
+      <c r="C123" s="10" t="n">
+        <v>112</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4813,13 +4813,13 @@
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124">
@@ -4832,7 +4832,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="125">
@@ -4866,30 +4866,30 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="7" t="n">
-        <v>158</v>
+      <c r="C125" s="10" t="n">
+        <v>89</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126">
@@ -4901,17 +4901,17 @@
       <c r="B126" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="10" t="n">
-        <v>92</v>
+      <c r="C126" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -4921,10 +4921,10 @@
         <v>3</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="127">
@@ -4936,30 +4936,30 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="10" t="n">
-        <v>94</v>
+      <c r="C127" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="128">
@@ -4971,30 +4971,30 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="5" t="n">
-        <v>135</v>
+      <c r="C128" s="10" t="n">
+        <v>94</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129">
@@ -5006,30 +5006,30 @@
       <c r="B129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="9" t="n">
-        <v>85</v>
+      <c r="C129" s="4" t="n">
+        <v>120</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130">
@@ -5041,30 +5041,30 @@
       <c r="B130" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C130" s="4" t="n">
-        <v>120</v>
+      <c r="C130" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="131">
@@ -5076,30 +5076,30 @@
       <c r="B131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="9" t="n">
-        <v>87</v>
+      <c r="C131" s="4" t="n">
+        <v>118</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132">
@@ -5111,17 +5111,17 @@
       <c r="B132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="4" t="n">
-        <v>123</v>
+      <c r="C132" s="5" t="n">
+        <v>141</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -5131,10 +5131,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133">
@@ -5147,16 +5147,16 @@
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -5166,10 +5166,10 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="134">
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="135">
@@ -5217,7 +5217,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="136">
@@ -5251,8 +5251,8 @@
       <c r="B136" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C136" s="10" t="n">
-        <v>114</v>
+      <c r="C136" s="4" t="n">
+        <v>123</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -5268,10 +5268,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>121</v>
@@ -5287,7 +5287,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138">
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5338,10 +5338,10 @@
         <v>1</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>159</v>
@@ -5356,8 +5356,8 @@
       <c r="B139" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C139" s="4" t="n">
-        <v>198</v>
+      <c r="C139" s="7" t="n">
+        <v>210</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="140">
@@ -5391,8 +5391,8 @@
       <c r="B140" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C140" s="9" t="n">
-        <v>128</v>
+      <c r="C140" s="4" t="n">
+        <v>148</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141">
@@ -5426,8 +5426,8 @@
       <c r="B141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="4" t="n">
-        <v>161</v>
+      <c r="C141" s="9" t="n">
+        <v>125</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142">
@@ -5461,8 +5461,8 @@
       <c r="B142" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C142" s="9" t="n">
-        <v>117</v>
+      <c r="C142" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5478,13 +5478,13 @@
         <v>1</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="143">
@@ -5497,7 +5497,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144">
@@ -5531,17 +5531,17 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="4" t="n">
-        <v>134</v>
+      <c r="C144" s="5" t="n">
+        <v>151</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145">
@@ -5566,12 +5566,12 @@
       <c r="B145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C145" s="10" t="n">
-        <v>106</v>
+      <c r="C145" s="7" t="n">
+        <v>255</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -5583,13 +5583,13 @@
         <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>126</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146">
@@ -5602,29 +5602,29 @@
         <v>145</v>
       </c>
       <c r="C146" s="7" t="n">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
     </row>
     <row r="147">
@@ -5637,29 +5637,29 @@
         <v>146</v>
       </c>
       <c r="C147" s="7" t="n">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148">
@@ -5672,16 +5672,16 @@
         <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -5691,10 +5691,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149">
@@ -5707,16 +5707,16 @@
         <v>148</v>
       </c>
       <c r="C149" s="7" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -5726,10 +5726,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>207</v>
+        <v>166</v>
       </c>
     </row>
     <row r="150">
@@ -5742,7 +5742,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5761,10 +5761,10 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151">
@@ -5777,7 +5777,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152">
@@ -5811,30 +5811,30 @@
       <c r="B152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="5" t="n">
-        <v>190</v>
+      <c r="C152" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="153">
@@ -5846,30 +5846,30 @@
       <c r="B153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="4" t="n">
-        <v>148</v>
+      <c r="C153" s="10" t="n">
+        <v>107</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154">
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="155">
@@ -5917,7 +5917,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="156">
@@ -5952,7 +5952,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="9" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5968,13 +5968,13 @@
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157">
@@ -5987,7 +5987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="158">
@@ -6022,29 +6022,29 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="159">
@@ -6057,16 +6057,16 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160">
@@ -6092,7 +6092,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="161">
@@ -6126,8 +6126,8 @@
       <c r="B161" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C161" s="10" t="n">
-        <v>156</v>
+      <c r="C161" s="9" t="n">
+        <v>145</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162">
@@ -6162,7 +6162,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -6181,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163">
@@ -6197,7 +6197,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>203</v>
@@ -6232,29 +6232,29 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" s="3" t="n">
-        <v>203</v>
-      </c>
       <c r="I164" s="3" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="165">
@@ -6286,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166">
@@ -6302,16 +6302,16 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>217</v>
+        <v>255</v>
       </c>
     </row>
     <row r="167">
@@ -6336,17 +6336,17 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="5" t="n">
-        <v>208</v>
+      <c r="C167" s="4" t="n">
+        <v>176</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
@@ -6356,10 +6356,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="168">
@@ -6371,17 +6371,17 @@
       <c r="B168" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="4" t="n">
-        <v>162</v>
+      <c r="C168" s="5" t="n">
+        <v>209</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
     </row>
     <row r="169">
@@ -6406,17 +6406,17 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="5" t="n">
-        <v>269</v>
+      <c r="C169" s="4" t="n">
+        <v>164</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
@@ -6426,10 +6426,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="170">
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6458,13 +6458,13 @@
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171">
@@ -6477,7 +6477,7 @@
         <v>182</v>
       </c>
       <c r="C171" s="9" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
@@ -6511,8 +6511,8 @@
       <c r="B172" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="C172" s="10" t="n">
-        <v>150</v>
+      <c r="C172" s="9" t="n">
+        <v>136</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>136</v>
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="174">
@@ -6582,7 +6582,7 @@
         <v>185</v>
       </c>
       <c r="C174" s="9" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6601,10 +6601,10 @@
         <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175">
@@ -6639,7 +6639,7 @@
         <v>183</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="176">
@@ -6652,7 +6652,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6671,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177">
@@ -6687,7 +6687,7 @@
         <v>188</v>
       </c>
       <c r="C177" s="10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>207</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
@@ -6722,7 +6722,7 @@
         <v>189</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>192</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="179">
@@ -6756,8 +6756,8 @@
       <c r="B179" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="C179" s="4" t="n">
-        <v>164</v>
+      <c r="C179" s="10" t="n">
+        <v>153</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6773,13 +6773,13 @@
         <v>0</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="180">
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="181">
@@ -6846,10 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="182">
@@ -6862,16 +6862,16 @@
         <v>193</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="183">
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="184">
@@ -6932,7 +6932,7 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185">
@@ -6966,8 +6966,8 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="4" t="n">
-        <v>178</v>
+      <c r="C185" s="10" t="n">
+        <v>163</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="186">
@@ -7001,17 +7001,17 @@
       <c r="B186" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C186" s="4" t="n">
-        <v>200</v>
+      <c r="C186" s="5" t="n">
+        <v>264</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="187">
@@ -7037,7 +7037,7 @@
         <v>198</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -7053,13 +7053,13 @@
         <v>0</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188">
@@ -7072,7 +7072,7 @@
         <v>199</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="189">
@@ -7107,7 +7107,7 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>202</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190">
@@ -7142,16 +7142,16 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="191">
@@ -7174,19 +7174,19 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C191" s="10" t="n">
-        <v>171</v>
+        <v>202</v>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>222</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -7196,10 +7196,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="192">
@@ -7209,19 +7209,19 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193">
@@ -7246,17 +7246,17 @@
       <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C193" s="4" t="n">
-        <v>191</v>
+      <c r="C193" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="194">
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="195">
@@ -7317,7 +7317,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="196">
@@ -7352,29 +7352,29 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Zachariah Branch</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I196" s="3" t="n">
         <v>254</v>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>Kayshon Boutte</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="I196" s="3" t="n">
-        <v>230</v>
       </c>
     </row>
     <row r="197">
@@ -7386,17 +7386,17 @@
       <c r="B197" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C197" s="10" t="n">
-        <v>172</v>
+      <c r="C197" s="4" t="n">
+        <v>223</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7406,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198">
@@ -7422,16 +7422,16 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -7441,10 +7441,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="199">
@@ -7456,17 +7456,17 @@
       <c r="B199" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C199" s="5" t="n">
-        <v>293</v>
+      <c r="C199" s="4" t="n">
+        <v>202</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -7476,9 +7476,11 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="I199" s="3" t="inlineStr"/>
+        <v>217</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7490,7 +7492,7 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
@@ -7509,10 +7511,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201">
@@ -7547,7 +7549,7 @@
         <v>228</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="202">
@@ -7560,7 +7562,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
@@ -7579,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="203">
@@ -7595,7 +7597,7 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7614,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="204">
@@ -7630,7 +7632,7 @@
         <v>216</v>
       </c>
       <c r="C204" s="10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
@@ -7649,10 +7651,10 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="205">
@@ -7665,7 +7667,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
@@ -7681,13 +7683,13 @@
         <v>0</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="206">
@@ -7700,7 +7702,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
@@ -7719,10 +7721,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="207">
@@ -7735,7 +7737,7 @@
         <v>219</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
@@ -7754,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="208">
@@ -7789,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="209">
@@ -7805,7 +7807,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7824,10 +7826,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="210">
@@ -7840,7 +7842,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7859,10 +7861,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="211">
@@ -7875,7 +7877,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
@@ -7894,10 +7896,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="212">
@@ -7910,16 +7912,16 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7929,9 +7931,11 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I212" s="3" t="inlineStr"/>
+        <v>260</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>234</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7943,7 +7947,7 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
@@ -7962,7 +7966,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>175</v>
+        <v>265</v>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
     </row>
@@ -7976,7 +7980,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -7995,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="215">
@@ -8010,17 +8014,17 @@
       <c r="B215" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="C215" s="4" t="n">
-        <v>236</v>
+      <c r="C215" s="5" t="n">
+        <v>285</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -8030,11 +8034,9 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="I215" s="3" t="n">
-        <v>229</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="I215" s="3" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -8046,16 +8048,16 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -8065,11 +8067,9 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I216" s="3" t="n">
-        <v>280</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -8080,17 +8080,17 @@
       <c r="B217" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C217" s="5" t="n">
-        <v>285</v>
+      <c r="C217" s="4" t="n">
+        <v>256</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F217" s="3" t="n">
@@ -8100,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>271</v>
+        <v>232</v>
       </c>
     </row>
     <row r="218">
@@ -8116,16 +8116,16 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="219">
@@ -8150,17 +8150,17 @@
       <c r="B219" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C219" s="5" t="n">
-        <v>268</v>
+      <c r="C219" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8170,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>269</v>
+        <v>204</v>
       </c>
     </row>
     <row r="220">
@@ -8186,16 +8186,16 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -8205,10 +8205,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="221">
@@ -8221,16 +8221,16 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -8243,7 +8243,7 @@
         <v>261</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222">
@@ -8256,16 +8256,16 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -8275,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>204</v>
+        <v>268</v>
       </c>
     </row>
     <row r="223">
@@ -8291,7 +8291,7 @@
         <v>237</v>
       </c>
       <c r="C223" s="10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>200</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224">
@@ -8326,7 +8326,7 @@
         <v>238</v>
       </c>
       <c r="C224" s="10" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -8345,10 +8345,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="225">
@@ -8360,8 +8360,8 @@
       <c r="B225" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C225" s="4" t="n">
-        <v>203</v>
+      <c r="C225" s="10" t="n">
+        <v>196</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8380,10 +8380,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="226">
@@ -8396,7 +8396,7 @@
         <v>240</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -8415,10 +8415,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="227">
@@ -8431,7 +8431,7 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
@@ -8450,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="228">
@@ -8465,8 +8465,8 @@
       <c r="B228" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C228" s="4" t="n">
-        <v>255</v>
+      <c r="C228" s="5" t="n">
+        <v>299</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -8485,10 +8485,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="229">
@@ -8501,7 +8501,7 @@
         <v>243</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I229" s="3" t="inlineStr"/>
     </row>
@@ -8533,8 +8533,8 @@
       <c r="B230" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C230" s="4" t="n">
-        <v>273</v>
+      <c r="C230" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231">
@@ -8569,7 +8569,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="232">
@@ -8604,7 +8604,7 @@
         <v>246</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
@@ -8623,10 +8623,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="233">
@@ -8639,7 +8639,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8658,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="234">
@@ -8674,7 +8674,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
@@ -8693,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235">
@@ -8708,8 +8708,8 @@
       <c r="B235" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C235" s="5" t="n">
-        <v>287</v>
+      <c r="C235" s="4" t="n">
+        <v>274</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
@@ -8728,10 +8728,10 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="236">
@@ -8744,7 +8744,7 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="237">
@@ -8779,7 +8779,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8798,10 +8798,10 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="238">
@@ -8814,16 +8814,16 @@
         <v>252</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8833,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="239">
@@ -8849,16 +8849,16 @@
         <v>253</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8868,10 +8868,10 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="240">
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="241">
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8951,8 +8951,8 @@
       <c r="B242" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C242" s="10" t="n">
-        <v>193</v>
+      <c r="C242" s="4" t="n">
+        <v>219</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="243">
@@ -8986,8 +8986,8 @@
       <c r="B243" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C243" s="5" t="n">
-        <v>318</v>
+      <c r="C243" s="4" t="n">
+        <v>291</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
     </row>
@@ -9020,7 +9020,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9039,10 +9039,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="245">
@@ -9054,12 +9054,12 @@
       <c r="B245" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C245" s="5" t="n">
-        <v>306</v>
+      <c r="C245" s="4" t="n">
+        <v>205</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -9074,10 +9074,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>292</v>
+        <v>211</v>
       </c>
     </row>
     <row r="246">
@@ -9087,19 +9087,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C246" s="4" t="n">
-        <v>291</v>
+        <v>262</v>
+      </c>
+      <c r="C246" s="5" t="n">
+        <v>319</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>252</v>
+        <v>293</v>
       </c>
     </row>
     <row r="247">
@@ -9125,16 +9125,16 @@
         <v>264</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F247" s="3" t="n">
@@ -9144,10 +9144,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>291</v>
+        <v>256</v>
       </c>
     </row>
     <row r="248">
@@ -9160,7 +9160,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9179,10 +9179,10 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="249">
@@ -9214,10 +9214,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250">
@@ -9230,7 +9230,7 @@
         <v>268</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
@@ -9249,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="251">
@@ -9265,7 +9265,7 @@
         <v>269</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
@@ -9284,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="252">
@@ -9300,7 +9300,7 @@
         <v>270</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253">
@@ -9335,16 +9335,16 @@
         <v>271</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F253" s="3" t="n">
@@ -9354,10 +9354,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="254">
@@ -9369,17 +9369,17 @@
       <c r="B254" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="C254" s="5" t="n">
-        <v>328</v>
+      <c r="C254" s="4" t="n">
+        <v>260</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Ashton Dulin</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -9389,9 +9389,11 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I254" s="3" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -9402,17 +9404,17 @@
       <c r="B255" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C255" s="4" t="n">
-        <v>294</v>
+      <c r="C255" s="5" t="n">
+        <v>332</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Ashton Dulin</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9422,11 +9424,9 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>276</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="I255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -9437,17 +9437,17 @@
       <c r="B256" s="3" t="n">
         <v>274</v>
       </c>
-      <c r="C256" s="5" t="n">
-        <v>339</v>
+      <c r="C256" s="4" t="n">
+        <v>300</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9457,9 +9457,11 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I256" s="3" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>274</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9471,16 +9473,16 @@
         <v>275</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
@@ -9490,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
     </row>
@@ -9503,8 +9505,8 @@
       <c r="B258" s="3" t="n">
         <v>276</v>
       </c>
-      <c r="C258" s="4" t="n">
-        <v>317</v>
+      <c r="C258" s="5" t="n">
+        <v>318</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
@@ -9523,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9537,7 +9539,7 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
@@ -9556,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9570,7 +9572,7 @@
         <v>278</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9602,8 +9604,8 @@
       <c r="B261" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="C261" s="5" t="n">
-        <v>322</v>
+      <c r="C261" s="4" t="n">
+        <v>314</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9622,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9636,7 +9638,7 @@
         <v>280</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9655,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9668,8 +9670,8 @@
       <c r="B263" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C263" s="4" t="n">
-        <v>323</v>
+      <c r="C263" s="5" t="n">
+        <v>341</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9688,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9721,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9735,7 +9737,7 @@
         <v>283</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
@@ -9754,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I265" s="3" t="inlineStr"/>
     </row>
@@ -9767,17 +9769,17 @@
       <c r="B266" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="C266" s="4" t="n">
-        <v>261</v>
+      <c r="C266" s="5" t="n">
+        <v>359</v>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Malachi Fields</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F266" s="3" t="n">
@@ -9787,11 +9789,9 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="I266" s="3" t="n">
-        <v>294</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>287</v>
       </c>
       <c r="C267" s="10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
@@ -9822,10 +9822,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268">
@@ -9857,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="I268" s="3" t="inlineStr"/>
     </row>
@@ -9871,7 +9871,7 @@
         <v>289</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="270">
@@ -9906,7 +9906,7 @@
         <v>290</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
@@ -9925,10 +9925,10 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="271">
@@ -9941,7 +9941,7 @@
         <v>291</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
@@ -9960,10 +9960,10 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I271" s="3" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="272">
@@ -9998,7 +9998,7 @@
         <v>257</v>
       </c>
       <c r="I272" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="273">
@@ -10011,7 +10011,7 @@
         <v>293</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="I273" s="3" t="inlineStr"/>
     </row>
@@ -10044,64 +10044,99 @@
         <v>294</v>
       </c>
       <c r="C274" s="4" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
+          <t>Malachi Fields</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="I274" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="C275" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
           <t>Andrei Iosivas</t>
         </is>
       </c>
-      <c r="E274" s="3" t="inlineStr">
+      <c r="E275" s="3" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="F274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="I274" s="3" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="11" t="inlineStr">
+      <c r="F275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I275" s="3" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B275" s="3" t="n">
+      <c r="B276" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C275" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="D275" s="3" t="inlineStr">
+      <c r="C276" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E275" s="3" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F275" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="I275" s="3" t="n">
-        <v>248</v>
+      <c r="F276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="I276" s="3" t="n">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,16 +632,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -654,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -667,16 +667,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -689,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>54</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>5</v>
@@ -737,7 +737,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>6</v>
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>5</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -982,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -1052,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1067,8 +1067,8 @@
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>38</v>
+      <c r="G16" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -1121,8 +1121,8 @@
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>41</v>
+      <c r="C18" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
       <c r="F18" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>19</v>
+      <c r="G18" s="5" t="n">
+        <v>29</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1156,30 +1156,30 @@
       <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>15</v>
+      <c r="C19" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>42</v>
+      <c r="G19" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1192,29 +1192,29 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1227,23 +1227,23 @@
         <v>20</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
@@ -1262,29 +1262,29 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Kenneth Walker</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1296,30 +1296,30 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>26</v>
+      <c r="C23" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Kenneth Walker</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1331,30 +1331,30 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>25</v>
+      <c r="C24" s="7" t="n">
+        <v>42</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>31</v>
+      <c r="G24" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1424,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>30</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -1494,7 +1494,7 @@
         <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1506,30 +1506,30 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>19</v>
+      <c r="C29" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>36</v>
+      <c r="G29" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -1541,30 +1541,30 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>42</v>
+      <c r="C30" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>19</v>
+      <c r="G30" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -1577,29 +1577,29 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1647,29 +1647,29 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1697,14 +1697,14 @@
       <c r="F34" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>24</v>
+      <c r="G34" s="10" t="n">
+        <v>30</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1732,14 +1732,14 @@
       <c r="F35" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>29</v>
+      <c r="G35" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -1774,7 +1774,7 @@
         <v>36</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
@@ -1787,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>22</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>37</v>
@@ -1822,29 +1822,29 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Travis Etienne</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>21</v>
+      <c r="G38" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>35</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -1857,29 +1857,29 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Travis Etienne</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -1892,7 +1892,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
         <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -1927,7 +1927,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1961,8 +1961,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>64</v>
+      <c r="C42" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       <c r="F42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>7</v>
+      <c r="G42" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>42</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43">
@@ -1996,8 +1996,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="10" t="n">
-        <v>31</v>
+      <c r="C43" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         <v>19</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>41</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -2031,8 +2031,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="5" t="n">
-        <v>51</v>
+      <c r="C44" s="7" t="n">
+        <v>57</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>43</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>44</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47">
@@ -2136,8 +2136,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="9" t="n">
-        <v>30</v>
+      <c r="C47" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2152,14 +2152,14 @@
       <c r="F47" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G47" s="9" t="n">
-        <v>27</v>
+      <c r="G47" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>35</v>
@@ -2207,29 +2207,29 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -2242,7 +2242,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         <v>13</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -2311,30 +2311,30 @@
       <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="4" t="n">
-        <v>50</v>
+      <c r="C52" s="7" t="n">
+        <v>88</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="4" t="n">
-        <v>13</v>
+      <c r="G52" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53">
@@ -2347,29 +2347,29 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>14</v>
+      <c r="G53" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>53</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -2404,7 +2404,7 @@
         <v>52</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -2416,30 +2416,30 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="7" t="n">
-        <v>96</v>
+      <c r="C55" s="4" t="n">
+        <v>48</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G55" s="5" t="n">
-        <v>2</v>
+      <c r="G55" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
@@ -2471,10 +2471,10 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
@@ -2487,7 +2487,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>56</v>
@@ -2541,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59">
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -2592,29 +2592,29 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>60</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
@@ -2626,30 +2626,30 @@
       <c r="B61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="9" t="n">
-        <v>52</v>
+      <c r="C61" s="4" t="n">
+        <v>61</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62">
@@ -2662,29 +2662,29 @@
         <v>61</v>
       </c>
       <c r="C62" s="9" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>11</v>
+      <c r="G62" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -2696,30 +2696,30 @@
       <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C63" s="4" t="n">
-        <v>67</v>
+      <c r="C63" s="9" t="n">
+        <v>55</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
@@ -2731,30 +2731,30 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>69</v>
+      <c r="C64" s="10" t="n">
+        <v>59</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -2767,29 +2767,29 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G65" s="4" t="n">
-        <v>6</v>
+      <c r="G65" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>67</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66">
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2817,14 +2817,14 @@
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>3</v>
+      <c r="G66" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2852,14 +2852,14 @@
       <c r="F67" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="4" t="n">
-        <v>1</v>
+      <c r="G67" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68">
@@ -2872,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>1</v>
+      <c r="G68" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>65</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69">
@@ -2929,7 +2929,7 @@
         <v>73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70">
@@ -2942,7 +2942,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2958,13 +2958,13 @@
         <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
@@ -2976,30 +2976,30 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="9" t="n">
-        <v>46</v>
+      <c r="C71" s="7" t="n">
+        <v>107</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>15</v>
+      <c r="G71" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>68</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>47</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72">
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
@@ -3047,7 +3047,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3081,8 +3081,8 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>70</v>
+      <c r="C74" s="10" t="n">
+        <v>69</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75">
@@ -3116,8 +3116,8 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="10" t="n">
-        <v>61</v>
+      <c r="C75" s="4" t="n">
+        <v>64</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3133,13 +3133,13 @@
         <v>5</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76">
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3168,13 +3168,13 @@
         <v>5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77">
@@ -3186,8 +3186,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>59</v>
+      <c r="C77" s="10" t="n">
+        <v>54</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78">
@@ -3221,30 +3221,30 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="4" t="n">
-        <v>77</v>
+      <c r="C78" s="9" t="n">
+        <v>47</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>5</v>
+      <c r="G78" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79">
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>82</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80">
@@ -3291,8 +3291,8 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="10" t="n">
-        <v>58</v>
+      <c r="C80" s="4" t="n">
+        <v>73</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81">
@@ -3326,8 +3326,8 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="5" t="n">
-        <v>86</v>
+      <c r="C81" s="4" t="n">
+        <v>83</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         <v>4</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>80</v>
@@ -3397,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>78</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -3432,7 +3432,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3467,7 +3467,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86">
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3518,13 +3518,13 @@
         <v>4</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87">
@@ -3537,7 +3537,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88">
@@ -3572,7 +3572,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91">
@@ -3677,29 +3677,29 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
@@ -3712,29 +3712,29 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93">
@@ -3746,30 +3746,30 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="7" t="n">
-        <v>124</v>
+      <c r="C93" s="4" t="n">
+        <v>85</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>92</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>140</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94">
@@ -3782,7 +3782,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>90</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96">
@@ -3886,30 +3886,30 @@
       <c r="B97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="4" t="n">
-        <v>99</v>
+      <c r="C97" s="9" t="n">
+        <v>67</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98">
@@ -3921,30 +3921,30 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="9" t="n">
-        <v>74</v>
+      <c r="C98" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="99">
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100">
@@ -3991,12 +3991,12 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="9" t="n">
-        <v>80</v>
+      <c r="C100" s="4" t="n">
+        <v>99</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -4046,10 +4046,10 @@
         <v>1</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102">
@@ -4061,30 +4061,30 @@
       <c r="B102" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C102" s="9" t="n">
-        <v>81</v>
+      <c r="C102" s="10" t="n">
+        <v>97</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>73</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103">
@@ -4096,30 +4096,30 @@
       <c r="B103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="4" t="n">
-        <v>125</v>
+      <c r="C103" s="9" t="n">
+        <v>70</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104">
@@ -4131,8 +4131,8 @@
       <c r="B104" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C104" s="4" t="n">
-        <v>103</v>
+      <c r="C104" s="10" t="n">
+        <v>98</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105">
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,10 +4186,10 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106">
@@ -4201,30 +4201,30 @@
       <c r="B106" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="C106" s="9" t="n">
-        <v>88</v>
+      <c r="C106" s="4" t="n">
+        <v>102</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107">
@@ -4236,30 +4236,30 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="10" t="n">
-        <v>101</v>
+      <c r="C107" s="9" t="n">
+        <v>72</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108">
@@ -4272,16 +4272,16 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109">
@@ -4306,30 +4306,30 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="9" t="n">
-        <v>90</v>
+      <c r="C109" s="4" t="n">
+        <v>112</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110">
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>154</v>
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112">
@@ -4412,7 +4412,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113">
@@ -4446,30 +4446,30 @@
       <c r="B113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C113" s="4" t="n">
-        <v>93</v>
+      <c r="C113" s="7" t="n">
+        <v>137</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114">
@@ -4482,29 +4482,29 @@
         <v>113</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="115">
@@ -4517,16 +4517,16 @@
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -4536,10 +4536,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="I115" s="3" t="n">
         <v>108</v>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>88</v>
       </c>
     </row>
     <row r="116">
@@ -4551,17 +4551,17 @@
       <c r="B116" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C116" s="4" t="n">
-        <v>116</v>
+      <c r="C116" s="10" t="n">
+        <v>111</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -4571,10 +4571,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117">
@@ -4586,30 +4586,30 @@
       <c r="B117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C117" s="4" t="n">
-        <v>119</v>
+      <c r="C117" s="7" t="n">
+        <v>279</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>133</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118">
@@ -4622,16 +4622,16 @@
         <v>117</v>
       </c>
       <c r="C118" s="10" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119">
@@ -4656,30 +4656,30 @@
       <c r="B119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="7" t="n">
-        <v>279</v>
+      <c r="C119" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>262</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120">
@@ -4691,8 +4691,8 @@
       <c r="B120" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C120" s="4" t="n">
-        <v>146</v>
+      <c r="C120" s="7" t="n">
+        <v>174</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -4708,13 +4708,13 @@
         <v>2</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="121">
@@ -4727,29 +4727,29 @@
         <v>120</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="122">
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123">
@@ -4796,30 +4796,30 @@
       <c r="B123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="9" t="n">
-        <v>91</v>
+      <c r="C123" s="4" t="n">
+        <v>146</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124">
@@ -4832,16 +4832,16 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -4851,10 +4851,10 @@
         <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125">
@@ -4866,30 +4866,30 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="7" t="n">
-        <v>158</v>
+      <c r="C125" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>182</v>
+        <v>93</v>
       </c>
     </row>
     <row r="126">
@@ -4901,30 +4901,30 @@
       <c r="B126" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C126" s="10" t="n">
-        <v>92</v>
+      <c r="C126" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="127">
@@ -4936,30 +4936,30 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="10" t="n">
-        <v>94</v>
+      <c r="C127" s="7" t="n">
+        <v>170</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>90</v>
+        <v>183</v>
       </c>
     </row>
     <row r="128">
@@ -4971,30 +4971,30 @@
       <c r="B128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C128" s="5" t="n">
-        <v>135</v>
+      <c r="C128" s="10" t="n">
+        <v>94</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Chris Godwin</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129">
@@ -5006,27 +5006,27 @@
       <c r="B129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C129" s="9" t="n">
-        <v>85</v>
+      <c r="C129" s="4" t="n">
+        <v>120</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>109</v>
@@ -5042,16 +5042,16 @@
         <v>129</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -5061,10 +5061,10 @@
         <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I130" s="3" t="n">
         <v>126</v>
-      </c>
-      <c r="I130" s="3" t="n">
-        <v>115</v>
       </c>
     </row>
     <row r="131">
@@ -5076,30 +5076,30 @@
       <c r="B131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="9" t="n">
-        <v>87</v>
+      <c r="C131" s="5" t="n">
+        <v>141</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132">
@@ -5111,30 +5111,30 @@
       <c r="B132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="4" t="n">
-        <v>123</v>
+      <c r="C132" s="7" t="n">
+        <v>255</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133">
@@ -5147,16 +5147,16 @@
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -5166,10 +5166,10 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="134">
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="135">
@@ -5217,7 +5217,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136">
@@ -5251,8 +5251,8 @@
       <c r="B136" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C136" s="10" t="n">
-        <v>114</v>
+      <c r="C136" s="4" t="n">
+        <v>123</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -5268,13 +5268,13 @@
         <v>1</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137">
@@ -5287,7 +5287,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="138">
@@ -5321,30 +5321,30 @@
       <c r="B138" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C138" s="4" t="n">
-        <v>176</v>
+      <c r="C138" s="9" t="n">
+        <v>126</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>151</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="139">
@@ -5356,8 +5356,8 @@
       <c r="B139" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C139" s="4" t="n">
-        <v>198</v>
+      <c r="C139" s="7" t="n">
+        <v>210</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140">
@@ -5391,30 +5391,30 @@
       <c r="B140" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C140" s="9" t="n">
-        <v>128</v>
+      <c r="C140" s="4" t="n">
+        <v>211</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
     </row>
     <row r="141">
@@ -5426,8 +5426,8 @@
       <c r="B141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="4" t="n">
-        <v>161</v>
+      <c r="C141" s="9" t="n">
+        <v>125</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5443,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142">
@@ -5461,30 +5461,30 @@
       <c r="B142" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C142" s="9" t="n">
-        <v>117</v>
+      <c r="C142" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="143">
@@ -5497,16 +5497,16 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144">
@@ -5531,17 +5531,17 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="4" t="n">
-        <v>134</v>
+      <c r="C144" s="7" t="n">
+        <v>160</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145">
@@ -5566,30 +5566,30 @@
       <c r="B145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C145" s="10" t="n">
-        <v>106</v>
+      <c r="C145" s="7" t="n">
+        <v>254</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>126</v>
+        <v>231</v>
       </c>
     </row>
     <row r="146">
@@ -5601,12 +5601,12 @@
       <c r="B146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="7" t="n">
-        <v>202</v>
+      <c r="C146" s="4" t="n">
+        <v>151</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -5618,13 +5618,13 @@
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>219</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147">
@@ -5636,17 +5636,17 @@
       <c r="B147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="7" t="n">
-        <v>159</v>
+      <c r="C147" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -5656,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="148">
@@ -5672,16 +5672,16 @@
         <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -5691,10 +5691,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>221</v>
+        <v>180</v>
       </c>
     </row>
     <row r="149">
@@ -5706,30 +5706,30 @@
       <c r="B149" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C149" s="7" t="n">
-        <v>201</v>
+      <c r="C149" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>207</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150">
@@ -5742,7 +5742,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5761,10 +5761,10 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151">
@@ -5777,7 +5777,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5796,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152">
@@ -5812,16 +5812,16 @@
         <v>151</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="153">
@@ -5846,30 +5846,30 @@
       <c r="B153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="4" t="n">
-        <v>148</v>
+      <c r="C153" s="5" t="n">
+        <v>295</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>141</v>
+        <v>275</v>
       </c>
     </row>
     <row r="154">
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="155">
@@ -5917,16 +5917,16 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="156">
@@ -5951,30 +5951,30 @@
       <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C156" s="9" t="n">
-        <v>144</v>
+      <c r="C156" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>131</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>101</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157">
@@ -5987,16 +5987,16 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>214</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158">
@@ -6022,29 +6022,29 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="159">
@@ -6057,16 +6057,16 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160">
@@ -6092,7 +6092,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161">
@@ -6126,8 +6126,8 @@
       <c r="B161" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C161" s="10" t="n">
-        <v>156</v>
+      <c r="C161" s="9" t="n">
+        <v>145</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="162">
@@ -6162,7 +6162,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -6181,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163">
@@ -6197,16 +6197,16 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="164">
@@ -6232,11 +6232,11 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165">
@@ -6266,17 +6266,17 @@
       <c r="B165" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C165" s="4" t="n">
-        <v>173</v>
+      <c r="C165" s="5" t="n">
+        <v>222</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
@@ -6286,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>183</v>
+        <v>216</v>
       </c>
     </row>
     <row r="166">
@@ -6302,29 +6302,29 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Tank Dell</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="I166" s="3" t="n">
         <v>257</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Germie Bernard</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="I166" s="3" t="n">
-        <v>217</v>
       </c>
     </row>
     <row r="167">
@@ -6336,30 +6336,30 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="5" t="n">
-        <v>208</v>
+      <c r="C167" s="4" t="n">
+        <v>148</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>190</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168">
@@ -6372,16 +6372,16 @@
         <v>167</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169">
@@ -6406,30 +6406,30 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="5" t="n">
-        <v>269</v>
+      <c r="C169" s="9" t="n">
+        <v>101</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>196</v>
+        <v>111</v>
       </c>
     </row>
     <row r="170">
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6458,13 +6458,13 @@
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171">
@@ -6477,7 +6477,7 @@
         <v>182</v>
       </c>
       <c r="C171" s="9" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>135</v>
@@ -6511,8 +6511,8 @@
       <c r="B172" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="C172" s="10" t="n">
-        <v>150</v>
+      <c r="C172" s="9" t="n">
+        <v>136</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>136</v>
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="174">
@@ -6582,7 +6582,7 @@
         <v>185</v>
       </c>
       <c r="C174" s="9" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6601,10 +6601,10 @@
         <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175">
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176">
@@ -6652,7 +6652,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6671,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177">
@@ -6687,7 +6687,7 @@
         <v>188</v>
       </c>
       <c r="C177" s="10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
@@ -6706,10 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="178">
@@ -6722,7 +6722,7 @@
         <v>189</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6741,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="179">
@@ -6756,8 +6756,8 @@
       <c r="B179" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="C179" s="4" t="n">
-        <v>164</v>
+      <c r="C179" s="10" t="n">
+        <v>153</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6773,13 +6773,13 @@
         <v>0</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="180">
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="181">
@@ -6846,10 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="182">
@@ -6861,17 +6861,17 @@
       <c r="B182" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="C182" s="4" t="n">
-        <v>210</v>
+      <c r="C182" s="5" t="n">
+        <v>272</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Jordan James</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>191</v>
+        <v>272</v>
       </c>
     </row>
     <row r="183">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>187</v>
@@ -6932,16 +6932,16 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185">
@@ -6966,17 +6966,17 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="4" t="n">
-        <v>178</v>
+      <c r="C185" s="5" t="n">
+        <v>270</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>157</v>
+        <v>254</v>
       </c>
     </row>
     <row r="186">
@@ -7001,17 +7001,17 @@
       <c r="B186" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C186" s="4" t="n">
-        <v>200</v>
+      <c r="C186" s="5" t="n">
+        <v>265</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
     </row>
     <row r="187">
@@ -7037,7 +7037,7 @@
         <v>198</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -7053,13 +7053,13 @@
         <v>0</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>161</v>
+        <v>271</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188">
@@ -7071,17 +7071,17 @@
       <c r="B188" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C188" s="4" t="n">
-        <v>194</v>
+      <c r="C188" s="5" t="n">
+        <v>232</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
     </row>
     <row r="189">
@@ -7107,16 +7107,16 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -7126,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190">
@@ -7142,16 +7142,16 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>254</v>
+        <v>274</v>
       </c>
     </row>
     <row r="191">
@@ -7174,32 +7174,32 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" s="3" t="n">
         <v>203</v>
       </c>
-      <c r="C191" s="10" t="n">
-        <v>171</v>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>Ryan Flournoy</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" s="3" t="n">
-        <v>181</v>
-      </c>
       <c r="I191" s="3" t="n">
-        <v>184</v>
+        <v>95</v>
       </c>
     </row>
     <row r="192">
@@ -7211,17 +7211,17 @@
       <c r="B192" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C192" s="5" t="n">
-        <v>256</v>
+      <c r="C192" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>250</v>
+        <v>182</v>
       </c>
     </row>
     <row r="193">
@@ -7246,17 +7246,17 @@
       <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C193" s="4" t="n">
-        <v>191</v>
+      <c r="C193" s="5" t="n">
+        <v>285</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>206</v>
+        <v>268</v>
       </c>
     </row>
     <row r="194">
@@ -7282,7 +7282,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="195">
@@ -7317,7 +7317,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="196">
@@ -7352,16 +7352,16 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -7371,11 +7371,9 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="I196" s="3" t="n">
-        <v>230</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -7386,17 +7384,17 @@
       <c r="B197" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C197" s="10" t="n">
-        <v>172</v>
+      <c r="C197" s="5" t="n">
+        <v>291</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7406,10 +7404,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>197</v>
+        <v>256</v>
       </c>
     </row>
     <row r="198">
@@ -7422,16 +7420,16 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -7441,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="199">
@@ -7456,17 +7454,17 @@
       <c r="B199" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C199" s="5" t="n">
-        <v>293</v>
+      <c r="C199" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -7476,9 +7474,11 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="I199" s="3" t="inlineStr"/>
+        <v>269</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>208</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7489,17 +7489,17 @@
       <c r="B200" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C200" s="5" t="n">
-        <v>271</v>
+      <c r="C200" s="10" t="n">
+        <v>179</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -7509,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>267</v>
+        <v>177</v>
       </c>
     </row>
     <row r="201">
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="202">
@@ -7560,16 +7560,16 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F202" s="3" t="n">
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="203">
@@ -7595,7 +7595,7 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="204">
@@ -7630,7 +7630,7 @@
         <v>216</v>
       </c>
       <c r="C204" s="10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
@@ -7649,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="205">
@@ -7665,7 +7665,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
@@ -7681,13 +7681,13 @@
         <v>0</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="206">
@@ -7700,16 +7700,16 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7719,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="207">
@@ -7735,16 +7735,16 @@
         <v>219</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>228</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208">
@@ -7770,16 +7770,16 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>246</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>283</v>
@@ -7840,16 +7840,16 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Ollie Gordon</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
@@ -7859,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="211">
@@ -7874,17 +7874,17 @@
       <c r="B211" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C211" s="4" t="n">
-        <v>209</v>
+      <c r="C211" s="5" t="n">
+        <v>273</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7894,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>233</v>
+        <v>271</v>
       </c>
     </row>
     <row r="212">
@@ -7909,17 +7909,17 @@
       <c r="B212" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C212" s="5" t="n">
-        <v>266</v>
+      <c r="C212" s="4" t="n">
+        <v>202</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7929,9 +7929,11 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I212" s="3" t="inlineStr"/>
+        <v>270</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7943,16 +7945,16 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Ty Johnson</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
@@ -7962,9 +7964,11 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="I213" s="3" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>284</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7976,16 +7980,16 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -7995,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="215">
@@ -8010,17 +8014,17 @@
       <c r="B215" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="C215" s="4" t="n">
-        <v>236</v>
+      <c r="C215" s="5" t="n">
+        <v>359</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -8030,10 +8034,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>229</v>
+        <v>299</v>
       </c>
     </row>
     <row r="216">
@@ -8046,16 +8050,16 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -8065,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>280</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217">
@@ -8080,12 +8084,12 @@
       <c r="B217" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C217" s="5" t="n">
-        <v>285</v>
+      <c r="C217" s="4" t="n">
+        <v>224</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -8100,10 +8104,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>271</v>
+        <v>209</v>
       </c>
     </row>
     <row r="218">
@@ -8115,17 +8119,17 @@
       <c r="B218" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C218" s="5" t="n">
-        <v>290</v>
+      <c r="C218" s="4" t="n">
+        <v>257</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8135,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>267</v>
+        <v>181</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>300</v>
+        <v>234</v>
       </c>
     </row>
     <row r="219">
@@ -8151,16 +8155,16 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8170,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="220">
@@ -8185,17 +8189,17 @@
       <c r="B220" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C220" s="5" t="n">
-        <v>283</v>
+      <c r="C220" s="10" t="n">
+        <v>191</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -8205,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>265</v>
+        <v>181</v>
       </c>
     </row>
     <row r="221">
@@ -8220,30 +8224,30 @@
       <c r="B221" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C221" s="5" t="n">
+      <c r="C221" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hurst</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I221" s="3" t="n">
         <v>286</v>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>Jaylin Noel</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="I221" s="3" t="n">
-        <v>277</v>
       </c>
     </row>
     <row r="222">
@@ -8255,8 +8259,8 @@
       <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C222" s="5" t="n">
-        <v>277</v>
+      <c r="C222" s="4" t="n">
+        <v>204</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -8275,10 +8279,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="223">
@@ -8291,7 +8295,7 @@
         <v>237</v>
       </c>
       <c r="C223" s="10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
@@ -8310,10 +8314,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="224">
@@ -8326,7 +8330,7 @@
         <v>238</v>
       </c>
       <c r="C224" s="10" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -8345,10 +8349,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="225">
@@ -8360,17 +8364,17 @@
       <c r="B225" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C225" s="4" t="n">
-        <v>203</v>
+      <c r="C225" s="5" t="n">
+        <v>281</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -8380,11 +8384,9 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>205</v>
-      </c>
-      <c r="I225" s="3" t="n">
-        <v>189</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="I225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8396,16 +8398,16 @@
         <v>240</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -8415,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="227">
@@ -8431,16 +8433,16 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -8450,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>282</v>
@@ -8465,17 +8467,17 @@
       <c r="B228" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C228" s="4" t="n">
-        <v>255</v>
+      <c r="C228" s="10" t="n">
+        <v>163</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -8485,10 +8487,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>288</v>
+        <v>156</v>
       </c>
     </row>
     <row r="229">
@@ -8500,17 +8502,17 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="5" t="n">
-        <v>287</v>
+      <c r="C229" s="10" t="n">
+        <v>196</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Adam Randall</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -8520,9 +8522,11 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="I229" s="3" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="I229" s="3" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8533,17 +8537,17 @@
       <c r="B230" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C230" s="4" t="n">
-        <v>273</v>
+      <c r="C230" s="5" t="n">
+        <v>289</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -8553,10 +8557,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>213</v>
+        <v>280</v>
       </c>
     </row>
     <row r="231">
@@ -8569,16 +8573,16 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>LeQuint Allen</t>
+          <t>Ty Johnson</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -8588,11 +8592,9 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="I231" s="3" t="n">
-        <v>281</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="I231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8603,17 +8605,17 @@
       <c r="B232" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C232" s="5" t="n">
-        <v>288</v>
+      <c r="C232" s="4" t="n">
+        <v>274</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -8623,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>264</v>
+        <v>162</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="233">
@@ -8638,17 +8640,17 @@
       <c r="B233" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="C233" s="4" t="n">
-        <v>211</v>
+      <c r="C233" s="5" t="n">
+        <v>298</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -8658,10 +8660,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>215</v>
+        <v>290</v>
       </c>
     </row>
     <row r="234">
@@ -8673,17 +8675,17 @@
       <c r="B234" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="C234" s="4" t="n">
-        <v>270</v>
+      <c r="C234" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -8693,10 +8695,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>255</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235">
@@ -8708,17 +8710,17 @@
       <c r="B235" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C235" s="5" t="n">
-        <v>287</v>
+      <c r="C235" s="4" t="n">
+        <v>273</v>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F235" s="3" t="n">
@@ -8728,10 +8730,10 @@
         <v>0</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>268</v>
+        <v>291</v>
       </c>
     </row>
     <row r="236">
@@ -8744,16 +8746,16 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Chris Brooks</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -8766,7 +8768,7 @@
         <v>249</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="237">
@@ -8779,7 +8781,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8798,10 +8800,10 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="238">
@@ -8813,17 +8815,17 @@
       <c r="B238" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C238" s="4" t="n">
-        <v>263</v>
+      <c r="C238" s="10" t="n">
+        <v>173</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8833,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>232</v>
+        <v>167</v>
       </c>
     </row>
     <row r="239">
@@ -8848,17 +8850,17 @@
       <c r="B239" s="3" t="n">
         <v>253</v>
       </c>
-      <c r="C239" s="4" t="n">
-        <v>222</v>
+      <c r="C239" s="5" t="n">
+        <v>358</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8868,11 +8870,9 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>220</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="I239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="241">
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8951,17 +8951,17 @@
       <c r="B242" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C242" s="10" t="n">
-        <v>193</v>
+      <c r="C242" s="4" t="n">
+        <v>233</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F242" s="3" t="n">
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>223</v>
+        <v>248</v>
       </c>
     </row>
     <row r="243">
@@ -8986,17 +8986,17 @@
       <c r="B243" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C243" s="5" t="n">
-        <v>318</v>
+      <c r="C243" s="4" t="n">
+        <v>219</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Darren Waller</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F243" s="3" t="n">
@@ -9006,9 +9006,11 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I243" s="3" t="inlineStr"/>
+        <v>259</v>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>206</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="8" t="inlineStr">
@@ -9020,7 +9022,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9039,10 +9041,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="245">
@@ -9054,12 +9056,12 @@
       <c r="B245" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C245" s="5" t="n">
-        <v>306</v>
+      <c r="C245" s="4" t="n">
+        <v>205</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -9074,10 +9076,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>292</v>
+        <v>219</v>
       </c>
     </row>
     <row r="246">
@@ -9087,19 +9089,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9109,10 +9111,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>252</v>
+        <v>292</v>
       </c>
     </row>
     <row r="247">
@@ -9122,19 +9124,19 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Elijah Sarratt</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F247" s="3" t="n">
@@ -9144,10 +9146,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>291</v>
+        <v>276</v>
       </c>
     </row>
     <row r="248">
@@ -9160,53 +9162,51 @@
         <v>265</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
+          <t>Malik Davis</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="I248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
           <t>Emanuel Wilson</t>
         </is>
       </c>
-      <c r="E248" s="3" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="I248" s="3" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C249" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>NYJ</t>
-        </is>
-      </c>
       <c r="F249" s="3" t="n">
         <v>0</v>
       </c>
@@ -9214,10 +9214,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>200</v>
+        <v>281</v>
       </c>
     </row>
     <row r="250">
@@ -9227,19 +9227,19 @@
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F250" s="3" t="n">
@@ -9249,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="251">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
@@ -9284,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="252">
@@ -9297,56 +9297,56 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="C252" s="4" t="n">
-        <v>252</v>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
+      <c r="C253" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
         <is>
           <t>Deshaun Watson</t>
         </is>
       </c>
-      <c r="E252" s="3" t="inlineStr">
+      <c r="E253" s="3" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="F252" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>Ted Hurst</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F253" s="3" t="n">
         <v>0</v>
       </c>
@@ -9354,10 +9354,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>285</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254">
@@ -9367,19 +9367,19 @@
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C254" s="5" t="n">
-        <v>328</v>
+        <v>271</v>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>256</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Ashton Dulin</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -9389,9 +9389,11 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I254" s="3" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -9400,32 +9402,32 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C255" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>338</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Treylon Burks</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="I255" s="3" t="n">
         <v>294</v>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>Darnell Mooney</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>NYG</t>
-        </is>
-      </c>
-      <c r="F255" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>276</v>
       </c>
     </row>
     <row r="256">
@@ -9435,19 +9437,19 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="C256" s="5" t="n">
-        <v>339</v>
+        <v>273</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>284</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9457,9 +9459,11 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I256" s="3" t="inlineStr"/>
+        <v>215</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>267</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9468,52 +9472,54 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="C257" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>Savion Williams</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F257" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="I257" s="3" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>276</v>
-      </c>
       <c r="C258" s="4" t="n">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
@@ -9523,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9537,7 +9543,7 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
@@ -9556,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9567,10 +9573,10 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9600,10 +9606,10 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="C261" s="5" t="n">
-        <v>322</v>
+        <v>280</v>
+      </c>
+      <c r="C261" s="4" t="n">
+        <v>321</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9622,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9633,10 +9639,10 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9655,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9666,10 +9672,10 @@
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>323</v>
+        <v>282</v>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>367</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9688,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9699,7 +9705,7 @@
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C264" s="5" t="n">
         <v>351</v>
@@ -9721,30 +9727,30 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="C265" s="5" t="n">
-        <v>348</v>
+        <v>284</v>
+      </c>
+      <c r="C265" s="4" t="n">
+        <v>311</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F265" s="3" t="n">
@@ -9754,30 +9760,32 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="I265" s="3" t="inlineStr"/>
+        <v>194</v>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>293</v>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A266" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="C266" s="4" t="n">
-        <v>261</v>
+        <v>287</v>
+      </c>
+      <c r="C266" s="10" t="n">
+        <v>186</v>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Malachi Fields</t>
+          <t>Trey Smack</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F266" s="3" t="n">
@@ -9787,10 +9795,10 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>294</v>
+        <v>222</v>
       </c>
     </row>
     <row r="267">
@@ -9800,19 +9808,19 @@
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="C267" s="10" t="n">
-        <v>185</v>
+        <v>288</v>
+      </c>
+      <c r="C267" s="4" t="n">
+        <v>226</v>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Trey Smack</t>
+          <t>Jake Elliott</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F267" s="3" t="n">
@@ -9822,32 +9830,30 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="I267" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I267" s="3" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="A268" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F268" s="3" t="n">
@@ -9857,9 +9863,11 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="I268" s="3" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>265</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="8" t="inlineStr">
@@ -9868,10 +9876,10 @@
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
@@ -9890,10 +9898,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="270">
@@ -9903,10 +9911,10 @@
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
@@ -9925,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="271">
@@ -9938,19 +9946,19 @@
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F271" s="3" t="n">
@@ -9960,11 +9968,9 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>224</v>
-      </c>
-      <c r="I271" s="3" t="n">
-        <v>242</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="8" t="inlineStr">
@@ -9973,19 +9979,19 @@
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C272" s="4" t="n">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Mike Gesicki</t>
+          <t>Jake Tonges</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F272" s="3" t="n">
@@ -9995,32 +10001,30 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I272" s="3" t="n">
-        <v>263</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="I272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C273" s="5" t="n">
-        <v>362</v>
+        <v>296</v>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>252</v>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F273" s="3" t="n">
@@ -10030,78 +10034,10 @@
         <v>0</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="I273" s="3" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="I274" s="3" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="C275" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="D275" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="F275" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="I275" s="3" t="n">
-        <v>248</v>
+        <v>217</v>
+      </c>
+      <c r="I273" s="3" t="n">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,16 +632,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -654,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -667,16 +667,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -689,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>5</v>
@@ -826,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -981,30 +981,30 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>25</v>
+      <c r="C14" s="4" t="n">
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>31</v>
+      <c r="G14" s="5" t="n">
+        <v>40</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1051,30 +1051,30 @@
       <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>16</v>
+      <c r="C16" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>40</v>
+      <c r="G16" s="7" t="n">
+        <v>31</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1156,30 +1156,30 @@
       <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>24</v>
+      <c r="C19" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>32</v>
+      <c r="G19" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1192,29 +1192,29 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1227,29 +1227,29 @@
         <v>20</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1262,29 +1262,29 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kenneth Walker</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1296,30 +1296,30 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>10</v>
+      <c r="C23" s="7" t="n">
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Kenneth Walker</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>50</v>
+      <c r="G23" s="7" t="n">
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -1331,30 +1331,30 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>42</v>
+      <c r="C24" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>19</v>
+      <c r="G24" s="4" t="n">
+        <v>32</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1436,30 +1436,30 @@
       <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>35</v>
+      <c r="C27" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>22</v>
+      <c r="G27" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1471,30 +1471,30 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>22</v>
+      <c r="C28" s="5" t="n">
+        <v>35</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>33</v>
+      <c r="G28" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1507,29 +1507,29 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>30</v>
+      <c r="G29" s="10" t="n">
+        <v>33</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -1542,29 +1542,29 @@
         <v>29</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>28</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1577,29 +1577,29 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -1647,29 +1647,29 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>29</v>
@@ -1806,7 +1806,7 @@
         <v>20</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1822,29 +1822,29 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Travis Etienne</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>18</v>
+      <c r="G38" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>35</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -1857,29 +1857,29 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Travis Etienne</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -1911,7 +1911,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>45</v>
@@ -2207,29 +2207,29 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>38</v>
@@ -2296,7 +2296,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>66</v>
@@ -2311,30 +2311,30 @@
       <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="7" t="n">
-        <v>88</v>
+      <c r="C52" s="4" t="n">
+        <v>51</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="5" t="n">
-        <v>3</v>
+      <c r="G52" s="4" t="n">
+        <v>12</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>51</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2347,29 +2347,29 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="10" t="n">
-        <v>15</v>
+      <c r="G53" s="4" t="n">
+        <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -2401,7 +2401,7 @@
         <v>13</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>53</v>
@@ -2416,30 +2416,30 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="4" t="n">
-        <v>48</v>
+      <c r="C55" s="7" t="n">
+        <v>88</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>14</v>
+      <c r="G55" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56">
@@ -2471,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>60</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>51</v>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>59</v>
@@ -2576,7 +2576,7 @@
         <v>8</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>57</v>
@@ -2592,29 +2592,29 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61">
@@ -2626,30 +2626,30 @@
       <c r="B61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="4" t="n">
-        <v>61</v>
+      <c r="C61" s="9" t="n">
+        <v>44</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>9</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
@@ -2661,30 +2661,30 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>44</v>
+      <c r="C62" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G62" s="9" t="n">
-        <v>17</v>
+      <c r="G62" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63">
@@ -2696,30 +2696,30 @@
       <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C63" s="9" t="n">
-        <v>55</v>
+      <c r="C63" s="4" t="n">
+        <v>59</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -2731,30 +2731,30 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="10" t="n">
-        <v>59</v>
+      <c r="C64" s="4" t="n">
+        <v>68</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -2767,29 +2767,29 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G65" s="5" t="n">
-        <v>3</v>
+      <c r="G65" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66">
@@ -2821,7 +2821,7 @@
         <v>4</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>94</v>
@@ -2871,30 +2871,30 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="7" t="n">
-        <v>117</v>
+      <c r="C68" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>2</v>
+      <c r="G68" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69">
@@ -2907,16 +2907,16 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Marvin Harrison</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -2926,10 +2926,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70">
@@ -2941,30 +2941,30 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="5" t="n">
-        <v>76</v>
+      <c r="C70" s="9" t="n">
+        <v>47</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G70" s="4" t="n">
-        <v>5</v>
+      <c r="G70" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -2977,16 +2977,16 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -2996,10 +2996,10 @@
         <v>2</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72">
@@ -3031,7 +3031,7 @@
         <v>4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>82</v>
@@ -3066,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>92</v>
@@ -3101,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>71</v>
@@ -3136,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>58</v>
@@ -3171,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>121</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>55</v>
@@ -3222,29 +3222,29 @@
         <v>77</v>
       </c>
       <c r="C78" s="9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="9" t="n">
-        <v>15</v>
+      <c r="G78" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79">
@@ -3256,12 +3256,12 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="9" t="n">
-        <v>50</v>
+      <c r="C79" s="4" t="n">
+        <v>73</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3272,14 +3272,14 @@
       <c r="F79" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>13</v>
+      <c r="G79" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
@@ -3291,30 +3291,30 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="4" t="n">
-        <v>73</v>
+      <c r="C80" s="5" t="n">
+        <v>83</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
@@ -3327,29 +3327,29 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="I81" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="82">
@@ -3361,12 +3361,12 @@
       <c r="B82" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C82" s="4" t="n">
-        <v>77</v>
+      <c r="C82" s="7" t="n">
+        <v>140</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3378,13 +3378,13 @@
         <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83">
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>100</v>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>99</v>
@@ -3521,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>122</v>
@@ -3556,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>102</v>
@@ -3591,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3607,16 +3607,16 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90">
@@ -3641,30 +3641,30 @@
       <c r="B90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="7" t="n">
-        <v>139</v>
+      <c r="C90" s="4" t="n">
+        <v>85</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>163</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -3676,30 +3676,30 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="4" t="n">
-        <v>87</v>
+      <c r="C91" s="7" t="n">
+        <v>137</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92">
@@ -3712,29 +3712,29 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93">
@@ -3746,30 +3746,30 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="4" t="n">
-        <v>85</v>
+      <c r="C93" s="7" t="n">
+        <v>108</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>92</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94">
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>73</v>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>138</v>
@@ -3886,30 +3886,30 @@
       <c r="B97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="9" t="n">
-        <v>67</v>
+      <c r="C97" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="98">
@@ -3921,30 +3921,30 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="4" t="n">
-        <v>100</v>
+      <c r="C98" s="10" t="n">
+        <v>92</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99">
@@ -3976,7 +3976,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>131</v>
@@ -3991,12 +3991,12 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="4" t="n">
-        <v>99</v>
+      <c r="C100" s="9" t="n">
+        <v>72</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -4008,13 +4008,13 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
@@ -4027,29 +4027,29 @@
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102">
@@ -4061,30 +4061,30 @@
       <c r="B102" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C102" s="10" t="n">
-        <v>97</v>
+      <c r="C102" s="9" t="n">
+        <v>70</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
@@ -4096,30 +4096,30 @@
       <c r="B103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="C103" s="9" t="n">
-        <v>70</v>
+      <c r="C103" s="10" t="n">
+        <v>97</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104">
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>105</v>
@@ -4186,7 +4186,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>124</v>
@@ -4201,30 +4201,30 @@
       <c r="B106" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="C106" s="4" t="n">
-        <v>102</v>
+      <c r="C106" s="9" t="n">
+        <v>90</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107">
@@ -4236,30 +4236,30 @@
       <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C107" s="9" t="n">
-        <v>72</v>
+      <c r="C107" s="4" t="n">
+        <v>111</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108">
@@ -4272,16 +4272,16 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109">
@@ -4306,17 +4306,17 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="4" t="n">
-        <v>112</v>
+      <c r="C109" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -4326,10 +4326,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110">
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>154</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>130</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>205</v>
@@ -4446,30 +4446,30 @@
       <c r="B113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C113" s="7" t="n">
-        <v>137</v>
+      <c r="C113" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>144</v>
+        <v>93</v>
       </c>
     </row>
     <row r="114">
@@ -4481,30 +4481,30 @@
       <c r="B114" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C114" s="4" t="n">
-        <v>93</v>
+      <c r="C114" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="115">
@@ -4516,30 +4516,30 @@
       <c r="B115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C115" s="4" t="n">
-        <v>108</v>
+      <c r="C115" s="7" t="n">
+        <v>170</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>108</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116">
@@ -4551,30 +4551,30 @@
       <c r="B116" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C116" s="10" t="n">
-        <v>111</v>
+      <c r="C116" s="4" t="n">
+        <v>127</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117">
@@ -4586,30 +4586,30 @@
       <c r="B117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C117" s="7" t="n">
-        <v>279</v>
+      <c r="C117" s="4" t="n">
+        <v>113</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>264</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118">
@@ -4621,17 +4621,17 @@
       <c r="B118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C118" s="10" t="n">
-        <v>113</v>
+      <c r="C118" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -4641,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119">
@@ -4656,30 +4656,30 @@
       <c r="B119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C119" s="9" t="n">
-        <v>96</v>
+      <c r="C119" s="7" t="n">
+        <v>279</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>103</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120">
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>188</v>
@@ -4726,30 +4726,30 @@
       <c r="B121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="9" t="n">
-        <v>91</v>
+      <c r="C121" s="4" t="n">
+        <v>126</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122">
@@ -4781,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>90</v>
@@ -4796,30 +4796,30 @@
       <c r="B123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="4" t="n">
-        <v>146</v>
+      <c r="C123" s="10" t="n">
+        <v>112</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124">
@@ -4832,16 +4832,16 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -4851,10 +4851,10 @@
         <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125">
@@ -4866,17 +4866,17 @@
       <c r="B125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C125" s="4" t="n">
-        <v>95</v>
+      <c r="C125" s="10" t="n">
+        <v>89</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
@@ -4886,10 +4886,10 @@
         <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126">
@@ -4902,29 +4902,29 @@
         <v>125</v>
       </c>
       <c r="C126" s="9" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="127">
@@ -4936,30 +4936,30 @@
       <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C127" s="7" t="n">
-        <v>170</v>
+      <c r="C127" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>183</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128">
@@ -4991,7 +4991,7 @@
         <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>98</v>
@@ -5026,7 +5026,7 @@
         <v>2</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>109</v>
@@ -5041,30 +5041,30 @@
       <c r="B130" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C130" s="4" t="n">
-        <v>118</v>
+      <c r="C130" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
     </row>
     <row r="131">
@@ -5076,30 +5076,30 @@
       <c r="B131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="5" t="n">
-        <v>141</v>
+      <c r="C131" s="4" t="n">
+        <v>118</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132">
@@ -5111,30 +5111,30 @@
       <c r="B132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="7" t="n">
-        <v>255</v>
+      <c r="C132" s="5" t="n">
+        <v>141</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>229</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133">
@@ -5166,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>143</v>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>101</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>185</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>119</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>194</v>
@@ -5321,17 +5321,17 @@
       <c r="B138" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C138" s="9" t="n">
-        <v>126</v>
+      <c r="C138" s="4" t="n">
+        <v>147</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -5341,10 +5341,10 @@
         <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139">
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>202</v>
@@ -5392,29 +5392,29 @@
         <v>139</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>227</v>
+        <v>142</v>
       </c>
     </row>
     <row r="141">
@@ -5446,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>114</v>
@@ -5462,16 +5462,16 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="143">
@@ -5497,16 +5497,16 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="144">
@@ -5531,17 +5531,17 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="7" t="n">
-        <v>160</v>
+      <c r="C144" s="5" t="n">
+        <v>151</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>162</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145">
@@ -5567,16 +5567,16 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -5586,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146">
@@ -5601,17 +5601,17 @@
       <c r="B146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C146" s="4" t="n">
-        <v>151</v>
+      <c r="C146" s="7" t="n">
+        <v>160</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -5621,10 +5621,10 @@
         <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
     <row r="147">
@@ -5636,30 +5636,30 @@
       <c r="B147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C147" s="4" t="n">
-        <v>150</v>
+      <c r="C147" s="7" t="n">
+        <v>254</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>145</v>
+        <v>231</v>
       </c>
     </row>
     <row r="148">
@@ -5672,16 +5672,16 @@
         <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -5691,10 +5691,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>180</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149">
@@ -5706,30 +5706,30 @@
       <c r="B149" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C149" s="9" t="n">
-        <v>84</v>
+      <c r="C149" s="7" t="n">
+        <v>190</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150">
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>139</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>140</v>
@@ -5811,30 +5811,30 @@
       <c r="B152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C152" s="5" t="n">
-        <v>263</v>
+      <c r="C152" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153">
@@ -5846,30 +5846,30 @@
       <c r="B153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="5" t="n">
-        <v>295</v>
+      <c r="C153" s="10" t="n">
+        <v>107</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>275</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154">
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>215</v>
@@ -5917,16 +5917,16 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="156">
@@ -5951,30 +5951,30 @@
       <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C156" s="4" t="n">
-        <v>201</v>
+      <c r="C156" s="9" t="n">
+        <v>101</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>197</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157">
@@ -5987,16 +5987,16 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>157</v>
+        <v>227</v>
       </c>
     </row>
     <row r="158">
@@ -6022,16 +6022,16 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -6041,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="159">
@@ -6057,16 +6057,16 @@
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>196</v>
+        <v>155</v>
       </c>
     </row>
     <row r="160">
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>213</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>153</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>165</v>
@@ -6197,16 +6197,16 @@
         <v>162</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164">
@@ -6232,11 +6232,11 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>207</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165">
@@ -6266,17 +6266,17 @@
       <c r="B165" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C165" s="5" t="n">
-        <v>222</v>
+      <c r="C165" s="4" t="n">
+        <v>173</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
@@ -6286,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>216</v>
+        <v>167</v>
       </c>
     </row>
     <row r="166">
@@ -6302,16 +6302,16 @@
         <v>165</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>257</v>
+        <v>147</v>
       </c>
     </row>
     <row r="167">
@@ -6337,29 +6337,29 @@
         <v>166</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="168">
@@ -6371,17 +6371,17 @@
       <c r="B168" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="4" t="n">
-        <v>177</v>
+      <c r="C168" s="5" t="n">
+        <v>209</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="169">
@@ -6406,30 +6406,30 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="9" t="n">
-        <v>101</v>
+      <c r="C169" s="4" t="n">
+        <v>164</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="170">
@@ -6461,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>107</v>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>135</v>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>136</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>198</v>
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>106</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>174</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>297</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>151</v>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>191</v>
@@ -6776,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>152</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>172</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>237</v>
+        <v>187</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>158</v>
@@ -6861,17 +6861,17 @@
       <c r="B182" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="C182" s="5" t="n">
-        <v>272</v>
+      <c r="C182" s="4" t="n">
+        <v>177</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>272</v>
+        <v>176</v>
       </c>
     </row>
     <row r="183">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>187</v>
@@ -6932,16 +6932,16 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="185">
@@ -6966,17 +6966,17 @@
       <c r="B185" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>270</v>
+      <c r="C185" s="10" t="n">
+        <v>163</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>254</v>
+        <v>156</v>
       </c>
     </row>
     <row r="186">
@@ -7002,16 +7002,16 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>255</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187">
@@ -7056,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>120</v>
@@ -7071,17 +7071,17 @@
       <c r="B188" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C188" s="5" t="n">
-        <v>232</v>
+      <c r="C188" s="4" t="n">
+        <v>197</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>226</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189">
@@ -7107,16 +7107,16 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -7126,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="190">
@@ -7142,16 +7142,16 @@
         <v>201</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="191">
@@ -7176,30 +7176,30 @@
       <c r="B191" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C191" s="9" t="n">
-        <v>89</v>
+      <c r="C191" s="4" t="n">
+        <v>222</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>95</v>
+        <v>216</v>
       </c>
     </row>
     <row r="192">
@@ -7209,19 +7209,19 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C192" s="10" t="n">
-        <v>171</v>
+        <v>203</v>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>266</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>182</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193">
@@ -7246,17 +7246,17 @@
       <c r="B193" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C193" s="5" t="n">
-        <v>285</v>
+      <c r="C193" s="10" t="n">
+        <v>171</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>268</v>
+        <v>182</v>
       </c>
     </row>
     <row r="194">
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>260</v>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>211</v>
@@ -7352,16 +7352,16 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
@@ -7371,9 +7371,11 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="I196" s="3" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -7384,17 +7386,17 @@
       <c r="B197" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C197" s="5" t="n">
-        <v>291</v>
+      <c r="C197" s="4" t="n">
+        <v>223</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -7404,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>256</v>
+        <v>217</v>
       </c>
     </row>
     <row r="198">
@@ -7420,16 +7422,16 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -7439,10 +7441,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="199">
@@ -7455,11 +7457,11 @@
         <v>211</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -7474,10 +7476,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>269</v>
+        <v>217</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="200">
@@ -7489,17 +7491,17 @@
       <c r="B200" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C200" s="10" t="n">
-        <v>179</v>
+      <c r="C200" s="5" t="n">
+        <v>272</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Jordan James</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -7509,10 +7511,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>177</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201">
@@ -7544,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>238</v>
@@ -7560,16 +7562,16 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Kaytron Allen</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F202" s="3" t="n">
@@ -7579,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>172</v>
+        <v>253</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="203">
@@ -7614,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>261</v>
@@ -7649,7 +7651,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>179</v>
@@ -7684,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>178</v>
@@ -7700,16 +7702,16 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -7719,10 +7721,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="207">
@@ -7735,16 +7737,16 @@
         <v>219</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -7754,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
     </row>
     <row r="208">
@@ -7770,16 +7772,16 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -7789,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>192</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209">
@@ -7805,16 +7807,16 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -7824,10 +7826,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="210">
@@ -7840,16 +7842,16 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
@@ -7859,10 +7861,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="211">
@@ -7874,17 +7876,17 @@
       <c r="B211" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C211" s="5" t="n">
-        <v>273</v>
+      <c r="C211" s="4" t="n">
+        <v>238</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
@@ -7894,10 +7896,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>271</v>
+        <v>237</v>
       </c>
     </row>
     <row r="212">
@@ -7909,17 +7911,17 @@
       <c r="B212" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C212" s="4" t="n">
-        <v>202</v>
+      <c r="C212" s="5" t="n">
+        <v>283</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -7929,10 +7931,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="213">
@@ -7945,16 +7947,16 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Ty Johnson</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
@@ -7964,11 +7966,9 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="I213" s="3" t="n">
-        <v>284</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="I213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7980,16 +7980,16 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Ollie Gordon</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="215">
@@ -8015,16 +8015,16 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -8034,11 +8034,9 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="I215" s="3" t="n">
-        <v>299</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="I215" s="3" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -8050,16 +8048,16 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -8069,11 +8067,9 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="I216" s="3" t="n">
-        <v>235</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -8085,16 +8081,16 @@
         <v>229</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F217" s="3" t="n">
@@ -8104,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
     </row>
     <row r="218">
@@ -8119,17 +8115,17 @@
       <c r="B218" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C218" s="4" t="n">
-        <v>257</v>
+      <c r="C218" s="5" t="n">
+        <v>359</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -8139,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>234</v>
+        <v>299</v>
       </c>
     </row>
     <row r="219">
@@ -8154,17 +8150,17 @@
       <c r="B219" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C219" s="5" t="n">
-        <v>299</v>
+      <c r="C219" s="4" t="n">
+        <v>203</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -8174,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>300</v>
+        <v>208</v>
       </c>
     </row>
     <row r="220">
@@ -8189,17 +8185,17 @@
       <c r="B220" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C220" s="10" t="n">
-        <v>191</v>
+      <c r="C220" s="5" t="n">
+        <v>295</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -8209,10 +8205,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>181</v>
+        <v>275</v>
       </c>
     </row>
     <row r="221">
@@ -8224,17 +8220,17 @@
       <c r="B221" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C221" s="4" t="n">
-        <v>264</v>
+      <c r="C221" s="5" t="n">
+        <v>284</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -8244,10 +8240,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>176</v>
+        <v>261</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222">
@@ -8259,17 +8255,17 @@
       <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C222" s="4" t="n">
-        <v>204</v>
+      <c r="C222" s="5" t="n">
+        <v>285</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -8279,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="I222" s="3" t="n">
         <v>268</v>
-      </c>
-      <c r="I222" s="3" t="n">
-        <v>210</v>
       </c>
     </row>
     <row r="223">
@@ -8314,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="I223" s="3" t="n">
         <v>240</v>
@@ -8349,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>221</v>
@@ -8364,17 +8360,17 @@
       <c r="B225" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C225" s="5" t="n">
-        <v>281</v>
+      <c r="C225" s="10" t="n">
+        <v>196</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Adam Randall</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -8384,9 +8380,11 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="I225" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8398,16 +8396,16 @@
         <v>240</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -8420,7 +8418,7 @@
         <v>251</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="227">
@@ -8433,16 +8431,16 @@
         <v>241</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>LeQuint Allen</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -8452,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="228">
@@ -8467,17 +8465,17 @@
       <c r="B228" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C228" s="10" t="n">
-        <v>163</v>
+      <c r="C228" s="5" t="n">
+        <v>299</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -8487,10 +8485,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>156</v>
+        <v>289</v>
       </c>
     </row>
     <row r="229">
@@ -8502,17 +8500,17 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="10" t="n">
-        <v>196</v>
+      <c r="C229" s="5" t="n">
+        <v>280</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -8522,11 +8520,9 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="I229" s="3" t="n">
-        <v>195</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8537,17 +8533,17 @@
       <c r="B230" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C230" s="5" t="n">
-        <v>289</v>
+      <c r="C230" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -8557,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>280</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231">
@@ -8573,16 +8569,16 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Ty Johnson</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -8592,9 +8588,11 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="I231" s="3" t="inlineStr"/>
+        <v>265</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8605,17 +8603,17 @@
       <c r="B232" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C232" s="4" t="n">
-        <v>274</v>
+      <c r="C232" s="5" t="n">
+        <v>289</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -8625,10 +8623,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>162</v>
+        <v>266</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="233">
@@ -8640,17 +8638,17 @@
       <c r="B233" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="C233" s="5" t="n">
-        <v>298</v>
+      <c r="C233" s="4" t="n">
+        <v>240</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -8660,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="234">
@@ -8675,17 +8673,17 @@
       <c r="B234" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="C234" s="10" t="n">
-        <v>195</v>
+      <c r="C234" s="4" t="n">
+        <v>271</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -8695,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>201</v>
+        <v>253</v>
       </c>
     </row>
     <row r="235">
@@ -8711,29 +8709,29 @@
         <v>249</v>
       </c>
       <c r="C235" s="4" t="n">
+        <v>274</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="I235" s="3" t="n">
         <v>273</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I235" s="3" t="n">
-        <v>291</v>
       </c>
     </row>
     <row r="236">
@@ -8746,16 +8744,16 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -8765,10 +8763,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>228</v>
+        <v>291</v>
       </c>
     </row>
     <row r="237">
@@ -8800,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="I237" s="3" t="n">
         <v>279</v>
@@ -8815,17 +8813,17 @@
       <c r="B238" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C238" s="10" t="n">
-        <v>173</v>
+      <c r="C238" s="4" t="n">
+        <v>204</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8835,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>167</v>
+        <v>210</v>
       </c>
     </row>
     <row r="239">
@@ -8850,17 +8848,17 @@
       <c r="B239" s="3" t="n">
         <v>253</v>
       </c>
-      <c r="C239" s="5" t="n">
-        <v>358</v>
+      <c r="C239" s="4" t="n">
+        <v>268</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8870,9 +8868,11 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="I239" s="3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="I240" s="3" t="n">
         <v>173</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8952,16 +8952,16 @@
         <v>258</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F242" s="3" t="n">
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>248</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243">
@@ -8987,16 +8987,16 @@
         <v>259</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Darren Waller</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F243" s="3" t="n">
@@ -9006,11 +9006,9 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="I243" s="3" t="n">
-        <v>206</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I243" s="3" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="8" t="inlineStr">
@@ -9041,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>249</v>
@@ -9076,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="I245" s="3" t="n">
         <v>219</v>
@@ -9091,17 +9089,17 @@
       <c r="B246" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C246" s="4" t="n">
-        <v>280</v>
+      <c r="C246" s="5" t="n">
+        <v>311</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9111,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="247">
@@ -9124,19 +9122,19 @@
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Elijah Sarratt</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F247" s="3" t="n">
@@ -9146,10 +9144,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>276</v>
+        <v>256</v>
       </c>
     </row>
     <row r="248">
@@ -9162,16 +9160,16 @@
         <v>265</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F248" s="3" t="n">
@@ -9181,30 +9179,32 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="I248" s="3" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>RB</t>
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F249" s="3" t="n">
@@ -9214,10 +9214,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>281</v>
+        <v>203</v>
       </c>
     </row>
     <row r="250">
@@ -9227,19 +9227,19 @@
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F250" s="3" t="n">
@@ -9249,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="251">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C251" s="4" t="n">
         <v>231</v>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="I251" s="3" t="n">
         <v>204</v>
@@ -9297,19 +9297,19 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F252" s="3" t="n">
@@ -9319,32 +9319,32 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F253" s="3" t="n">
@@ -9354,10 +9354,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>251</v>
+        <v>292</v>
       </c>
     </row>
     <row r="254">
@@ -9367,19 +9367,19 @@
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
@@ -9389,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>233</v>
+        <v>286</v>
       </c>
     </row>
     <row r="255">
@@ -9402,19 +9402,19 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Ashton Dulin</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9424,11 +9424,9 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>294</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="I255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -9437,19 +9435,19 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9459,10 +9457,10 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="257">
@@ -9472,19 +9470,19 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="C257" s="4" t="n">
-        <v>262</v>
+        <v>275</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>325</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
@@ -9494,32 +9492,30 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="I257" s="3" t="n">
-        <v>266</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="I257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="C258" s="4" t="n">
-        <v>269</v>
+        <v>276</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>318</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F258" s="3" t="n">
@@ -9529,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9543,7 +9539,7 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
@@ -9562,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
     </row>
@@ -9573,10 +9569,10 @@
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9606,10 +9602,10 @@
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="C261" s="4" t="n">
-        <v>321</v>
+        <v>279</v>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>336</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9628,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9639,10 +9635,10 @@
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9661,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
     </row>
@@ -9672,10 +9668,10 @@
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9694,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9705,82 +9701,80 @@
         </is>
       </c>
       <c r="B264" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>352</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Jawhar Jordan</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C264" s="5" t="n">
-        <v>351</v>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>Jawhar Jordan</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="I264" s="3" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="inlineStr">
+      <c r="C265" s="5" t="n">
+        <v>333</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Kaleb Johnson</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="I265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="B265" s="3" t="n">
+      <c r="B266" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="C265" s="4" t="n">
-        <v>311</v>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>Marvin Mims</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="F265" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="I265" s="3" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="C266" s="10" t="n">
-        <v>186</v>
+      <c r="C266" s="5" t="n">
+        <v>358</v>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Trey Smack</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -9795,11 +9789,9 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="I266" s="3" t="n">
-        <v>222</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
@@ -9808,54 +9800,56 @@
         </is>
       </c>
       <c r="B267" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C267" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Trey Smack</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="C267" s="4" t="n">
+      <c r="C268" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="D267" s="3" t="inlineStr">
+      <c r="D268" s="3" t="inlineStr">
         <is>
           <t>Jake Elliott</t>
         </is>
       </c>
-      <c r="E267" s="3" t="inlineStr">
+      <c r="E268" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="F267" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H267" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="I267" s="3" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="8" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C268" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F268" s="3" t="n">
         <v>0</v>
       </c>
@@ -9863,11 +9857,9 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I268" s="3" t="n">
-        <v>265</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="8" t="inlineStr">
@@ -9876,7 +9868,7 @@
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C269" s="4" t="n">
         <v>258</v>
@@ -9898,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="I269" s="3" t="n">
         <v>247</v>
@@ -9911,7 +9903,7 @@
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C270" s="4" t="n">
         <v>281</v>
@@ -9933,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>262</v>
@@ -9946,19 +9938,19 @@
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>328</v>
+        <v>233</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F271" s="3" t="n">
@@ -9968,9 +9960,11 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="I271" s="3" t="inlineStr"/>
+        <v>222</v>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>248</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="8" t="inlineStr">
@@ -9979,64 +9973,169 @@
         </is>
       </c>
       <c r="B272" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="C272" s="4" t="n">
-        <v>312</v>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>Jake Tonges</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="I272" s="3" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="11" t="inlineStr">
+      <c r="C273" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Michael Mayer</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>Malachi Fields</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>NYG</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="I274" s="3" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="C275" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I275" s="3" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="11" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
-      <c r="B273" s="3" t="n">
+      <c r="B276" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="C273" s="4" t="n">
+      <c r="C276" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="D273" s="3" t="inlineStr">
+      <c r="D276" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E273" s="3" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="F273" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="I273" s="3" t="n">
+      <c r="F276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="I276" s="3" t="n">
         <v>252</v>
       </c>
     </row>

--- a/frontend/public/data/2026/espn/merged_formatted.xlsx
+++ b/frontend/public/data/2026/espn/merged_formatted.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I276"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
         <v>55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>2</v>
@@ -651,7 +651,7 @@
         <v>56</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -912,7 +912,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -962,8 +962,8 @@
       <c r="F13" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>43</v>
+      <c r="G13" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
@@ -982,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -1033,13 +1033,13 @@
         <v>43</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1052,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16</v>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>38</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>17</v>
@@ -1157,7 +1157,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>37</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>18</v>
@@ -1191,8 +1191,8 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>17</v>
+      <c r="C20" s="4" t="n">
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>19</v>
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>20</v>
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>21</v>
@@ -1296,30 +1296,30 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="7" t="n">
-        <v>38</v>
+      <c r="C23" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>21</v>
+      <c r="G23" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -1332,29 +1332,29 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>32</v>
+      <c r="G24" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -1367,7 +1367,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1383,13 +1383,13 @@
         <v>32</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -1401,8 +1401,8 @@
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>23</v>
+      <c r="C26" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1417,14 +1417,14 @@
       <c r="F26" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>32</v>
+      <c r="G26" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1437,7 +1437,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>30</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>27</v>
@@ -1472,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>30</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>26</v>
@@ -1541,8 +1541,8 @@
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>19</v>
+      <c r="C30" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1557,14 +1557,14 @@
       <c r="F30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>36</v>
+      <c r="G30" s="9" t="n">
+        <v>37</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1577,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>31</v>
@@ -1646,8 +1646,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="9" t="n">
-        <v>21</v>
+      <c r="C33" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1662,14 +1662,14 @@
       <c r="F33" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G33" s="9" t="n">
-        <v>34</v>
+      <c r="G33" s="10" t="n">
+        <v>32</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1682,7 +1682,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>33</v>
@@ -1752,7 +1752,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         <v>22</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>29</v>
@@ -1787,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>22</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>27</v>
@@ -1822,7 +1822,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         <v>22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>31</v>
@@ -1857,7 +1857,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>39</v>
@@ -1892,29 +1892,29 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>17</v>
+      <c r="G40" s="7" t="n">
+        <v>10</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>38</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
@@ -1927,29 +1927,29 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>40</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -1962,7 +1962,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>63</v>
@@ -1997,7 +1997,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -2012,11 +2012,11 @@
       <c r="F43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G43" s="10" t="n">
-        <v>24</v>
+      <c r="G43" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>42</v>
@@ -2031,8 +2031,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>57</v>
+      <c r="C44" s="5" t="n">
+        <v>55</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2082,8 +2082,8 @@
       <c r="F45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>22</v>
+      <c r="G45" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>44</v>
@@ -2102,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -2136,8 +2136,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="10" t="n">
-        <v>34</v>
+      <c r="C47" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>15</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>37</v>
@@ -2172,7 +2172,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>35</v>
@@ -2207,7 +2207,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>48</v>
@@ -2242,7 +2242,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>38</v>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>66</v>
@@ -2347,7 +2347,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -2362,8 +2362,8 @@
       <c r="F53" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>14</v>
+      <c r="G53" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>52</v>
@@ -2382,7 +2382,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         <v>10</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>86</v>
@@ -2451,8 +2451,8 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="5" t="n">
-        <v>66</v>
+      <c r="C56" s="7" t="n">
+        <v>69</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2467,11 +2467,11 @@
       <c r="F56" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>7</v>
+      <c r="G56" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>60</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>51</v>
@@ -2521,8 +2521,8 @@
       <c r="B58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>65</v>
+      <c r="C58" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2537,8 +2537,8 @@
       <c r="F58" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>7</v>
+      <c r="G58" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>57</v>
@@ -2557,7 +2557,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2573,10 +2573,10 @@
         <v>9</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>57</v>
@@ -2592,7 +2592,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>65</v>
@@ -2646,7 +2646,7 @@
         <v>17</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>41</v>
@@ -2662,7 +2662,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>62</v>
@@ -2732,7 +2732,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         <v>7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>69</v>
@@ -2802,7 +2802,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2817,14 +2817,14 @@
       <c r="F66" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="4" t="n">
-        <v>4</v>
+      <c r="G66" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>67</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67">
@@ -2837,7 +2837,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>125</v>
@@ -2872,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>5</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>74</v>
@@ -2906,8 +2906,8 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="5" t="n">
-        <v>76</v>
+      <c r="C69" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         <v>6</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>78</v>
@@ -2942,7 +2942,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>15</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>47</v>
@@ -2977,7 +2977,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>110</v>
@@ -3012,7 +3012,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>82</v>
@@ -3047,7 +3047,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>6</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>69</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74">
@@ -3082,7 +3082,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
         <v>6</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>71</v>
@@ -3117,7 +3117,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>58</v>
@@ -3152,7 +3152,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>121</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>55</v>
@@ -3222,7 +3222,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>13</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>49</v>
@@ -3256,8 +3256,8 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="4" t="n">
-        <v>73</v>
+      <c r="C79" s="5" t="n">
+        <v>82</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -3273,10 +3273,10 @@
         <v>4</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>75</v>
@@ -3292,7 +3292,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>4</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>81</v>
@@ -3362,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
         <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83">
@@ -3397,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>100</v>
@@ -3432,7 +3432,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>68</v>
@@ -3467,7 +3467,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>99</v>
@@ -3502,7 +3502,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3571,8 +3571,8 @@
       <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="10" t="n">
-        <v>71</v>
+      <c r="C88" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3588,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>67</v>
@@ -3607,7 +3607,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90">
@@ -3642,7 +3642,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>4</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>79</v>
@@ -3677,7 +3677,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3693,13 +3693,13 @@
         <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92">
@@ -3712,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>3</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>97</v>
@@ -3746,8 +3746,8 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="7" t="n">
-        <v>108</v>
+      <c r="C93" s="5" t="n">
+        <v>102</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>108</v>
@@ -3782,7 +3782,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>73</v>
@@ -3817,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>138</v>
@@ -3871,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>64</v>
@@ -3906,7 +3906,7 @@
         <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>85</v>
@@ -3921,8 +3921,8 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="10" t="n">
-        <v>92</v>
+      <c r="C98" s="4" t="n">
+        <v>94</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>3</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>83</v>
@@ -3957,7 +3957,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100">
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>76</v>
@@ -4046,10 +4046,10 @@
         <v>2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="102">
@@ -4062,7 +4062,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="9" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
         <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>72</v>
@@ -4116,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>104</v>
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>105</v>
@@ -4167,7 +4167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>2</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>124</v>
@@ -4202,7 +4202,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>77</v>
@@ -4237,7 +4237,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>2</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>115</v>
@@ -4272,7 +4272,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>84</v>
@@ -4306,8 +4306,8 @@
       <c r="B109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C109" s="10" t="n">
-        <v>102</v>
+      <c r="C109" s="4" t="n">
+        <v>105</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>112</v>
@@ -4342,7 +4342,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         <v>1</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111">
@@ -4377,7 +4377,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>120</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112">
@@ -4412,7 +4412,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="7" t="n">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113">
@@ -4447,7 +4447,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
@@ -4463,13 +4463,13 @@
         <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114">
@@ -4481,8 +4481,8 @@
       <c r="B114" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C114" s="9" t="n">
-        <v>74</v>
+      <c r="C114" s="10" t="n">
+        <v>81</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
         <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>96</v>
@@ -4517,7 +4517,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>183</v>
@@ -4552,7 +4552,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -4568,13 +4568,13 @@
         <v>2</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="117">
@@ -4587,7 +4587,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>2</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>123</v>
@@ -4622,7 +4622,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="9" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         <v>2</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>103</v>
@@ -4657,7 +4657,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>264</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120">
@@ -4692,7 +4692,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="7" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>188</v>
@@ -4726,8 +4726,8 @@
       <c r="B121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C121" s="4" t="n">
-        <v>126</v>
+      <c r="C121" s="9" t="n">
+        <v>107</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
         <v>2</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>113</v>
@@ -4762,7 +4762,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="123">
@@ -4796,8 +4796,8 @@
       <c r="B123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C123" s="10" t="n">
-        <v>112</v>
+      <c r="C123" s="9" t="n">
+        <v>101</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>2</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>116</v>
@@ -4832,7 +4832,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="125">
@@ -4886,7 +4886,7 @@
         <v>3</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>95</v>
@@ -4902,7 +4902,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="9" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4918,13 +4918,13 @@
         <v>1</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="127">
@@ -4937,7 +4937,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="9" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>4</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>87</v>
@@ -4972,7 +4972,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="10" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>3</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>98</v>
@@ -5007,7 +5007,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>2</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>109</v>
@@ -5041,8 +5041,8 @@
       <c r="B130" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C130" s="9" t="n">
-        <v>84</v>
+      <c r="C130" s="10" t="n">
+        <v>96</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -5058,13 +5058,13 @@
         <v>1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="131">
@@ -5076,12 +5076,12 @@
       <c r="B131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C131" s="4" t="n">
-        <v>118</v>
+      <c r="C131" s="7" t="n">
+        <v>223</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -5093,13 +5093,13 @@
         <v>1</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
     </row>
     <row r="132">
@@ -5111,8 +5111,8 @@
       <c r="B132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C132" s="5" t="n">
-        <v>141</v>
+      <c r="C132" s="4" t="n">
+        <v>121</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="133">
@@ -5147,7 +5147,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
         <v>1</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="134">
@@ -5182,7 +5182,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>101</v>
@@ -5217,7 +5217,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136">
@@ -5252,7 +5252,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>1</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137">
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>194</v>
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5357,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="140">
@@ -5411,10 +5411,10 @@
         <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141">
@@ -5426,8 +5426,8 @@
       <c r="B141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C141" s="9" t="n">
-        <v>125</v>
+      <c r="C141" s="10" t="n">
+        <v>131</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>114</v>
@@ -5462,16 +5462,16 @@
         <v>141</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>197</v>
+        <v>168</v>
       </c>
     </row>
     <row r="143">
@@ -5497,16 +5497,16 @@
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144">
@@ -5531,8 +5531,8 @@
       <c r="B144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C144" s="5" t="n">
-        <v>151</v>
+      <c r="C144" s="4" t="n">
+        <v>136</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="145">
@@ -5567,7 +5567,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="7" t="n">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5586,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146">
@@ -5602,7 +5602,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="7" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
@@ -5618,13 +5618,13 @@
         <v>1</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="147">
@@ -5637,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="7" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="148">
@@ -5672,7 +5672,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="7" t="n">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>209</v>
@@ -5707,7 +5707,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="7" t="n">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>180</v>
@@ -5742,7 +5742,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>139</v>
@@ -5777,7 +5777,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>140</v>
@@ -5812,7 +5812,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="153">
@@ -5846,8 +5846,8 @@
       <c r="B153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C153" s="10" t="n">
-        <v>107</v>
+      <c r="C153" s="4" t="n">
+        <v>122</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
@@ -5863,13 +5863,13 @@
         <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="154">
@@ -5882,7 +5882,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>215</v>
@@ -5916,30 +5916,30 @@
       <c r="B155" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="C155" s="4" t="n">
-        <v>178</v>
+      <c r="C155" s="9" t="n">
+        <v>104</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>161</v>
+        <v>111</v>
       </c>
     </row>
     <row r="156">
@@ -5951,30 +5951,30 @@
       <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C156" s="9" t="n">
-        <v>101</v>
+      <c r="C156" s="4" t="n">
+        <v>228</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="157">
@@ -5987,16 +5987,16 @@
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>227</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158">
@@ -6022,29 +6022,29 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="159">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -6076,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="160">
@@ -6092,7 +6092,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>213</v>
@@ -6127,7 +6127,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="9" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -6143,13 +6143,13 @@
         <v>1</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162">
@@ -6162,7 +6162,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -6181,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163">
@@ -6196,30 +6196,30 @@
       <c r="B163" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="C163" s="5" t="n">
-        <v>192</v>
+      <c r="C163" s="10" t="n">
+        <v>137</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164">
@@ -6232,11 +6232,11 @@
         <v>163</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165">
@@ -6267,7 +6267,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
@@ -6286,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166">
@@ -6301,17 +6301,17 @@
       <c r="B166" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C166" s="5" t="n">
-        <v>267</v>
+      <c r="C166" s="4" t="n">
+        <v>182</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>147</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167">
@@ -6336,17 +6336,17 @@
       <c r="B167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C167" s="4" t="n">
-        <v>176</v>
+      <c r="C167" s="5" t="n">
+        <v>198</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
@@ -6356,10 +6356,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="168">
@@ -6371,30 +6371,30 @@
       <c r="B168" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C168" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Mike Washington</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Dylan Sampson</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="3" t="n">
-        <v>212</v>
-      </c>
       <c r="I168" s="3" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="169">
@@ -6406,17 +6406,17 @@
       <c r="B169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C169" s="4" t="n">
-        <v>164</v>
+      <c r="C169" s="5" t="n">
+        <v>229</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
@@ -6426,10 +6426,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>157</v>
+        <v>243</v>
       </c>
     </row>
     <row r="170">
@@ -6442,7 +6442,7 @@
         <v>181</v>
       </c>
       <c r="C170" s="9" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>107</v>
@@ -6477,7 +6477,7 @@
         <v>182</v>
       </c>
       <c r="C171" s="9" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         <v>1</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="172">
@@ -6512,7 +6512,7 @@
         <v>183</v>
       </c>
       <c r="C172" s="9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6531,10 +6531,10 @@
         <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173">
@@ -6547,7 +6547,7 @@
         <v>184</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="174">
@@ -6582,7 +6582,7 @@
         <v>185</v>
       </c>
       <c r="C174" s="9" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6598,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>106</v>
@@ -6617,7 +6617,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176">
@@ -6652,7 +6652,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6671,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="177">
@@ -6706,10 +6706,10 @@
         <v>1</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
@@ -6722,7 +6722,7 @@
         <v>189</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>191</v>
@@ -6779,7 +6779,7 @@
         <v>206</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="180">
@@ -6792,7 +6792,7 @@
         <v>191</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="181">
@@ -6827,7 +6827,7 @@
         <v>192</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="182">
@@ -6862,7 +6862,7 @@
         <v>193</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="183">
@@ -6897,7 +6897,7 @@
         <v>194</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>187</v>
@@ -6932,7 +6932,7 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="185">
@@ -6967,7 +6967,7 @@
         <v>196</v>
       </c>
       <c r="C185" s="10" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
@@ -6983,13 +6983,13 @@
         <v>0</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="186">
@@ -7001,17 +7001,17 @@
       <c r="B186" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C186" s="5" t="n">
-        <v>264</v>
+      <c r="C186" s="4" t="n">
+        <v>175</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>218</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187">
@@ -7037,7 +7037,7 @@
         <v>198</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>1</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188">
@@ -7072,7 +7072,7 @@
         <v>199</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -7091,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189">
@@ -7107,7 +7107,7 @@
         <v>200</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
@@ -7126,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190">
@@ -7141,17 +7141,17 @@
       <c r="B190" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="C190" s="5" t="n">
-        <v>263</v>
+      <c r="C190" s="4" t="n">
+        <v>183</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -7161,10 +7161,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="191">
@@ -7177,16 +7177,16 @@
         <v>202</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -7196,10 +7196,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="192">
@@ -7211,17 +7211,17 @@
       <c r="B192" s="3" t="n">
         <v>203</v>
       </c>
-      <c r="C192" s="5" t="n">
-        <v>266</v>
+      <c r="C192" s="4" t="n">
+        <v>220</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Tank Dell</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>257</v>
+        <v>217</v>
       </c>
     </row>
     <row r="193">
@@ -7247,7 +7247,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="10" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>182</v>
@@ -7281,8 +7281,8 @@
       <c r="B194" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="C194" s="5" t="n">
-        <v>259</v>
+      <c r="C194" s="4" t="n">
+        <v>216</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="195">
@@ -7316,30 +7316,30 @@
       <c r="B195" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C195" s="4" t="n">
+      <c r="C195" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Schultz</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Schultz</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" s="3" t="n">
-        <v>215</v>
-      </c>
       <c r="I195" s="3" t="n">
-        <v>211</v>
+        <v>177</v>
       </c>
     </row>
     <row r="196">
@@ -7352,7 +7352,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -7371,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="197">
@@ -7386,8 +7386,8 @@
       <c r="B197" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="C197" s="4" t="n">
-        <v>223</v>
+      <c r="C197" s="5" t="n">
+        <v>266</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
@@ -7406,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="198">
@@ -7421,8 +7421,8 @@
       <c r="B198" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C198" s="5" t="n">
-        <v>257</v>
+      <c r="C198" s="4" t="n">
+        <v>184</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -7441,10 +7441,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>234</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199">
@@ -7456,8 +7456,8 @@
       <c r="B199" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C199" s="4" t="n">
-        <v>202</v>
+      <c r="C199" s="5" t="n">
+        <v>270</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
@@ -7476,10 +7476,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="200">
@@ -7492,7 +7492,7 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
@@ -7511,10 +7511,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="201">
@@ -7526,8 +7526,8 @@
       <c r="B201" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="C201" s="4" t="n">
-        <v>239</v>
+      <c r="C201" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
@@ -7546,10 +7546,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="202">
@@ -7562,7 +7562,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
@@ -7581,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="203">
@@ -7596,8 +7596,8 @@
       <c r="B203" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="C203" s="5" t="n">
-        <v>260</v>
+      <c r="C203" s="4" t="n">
+        <v>236</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7616,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="204">
@@ -7632,7 +7632,7 @@
         <v>216</v>
       </c>
       <c r="C204" s="10" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>179</v>
@@ -7667,7 +7667,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I205" s="3" t="n">
         <v>178</v>
@@ -7702,7 +7702,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>193</v>
@@ -7737,7 +7737,7 @@
         <v>219</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
@@ -7756,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208">
@@ -7772,7 +7772,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="209">
@@ -7807,7 +7807,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
@@ -7826,11 +7826,9 @@
         <v>0</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I209" s="3" t="n">
-        <v>284</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="I209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7861,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>288</v>
@@ -7877,7 +7875,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
@@ -7896,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="212">
@@ -7912,7 +7910,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
@@ -7931,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="213">
@@ -7947,7 +7945,7 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
@@ -7966,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
     </row>
@@ -7980,7 +7978,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -7999,10 +7997,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="215">
@@ -8015,7 +8013,7 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
@@ -8034,9 +8032,11 @@
         <v>0</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="I215" s="3" t="inlineStr"/>
+        <v>261</v>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -8047,8 +8047,8 @@
       <c r="B216" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C216" s="5" t="n">
-        <v>269</v>
+      <c r="C216" s="4" t="n">
+        <v>246</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
@@ -8067,9 +8067,11 @@
         <v>0</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="I216" s="3" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -8080,8 +8082,8 @@
       <c r="B217" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C217" s="4" t="n">
-        <v>256</v>
+      <c r="C217" s="5" t="n">
+        <v>271</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
@@ -8100,10 +8102,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="218">
@@ -8116,7 +8118,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
@@ -8135,10 +8137,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="219">
@@ -8151,7 +8153,7 @@
         <v>231</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
@@ -8170,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="I219" s="3" t="n">
         <v>208</v>
@@ -8186,7 +8188,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
@@ -8205,10 +8207,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="221">
@@ -8240,10 +8242,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>261</v>
+        <v>184</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="222">
@@ -8255,17 +8257,17 @@
       <c r="B222" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C222" s="5" t="n">
-        <v>285</v>
+      <c r="C222" s="4" t="n">
+        <v>204</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -8275,10 +8277,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>268</v>
+        <v>211</v>
       </c>
     </row>
     <row r="223">
@@ -8291,7 +8293,7 @@
         <v>237</v>
       </c>
       <c r="C223" s="10" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
@@ -8310,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224">
@@ -8326,7 +8328,7 @@
         <v>238</v>
       </c>
       <c r="C224" s="10" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -8345,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="225">
@@ -8360,8 +8362,8 @@
       <c r="B225" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C225" s="10" t="n">
-        <v>196</v>
+      <c r="C225" s="4" t="n">
+        <v>202</v>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
@@ -8380,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="I225" s="3" t="n">
         <v>195</v>
@@ -8396,7 +8398,7 @@
         <v>240</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -8415,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="227">
@@ -8450,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="228">
@@ -8465,8 +8467,8 @@
       <c r="B228" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C228" s="5" t="n">
-        <v>299</v>
+      <c r="C228" s="4" t="n">
+        <v>256</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
@@ -8485,11 +8487,9 @@
         <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I228" s="3" t="n">
-        <v>289</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -8500,8 +8500,8 @@
       <c r="B229" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C229" s="5" t="n">
-        <v>280</v>
+      <c r="C229" s="4" t="n">
+        <v>266</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="I229" s="3" t="inlineStr"/>
     </row>
@@ -8533,8 +8533,8 @@
       <c r="B230" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C230" s="10" t="n">
-        <v>195</v>
+      <c r="C230" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="231">
@@ -8569,7 +8569,7 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="232">
@@ -8604,7 +8604,7 @@
         <v>246</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
@@ -8623,10 +8623,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="233">
@@ -8639,7 +8639,7 @@
         <v>247</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
@@ -8658,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="234">
@@ -8674,7 +8674,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
@@ -8693,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="235">
@@ -8709,29 +8709,29 @@
         <v>249</v>
       </c>
       <c r="C235" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I235" s="3" t="n">
         <v>274</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Emari Demercado</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="I235" s="3" t="n">
-        <v>273</v>
       </c>
     </row>
     <row r="236">
@@ -8744,7 +8744,7 @@
         <v>250</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="237">
@@ -8779,7 +8779,7 @@
         <v>251</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
@@ -8798,10 +8798,10 @@
         <v>0</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>264</v>
+        <v>174</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="238">
@@ -8814,16 +8814,16 @@
         <v>252</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>204</v>
+        <v>285</v>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -8833,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="239">
@@ -8849,16 +8849,16 @@
         <v>253</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -8868,10 +8868,10 @@
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="240">
@@ -8884,7 +8884,7 @@
         <v>256</v>
       </c>
       <c r="C240" s="10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="241">
@@ -8919,7 +8919,7 @@
         <v>257</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
     </row>
@@ -8951,8 +8951,8 @@
       <c r="B242" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C242" s="4" t="n">
-        <v>219</v>
+      <c r="C242" s="10" t="n">
+        <v>186</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="243">
@@ -8987,7 +8987,7 @@
         <v>259</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
     </row>
@@ -9020,7 +9020,7 @@
         <v>260</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
@@ -9039,10 +9039,10 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="245">
@@ -9054,12 +9054,12 @@
       <c r="B245" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C245" s="4" t="n">
-        <v>205</v>
+      <c r="C245" s="5" t="n">
+        <v>306</v>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -9074,10 +9074,10 @@
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246">
@@ -9087,19 +9087,19 @@
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
@@ -9109,11 +9109,9 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>293</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="I246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -9125,7 +9123,7 @@
         <v>264</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
@@ -9144,10 +9142,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="248">
@@ -9160,7 +9158,7 @@
         <v>265</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
@@ -9179,10 +9177,10 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="249">
@@ -9214,10 +9212,10 @@
         <v>0</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="250">
@@ -9230,7 +9228,7 @@
         <v>268</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
@@ -9249,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>192</v>
@@ -9265,7 +9263,7 @@
         <v>269</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
@@ -9284,10 +9282,10 @@
         <v>0</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="252">
@@ -9300,7 +9298,7 @@
         <v>270</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
@@ -9319,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="253">
@@ -9335,7 +9333,7 @@
         <v>271</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
@@ -9354,10 +9352,10 @@
         <v>0</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="254">
@@ -9370,7 +9368,7 @@
         <v>272</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
@@ -9389,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="I254" s="3" t="n">
         <v>286</v>
@@ -9404,17 +9402,17 @@
       <c r="B255" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C255" s="5" t="n">
-        <v>334</v>
+      <c r="C255" s="4" t="n">
+        <v>299</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Ashton Dulin</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F255" s="3" t="n">
@@ -9424,9 +9422,11 @@
         <v>0</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="I255" s="3" t="inlineStr"/>
+        <v>260</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>275</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -9437,17 +9437,17 @@
       <c r="B256" s="3" t="n">
         <v>274</v>
       </c>
-      <c r="C256" s="4" t="n">
-        <v>300</v>
+      <c r="C256" s="5" t="n">
+        <v>324</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
@@ -9457,11 +9457,9 @@
         <v>0</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="I256" s="3" t="n">
-        <v>274</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -9473,16 +9471,16 @@
         <v>275</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F257" s="3" t="n">
@@ -9492,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
     </row>
@@ -9525,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
     </row>
@@ -9539,11 +9537,11 @@
         <v>277</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
@@ -9558,9 +9556,11 @@
         <v>0</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I259" s="3" t="inlineStr"/>
+        <v>241</v>
+      </c>
+      <c r="I259" s="3" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
         <v>278</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         <v>279</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
     </row>
@@ -9638,7 +9638,7 @@
         <v>280</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
@@ -9657,9 +9657,11 @@
         <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="I262" s="3" t="inlineStr"/>
+        <v>262</v>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -9671,7 +9673,7 @@
         <v>281</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
@@ -9690,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
     </row>
@@ -9723,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>176</v>
+        <v>271</v>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
     </row>
@@ -9737,7 +9739,7 @@
         <v>283</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
@@ -9756,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="I265" s="3" t="inlineStr"/>
     </row>
@@ -9769,17 +9771,17 @@
       <c r="B266" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="C266" s="5" t="n">
-        <v>358</v>
+      <c r="C266" s="4" t="n">
+        <v>248</v>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Malachi Fields</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="F266" s="3" t="n">
@@ -9789,9 +9791,11 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="I266" s="3" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="I266" s="3" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
@@ -9803,7 +9807,7 @@
         <v>287</v>
       </c>
       <c r="C267" s="10" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
@@ -9822,10 +9826,10 @@
         <v>0</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="268">
@@ -9838,7 +9842,7 @@
         <v>288</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
@@ -9857,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I268" s="3" t="inlineStr"/>
     </row>
@@ -9871,7 +9875,7 @@
         <v>289</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
@@ -9890,10 +9894,10 @@
         <v>0</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="270">
@@ -9906,7 +9910,7 @@
         <v>290</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
@@ -9925,10 +9929,10 @@
         <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>259</v>
+        <v>178</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="271">
@@ -9941,7 +9945,7 @@
         <v>291</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
@@ -9960,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="I271" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="272">
@@ -9976,7 +9980,7 @@
         <v>292</v>
       </c>
       <c r="C272" s="4" t="n">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
@@ -9995,10 +9999,10 @@
         <v>0</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="I272" s="3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="273">
@@ -10011,7 +10015,7 @@
         <v>293</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r=